--- a/research/traditional_assets/database/data/south_africa/south_africa_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_paper_forest_products.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0102</v>
+        <v>0.00365</v>
       </c>
       <c r="E2">
         <v>-0.31</v>
       </c>
       <c r="G2">
-        <v>0.1066324661048003</v>
+        <v>0.1055459521751656</v>
       </c>
       <c r="H2">
-        <v>0.09893733968486625</v>
+        <v>0.09798329011812157</v>
       </c>
       <c r="I2">
-        <v>0.05258336386954929</v>
+        <v>0.05145311149524633</v>
       </c>
       <c r="J2">
-        <v>0.02629168193477464</v>
+        <v>0.03170419664192384</v>
       </c>
       <c r="K2">
-        <v>33</v>
+        <v>40.45</v>
       </c>
       <c r="L2">
-        <v>0.006046170758519604</v>
+        <v>0.007283563814462691</v>
       </c>
       <c r="M2">
         <v>84</v>
       </c>
       <c r="N2">
-        <v>0.05371530886302597</v>
+        <v>0.05184225143491946</v>
       </c>
       <c r="O2">
-        <v>2.545454545454545</v>
+        <v>2.07663782447466</v>
       </c>
       <c r="P2">
         <v>84</v>
       </c>
       <c r="Q2">
-        <v>0.05371530886302597</v>
+        <v>0.05184225143491946</v>
       </c>
       <c r="R2">
-        <v>2.545454545454545</v>
+        <v>2.07663782447466</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -638,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>317</v>
+        <v>320.12</v>
       </c>
       <c r="V2">
-        <v>0.2027113441616575</v>
+        <v>0.1975683515398383</v>
       </c>
       <c r="W2">
-        <v>0.01349693251533742</v>
+        <v>0.03290717412283725</v>
       </c>
       <c r="X2">
-        <v>0.1464241157441407</v>
+        <v>0.1334164176066413</v>
       </c>
       <c r="Y2">
-        <v>-0.1329271832288033</v>
+        <v>-0.100509243483804</v>
       </c>
       <c r="Z2">
-        <v>1.570195627157652</v>
+        <v>1.529622386867546</v>
       </c>
       <c r="AA2">
-        <v>0.04128308400460299</v>
+        <v>0.01768277931170489</v>
       </c>
       <c r="AB2">
-        <v>0.1054198300456259</v>
+        <v>0.1038788210958037</v>
       </c>
       <c r="AC2">
-        <v>-0.06413674604102293</v>
+        <v>-0.08619604178409879</v>
       </c>
       <c r="AD2">
-        <v>1739</v>
+        <v>1765.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1739</v>
+        <v>1765.6</v>
       </c>
       <c r="AG2">
-        <v>1422</v>
+        <v>1445.48</v>
       </c>
       <c r="AH2">
-        <v>0.5265229502240523</v>
+        <v>0.5214566289612806</v>
       </c>
       <c r="AI2">
-        <v>0.4028260365994904</v>
+        <v>0.3925212867655232</v>
       </c>
       <c r="AJ2">
-        <v>0.4762542702123383</v>
+        <v>0.4714884955867675</v>
       </c>
       <c r="AK2">
-        <v>0.3555</v>
+        <v>0.3459758064902178</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>103.16</v>
       </c>
       <c r="AM2">
-        <v>72</v>
+        <v>74.23599999999999</v>
       </c>
       <c r="AN2">
-        <v>3.22037037037037</v>
+        <v>3.244633931196707</v>
       </c>
       <c r="AO2">
-        <v>2.87</v>
+        <v>2.769968980224893</v>
       </c>
       <c r="AP2">
-        <v>2.633333333333333</v>
+        <v>2.656351073213761</v>
       </c>
       <c r="AQ2">
-        <v>3.986111111111111</v>
+        <v>3.849210625572499</v>
       </c>
     </row>
     <row r="3">
@@ -781,10 +781,10 @@
         <v>0.01349693251533742</v>
       </c>
       <c r="X3">
-        <v>0.1464241157441407</v>
+        <v>0.1464140487457471</v>
       </c>
       <c r="Y3">
-        <v>-0.1329271832288033</v>
+        <v>-0.1329171162304096</v>
       </c>
       <c r="Z3">
         <v>1.570195627157652</v>
@@ -793,10 +793,10 @@
         <v>0.04128308400460299</v>
       </c>
       <c r="AB3">
-        <v>0.1054198300456259</v>
+        <v>0.1054150635529264</v>
       </c>
       <c r="AC3">
-        <v>-0.06413674604102293</v>
+        <v>-0.06413197954832342</v>
       </c>
       <c r="AD3">
         <v>1739</v>
@@ -839,6 +839,134 @@
       </c>
       <c r="AQ3">
         <v>3.986111111111111</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>York Timber Holdings Limited (JSE:YRK)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Paper/Forest Products</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0175</v>
+      </c>
+      <c r="G4">
+        <v>0.04351464435146444</v>
+      </c>
+      <c r="H4">
+        <v>0.04351464435146444</v>
+      </c>
+      <c r="I4">
+        <v>-0.01307531380753138</v>
+      </c>
+      <c r="J4">
+        <v>-0.009575744523750925</v>
+      </c>
+      <c r="K4">
+        <v>7.45</v>
+      </c>
+      <c r="L4">
+        <v>0.07792887029288703</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>3.12</v>
+      </c>
+      <c r="V4">
+        <v>0.0552212389380531</v>
+      </c>
+      <c r="W4">
+        <v>0.05231741573033707</v>
+      </c>
+      <c r="X4">
+        <v>0.1204187864675355</v>
+      </c>
+      <c r="Y4">
+        <v>-0.06810137073719841</v>
+      </c>
+      <c r="Z4">
+        <v>0.6179702650290885</v>
+      </c>
+      <c r="AA4">
+        <v>-0.005917525381193201</v>
+      </c>
+      <c r="AB4">
+        <v>0.102342578638681</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1082601040198742</v>
+      </c>
+      <c r="AD4">
+        <v>26.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>26.6</v>
+      </c>
+      <c r="AG4">
+        <v>23.48</v>
+      </c>
+      <c r="AH4">
+        <v>0.3200962695547533</v>
+      </c>
+      <c r="AI4">
+        <v>0.1468801766979569</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2935733933483371</v>
+      </c>
+      <c r="AK4">
+        <v>0.1319249353859984</v>
+      </c>
+      <c r="AL4">
+        <v>3.16</v>
+      </c>
+      <c r="AM4">
+        <v>2.236</v>
+      </c>
+      <c r="AN4">
+        <v>6.394230769230769</v>
+      </c>
+      <c r="AO4">
+        <v>-0.3955696202531646</v>
+      </c>
+      <c r="AP4">
+        <v>5.644230769230769</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.5590339892665473</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1261,7 @@
         <v>2.87</v>
       </c>
       <c r="F2">
-        <v>13.0645378347269</v>
+        <v>13.2928832776949</v>
       </c>
       <c r="G2">
         <v>3.22037037037037</v>
@@ -1151,13 +1279,13 @@
         <v>1563.8</v>
       </c>
       <c r="L2">
-        <v>3134.90527175185</v>
+        <v>3142.09461268774</v>
       </c>
       <c r="M2">
         <v>2985.8</v>
       </c>
       <c r="N2">
-        <v>3214.24127175185</v>
+        <v>3221.43061268774</v>
       </c>
       <c r="O2">
         <v>1739</v>
@@ -1166,16 +1294,16 @@
         <v>396.336</v>
       </c>
       <c r="Q2">
-        <v>0.105419830045626</v>
+        <v>0.105415063552926</v>
       </c>
       <c r="R2">
-        <v>0.101182553299494</v>
+        <v>0.101054536930044</v>
       </c>
       <c r="S2">
         <v>0.06854662591949751</v>
       </c>
       <c r="T2">
-        <v>0.0594946259194975</v>
+        <v>0.0584726259194975</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1316,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.146424115744141</v>
+        <v>0.146414048745747</v>
       </c>
       <c r="X2">
-        <v>0.106867270669493</v>
+        <v>0.106861161158754</v>
       </c>
       <c r="Y2">
         <v>1.20533037820222</v>
@@ -1230,7 +1358,7 @@
         <v>1563.8</v>
       </c>
       <c r="AK2">
-        <v>0.08348260158698076</v>
+        <v>0.08347424952137643</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1013386504641941</v>
+        <v>0.1013330940674907</v>
       </c>
       <c r="C2">
-        <v>3522.207311708001</v>
+        <v>3522.271734724556</v>
       </c>
       <c r="D2">
-        <v>3205.207311708001</v>
+        <v>3205.271734724556</v>
       </c>
       <c r="E2">
         <v>-1739</v>
@@ -1469,19 +1597,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1013386504641941</v>
+        <v>0.1013330940674907</v>
       </c>
       <c r="T2">
         <v>0.6652721574126822</v>
       </c>
       <c r="U2">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V2">
         <v>0.27</v>
       </c>
       <c r="W2">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1628,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1013256423671357</v>
+        <v>0.1013098809727034</v>
       </c>
       <c r="C3">
-        <v>3489.930201675688</v>
+        <v>3490.584113685801</v>
       </c>
       <c r="D3">
-        <v>3205.958201675688</v>
+        <v>3206.612113685801</v>
       </c>
       <c r="E3">
         <v>-1705.972</v>
@@ -1533,37 +1661,37 @@
         <v>422</v>
       </c>
       <c r="M3">
-        <v>2.691765075163237</v>
+        <v>2.645525875163237</v>
       </c>
       <c r="N3">
-        <v>419.3082349248368</v>
+        <v>419.3544741248368</v>
       </c>
       <c r="O3">
-        <v>113.2132234297059</v>
+        <v>113.2257080137059</v>
       </c>
       <c r="P3">
-        <v>306.0950114951308</v>
+        <v>306.1287661111309</v>
       </c>
       <c r="Q3">
-        <v>559.0950114951308</v>
+        <v>559.1287661111309</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1017481778868089</v>
+        <v>0.1017425805186954</v>
       </c>
       <c r="T3">
         <v>0.670177699583503</v>
       </c>
       <c r="U3">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V3">
         <v>0.27</v>
       </c>
       <c r="W3">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>156.7744540167231</v>
+        <v>159.5145993323393</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1710,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1013126342700774</v>
+        <v>0.1012866678779162</v>
       </c>
       <c r="C4">
-        <v>3457.653443550636</v>
+        <v>3458.89761415407</v>
       </c>
       <c r="D4">
-        <v>3206.709443550636</v>
+        <v>3207.95361415407</v>
       </c>
       <c r="E4">
         <v>-1672.944</v>
@@ -1615,37 +1743,37 @@
         <v>422</v>
       </c>
       <c r="M4">
-        <v>5.383530150326474</v>
+        <v>5.291051750326474</v>
       </c>
       <c r="N4">
-        <v>416.6164698496735</v>
+        <v>416.7089482496735</v>
       </c>
       <c r="O4">
-        <v>112.4864468594119</v>
+        <v>112.5114160274119</v>
       </c>
       <c r="P4">
-        <v>304.1300229902617</v>
+        <v>304.1975322222617</v>
       </c>
       <c r="Q4">
-        <v>557.1300229902618</v>
+        <v>557.1975322222617</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.102166063011926</v>
+        <v>0.1021604238362512</v>
       </c>
       <c r="T4">
         <v>0.6751833548598508</v>
       </c>
       <c r="U4">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V4">
         <v>0.27</v>
       </c>
       <c r="W4">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>78.38722700836153</v>
+        <v>79.75729966616964</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1792,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.101299626173019</v>
+        <v>0.1012634547831289</v>
       </c>
       <c r="C5">
-        <v>3425.377037580291</v>
+        <v>3427.212237537516</v>
       </c>
       <c r="D5">
-        <v>3207.46103758029</v>
+        <v>3209.296237537515</v>
       </c>
       <c r="E5">
         <v>-1639.916</v>
@@ -1697,37 +1825,37 @@
         <v>422</v>
       </c>
       <c r="M5">
-        <v>8.075295225489711</v>
+        <v>7.93657762548971</v>
       </c>
       <c r="N5">
-        <v>413.9247047745103</v>
+        <v>414.0634223745103</v>
       </c>
       <c r="O5">
-        <v>111.7596702891178</v>
+        <v>111.7971240411178</v>
       </c>
       <c r="P5">
-        <v>302.1650344853925</v>
+        <v>302.2662983333925</v>
       </c>
       <c r="Q5">
-        <v>555.1650344853925</v>
+        <v>555.2662983333926</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1025925643251898</v>
+        <v>0.1025868824799422</v>
       </c>
       <c r="T5">
         <v>0.6802922195233396</v>
       </c>
       <c r="U5">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V5">
         <v>0.27</v>
       </c>
       <c r="W5">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>52.25815133890769</v>
+        <v>53.17153311077978</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1874,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1012866180759607</v>
+        <v>0.1012402416883417</v>
       </c>
       <c r="C6">
-        <v>3393.100984012322</v>
+        <v>3395.527985246646</v>
       </c>
       <c r="D6">
-        <v>3208.212984012323</v>
+        <v>3210.639985246646</v>
       </c>
       <c r="E6">
         <v>-1606.888</v>
@@ -1779,37 +1907,37 @@
         <v>422</v>
       </c>
       <c r="M6">
-        <v>10.76706030065295</v>
+        <v>10.58210350065295</v>
       </c>
       <c r="N6">
-        <v>411.2329396993471</v>
+        <v>411.4178964993471</v>
       </c>
       <c r="O6">
-        <v>111.0328937188237</v>
+        <v>111.0828320548237</v>
       </c>
       <c r="P6">
-        <v>300.2000459805233</v>
+        <v>300.3350644445234</v>
       </c>
       <c r="Q6">
-        <v>553.2000459805233</v>
+        <v>553.3350644445234</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.10302795108248</v>
+        <v>0.1030222256787102</v>
       </c>
       <c r="T6">
         <v>0.685507518867318</v>
       </c>
       <c r="U6">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V6">
         <v>0.27</v>
       </c>
       <c r="W6">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.19361350418077</v>
+        <v>39.87864983308482</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1956,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1012736099789023</v>
+        <v>0.1012170285935544</v>
       </c>
       <c r="C7">
-        <v>3360.825283094638</v>
+        <v>3363.844858694334</v>
       </c>
       <c r="D7">
-        <v>3208.965283094638</v>
+        <v>3211.984858694334</v>
       </c>
       <c r="E7">
         <v>-1573.86</v>
@@ -1861,37 +1989,37 @@
         <v>422</v>
       </c>
       <c r="M7">
-        <v>13.45882537581619</v>
+        <v>13.22762937581618</v>
       </c>
       <c r="N7">
-        <v>408.5411746241838</v>
+        <v>408.7723706241838</v>
       </c>
       <c r="O7">
-        <v>110.3061171485296</v>
+        <v>110.3685400685296</v>
       </c>
       <c r="P7">
-        <v>298.2350574756542</v>
+        <v>298.4038305556542</v>
       </c>
       <c r="Q7">
-        <v>551.2350574756542</v>
+        <v>551.4038305556542</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1034725038767658</v>
+        <v>0.1034667339974521</v>
       </c>
       <c r="T7">
         <v>0.6908326139869589</v>
       </c>
       <c r="U7">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V7">
         <v>0.27</v>
       </c>
       <c r="W7">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.35489080334461</v>
+        <v>31.90291986646786</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2038,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.101260601881844</v>
+        <v>0.1011938154987671</v>
       </c>
       <c r="C8">
-        <v>3328.549935075378</v>
+        <v>3332.162859295823</v>
       </c>
       <c r="D8">
-        <v>3209.717935075378</v>
+        <v>3213.330859295823</v>
       </c>
       <c r="E8">
         <v>-1540.832</v>
@@ -1943,37 +2071,37 @@
         <v>422</v>
       </c>
       <c r="M8">
-        <v>16.15059045097942</v>
+        <v>15.87315525097942</v>
       </c>
       <c r="N8">
-        <v>405.8494095490206</v>
+        <v>406.1268447490206</v>
       </c>
       <c r="O8">
-        <v>109.5793405782356</v>
+        <v>109.6542480822356</v>
       </c>
       <c r="P8">
-        <v>296.270068970785</v>
+        <v>296.472596666785</v>
       </c>
       <c r="Q8">
-        <v>549.270068970785</v>
+        <v>549.472596666785</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1039265152411427</v>
+        <v>0.1039206999399971</v>
       </c>
       <c r="T8">
         <v>0.6962710090027625</v>
       </c>
       <c r="U8">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V8">
         <v>0.27</v>
       </c>
       <c r="W8">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.12907566945385</v>
+        <v>26.58576655538988</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2120,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1012475937847856</v>
+        <v>0.1011706024039799</v>
       </c>
       <c r="C9">
-        <v>3296.274940202912</v>
+        <v>3300.481988468726</v>
       </c>
       <c r="D9">
-        <v>3210.470940202912</v>
+        <v>3214.677988468726</v>
       </c>
       <c r="E9">
         <v>-1507.804</v>
@@ -2025,37 +2153,37 @@
         <v>422</v>
       </c>
       <c r="M9">
-        <v>18.84235552614266</v>
+        <v>18.51868112614266</v>
       </c>
       <c r="N9">
-        <v>403.1576444738573</v>
+        <v>403.4813188738573</v>
       </c>
       <c r="O9">
-        <v>108.8525640079415</v>
+        <v>108.9399560959415</v>
       </c>
       <c r="P9">
-        <v>294.3050804659158</v>
+        <v>294.5413627779159</v>
       </c>
       <c r="Q9">
-        <v>547.3050804659158</v>
+        <v>547.5413627779159</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1043902902907751</v>
+        <v>0.104384428590984</v>
       </c>
       <c r="T9">
         <v>0.7018263587500887</v>
       </c>
       <c r="U9">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V9">
         <v>0.27</v>
       </c>
       <c r="W9">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.39635057381757</v>
+        <v>22.7877999046199</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2202,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1012345856877273</v>
+        <v>0.1011473893091926</v>
       </c>
       <c r="C10">
-        <v>3264.000298725845</v>
+        <v>3268.802247633037</v>
       </c>
       <c r="D10">
-        <v>3211.224298725845</v>
+        <v>3216.026247633037</v>
       </c>
       <c r="E10">
         <v>-1474.776</v>
@@ -2107,37 +2235,37 @@
         <v>422</v>
       </c>
       <c r="M10">
-        <v>21.5341206013059</v>
+        <v>21.1642070013059</v>
       </c>
       <c r="N10">
-        <v>400.4658793986941</v>
+        <v>400.8357929986941</v>
       </c>
       <c r="O10">
-        <v>108.1257874376474</v>
+        <v>108.2256641096474</v>
       </c>
       <c r="P10">
-        <v>292.3400919610467</v>
+        <v>292.6101288890467</v>
       </c>
       <c r="Q10">
-        <v>545.3400919610467</v>
+        <v>545.6101288890467</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1048641474067038</v>
+        <v>0.1048582382996009</v>
       </c>
       <c r="T10">
         <v>0.7075024769701829</v>
       </c>
       <c r="U10">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V10">
         <v>0.27</v>
       </c>
       <c r="W10">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.59680675209038</v>
+        <v>19.93932491654241</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2284,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.101221577590669</v>
+        <v>0.1011241762144054</v>
       </c>
       <c r="C11">
-        <v>3231.726010893017</v>
+        <v>3237.123638211132</v>
       </c>
       <c r="D11">
-        <v>3211.978010893017</v>
+        <v>3217.375638211132</v>
       </c>
       <c r="E11">
         <v>-1441.748</v>
@@ -2189,37 +2317,37 @@
         <v>422</v>
       </c>
       <c r="M11">
-        <v>24.22588567646913</v>
+        <v>23.80973287646913</v>
       </c>
       <c r="N11">
-        <v>397.7741143235309</v>
+        <v>398.1902671235309</v>
       </c>
       <c r="O11">
-        <v>107.3990108673533</v>
+        <v>107.5113721233533</v>
       </c>
       <c r="P11">
-        <v>290.3751034561775</v>
+        <v>290.6788950001775</v>
       </c>
       <c r="Q11">
-        <v>543.3751034561775</v>
+        <v>543.6788950001776</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1053484189647409</v>
+        <v>0.1053424614084073</v>
       </c>
       <c r="T11">
         <v>0.7133033450412682</v>
       </c>
       <c r="U11">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V11">
         <v>0.27</v>
       </c>
       <c r="W11">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.4193837796359</v>
+        <v>17.72384437025992</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2366,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1012085694936106</v>
+        <v>0.1011009631196182</v>
       </c>
       <c r="C12">
-        <v>3199.452076953498</v>
+        <v>3205.446161627775</v>
       </c>
       <c r="D12">
-        <v>3212.732076953498</v>
+        <v>3218.726161627776</v>
       </c>
       <c r="E12">
         <v>-1408.72</v>
@@ -2271,37 +2399,37 @@
         <v>422</v>
       </c>
       <c r="M12">
-        <v>26.91765075163237</v>
+        <v>26.45525875163237</v>
       </c>
       <c r="N12">
-        <v>395.0823492483676</v>
+        <v>395.5447412483676</v>
       </c>
       <c r="O12">
-        <v>106.6722342970593</v>
+        <v>106.7970801370593</v>
       </c>
       <c r="P12">
-        <v>288.4101149513083</v>
+        <v>288.7476611113084</v>
       </c>
       <c r="Q12">
-        <v>541.4101149513083</v>
+        <v>541.7476611113084</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1058434521129565</v>
+        <v>0.1058374450307427</v>
       </c>
       <c r="T12">
         <v>0.7192331212917109</v>
       </c>
       <c r="U12">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V12">
         <v>0.27</v>
       </c>
       <c r="W12">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.6774454016723</v>
+        <v>15.95145993323393</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2448,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1011955613965523</v>
+        <v>0.1010777500248309</v>
       </c>
       <c r="C13">
-        <v>3167.178497156597</v>
+        <v>3173.769819310124</v>
       </c>
       <c r="D13">
-        <v>3213.486497156597</v>
+        <v>3220.077819310124</v>
       </c>
       <c r="E13">
         <v>-1375.692</v>
@@ -2353,37 +2481,37 @@
         <v>422</v>
       </c>
       <c r="M13">
-        <v>29.60941582679561</v>
+        <v>29.1007846267956</v>
       </c>
       <c r="N13">
-        <v>392.3905841732044</v>
+        <v>392.8992153732044</v>
       </c>
       <c r="O13">
-        <v>105.9454577267652</v>
+        <v>106.0827881507652</v>
       </c>
       <c r="P13">
-        <v>286.4451264464392</v>
+        <v>286.8164272224392</v>
       </c>
       <c r="Q13">
-        <v>539.4451264464392</v>
+        <v>539.8164272224392</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1063496096015815</v>
+        <v>0.1063435518805463</v>
       </c>
       <c r="T13">
         <v>0.7252961509410399</v>
       </c>
       <c r="U13">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.25222309242937</v>
+        <v>14.50132721203085</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2530,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1011825532994939</v>
+        <v>0.1010545369300437</v>
       </c>
       <c r="C14">
-        <v>3134.90527175185</v>
+        <v>3142.094612687737</v>
       </c>
       <c r="D14">
-        <v>3214.24127175185</v>
+        <v>3221.430612687737</v>
       </c>
       <c r="E14">
         <v>-1342.664</v>
@@ -2435,37 +2563,37 @@
         <v>422</v>
       </c>
       <c r="M14">
-        <v>32.30118090195884</v>
+        <v>31.74631050195884</v>
       </c>
       <c r="N14">
-        <v>389.6988190980412</v>
+        <v>390.2536894980412</v>
       </c>
       <c r="O14">
-        <v>105.2186811564711</v>
+        <v>105.3684961644711</v>
       </c>
       <c r="P14">
-        <v>284.48013794157</v>
+        <v>284.88519333357</v>
       </c>
       <c r="Q14">
-        <v>537.4801379415701</v>
+        <v>537.88519333357</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1068672706694934</v>
+        <v>0.1068611611587545</v>
       </c>
       <c r="T14">
         <v>0.7314969767187629</v>
       </c>
       <c r="U14">
-        <v>0.08149948756095546</v>
+        <v>0.08009948756095545</v>
       </c>
       <c r="V14">
         <v>0.27</v>
       </c>
       <c r="W14">
-        <v>0.05949462591949748</v>
+        <v>0.05847262591949747</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.06453783472692</v>
+        <v>13.29288327769494</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2612,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1012739352024356</v>
+        <v>0.1011736738352564</v>
       </c>
       <c r="C15">
-        <v>3096.582470096722</v>
+        <v>3102.135678780498</v>
       </c>
       <c r="D15">
-        <v>3208.946470096722</v>
+        <v>3214.499678780498</v>
       </c>
       <c r="E15">
         <v>-1309.636</v>
@@ -2517,37 +2645,37 @@
         <v>422</v>
       </c>
       <c r="M15">
-        <v>35.46524637712208</v>
+        <v>35.03588237712208</v>
       </c>
       <c r="N15">
-        <v>386.5347536228779</v>
+        <v>386.9641176228779</v>
       </c>
       <c r="O15">
-        <v>104.364383478177</v>
+        <v>104.480311758177</v>
       </c>
       <c r="P15">
-        <v>282.1703701447009</v>
+        <v>282.4838058647009</v>
       </c>
       <c r="Q15">
-        <v>535.1703701447009</v>
+        <v>535.4838058647008</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1073968319918401</v>
+        <v>0.1073906695008296</v>
       </c>
       <c r="T15">
         <v>0.7378403502155139</v>
       </c>
       <c r="U15">
-        <v>0.08259948756095545</v>
+        <v>0.08159948756095545</v>
       </c>
       <c r="V15">
         <v>0.27</v>
       </c>
       <c r="W15">
-        <v>0.06029762591949748</v>
+        <v>0.05956762591949748</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.89897274398251</v>
+        <v>12.04479440413808</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2694,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1012689571053772</v>
+        <v>0.1011614107404691</v>
       </c>
       <c r="C16">
-        <v>3063.84245905157</v>
+        <v>3069.819721947882</v>
       </c>
       <c r="D16">
-        <v>3209.23445905157</v>
+        <v>3215.211721947881</v>
       </c>
       <c r="E16">
         <v>-1276.608</v>
@@ -2599,37 +2727,37 @@
         <v>422</v>
       </c>
       <c r="M16">
-        <v>38.19334225228532</v>
+        <v>37.73095025228532</v>
       </c>
       <c r="N16">
-        <v>383.8066577477147</v>
+        <v>384.2690497477147</v>
       </c>
       <c r="O16">
-        <v>103.627797591883</v>
+        <v>103.752643431883</v>
       </c>
       <c r="P16">
-        <v>280.1788601558317</v>
+        <v>280.5164063158317</v>
       </c>
       <c r="Q16">
-        <v>533.1788601558317</v>
+        <v>533.5164063158318</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1079387086937762</v>
+        <v>0.1079324919903948</v>
       </c>
       <c r="T16">
         <v>0.7443312440261428</v>
       </c>
       <c r="U16">
-        <v>0.08259948756095545</v>
+        <v>0.08159948756095545</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.06029762591949748</v>
+        <v>0.05956762591949748</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.04904611941233</v>
+        <v>11.18445194669965</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2776,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1012639790083188</v>
+        <v>0.1011491476456819</v>
       </c>
       <c r="C17">
-        <v>3031.102499702561</v>
+        <v>3037.504080634227</v>
       </c>
       <c r="D17">
-        <v>3209.522499702561</v>
+        <v>3215.924080634227</v>
       </c>
       <c r="E17">
         <v>-1243.58</v>
@@ -2681,37 +2809,37 @@
         <v>422</v>
       </c>
       <c r="M17">
-        <v>40.92143812744855</v>
+        <v>40.42601812744855</v>
       </c>
       <c r="N17">
-        <v>381.0785618725515</v>
+        <v>381.5739818725514</v>
       </c>
       <c r="O17">
-        <v>102.8912117055889</v>
+        <v>103.0249751055889</v>
       </c>
       <c r="P17">
-        <v>278.1873501669626</v>
+        <v>278.5490067669625</v>
       </c>
       <c r="Q17">
-        <v>531.1873501669626</v>
+        <v>531.5490067669625</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1084933354357579</v>
+        <v>0.1084870632444203</v>
       </c>
       <c r="T17">
         <v>0.7509748647499631</v>
       </c>
       <c r="U17">
-        <v>0.08259948756095545</v>
+        <v>0.08159948756095545</v>
       </c>
       <c r="V17">
         <v>0.27</v>
       </c>
       <c r="W17">
-        <v>0.06029762591949748</v>
+        <v>0.05956762591949748</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.31244304478484</v>
+        <v>10.43882181691967</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2858,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1015159609112605</v>
+        <v>0.1011368845508946</v>
       </c>
       <c r="C18">
-        <v>2983.559061508878</v>
+        <v>3005.188755049304</v>
       </c>
       <c r="D18">
-        <v>3195.007061508878</v>
+        <v>3216.636755049304</v>
       </c>
       <c r="E18">
         <v>-1210.552</v>
@@ -2763,45 +2891,45 @@
         <v>422</v>
       </c>
       <c r="M18">
-        <v>44.81211960261179</v>
+        <v>43.12108600261179</v>
       </c>
       <c r="N18">
-        <v>377.1878803973882</v>
+        <v>378.8789139973882</v>
       </c>
       <c r="O18">
-        <v>101.8407277072948</v>
+        <v>102.2973067792948</v>
       </c>
       <c r="P18">
-        <v>275.3471526900934</v>
+        <v>276.5816072180934</v>
       </c>
       <c r="Q18">
-        <v>528.3471526900934</v>
+        <v>529.5816072180934</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1090611675763582</v>
+        <v>0.1090548385759227</v>
       </c>
       <c r="T18">
         <v>0.7577766669195886</v>
       </c>
       <c r="U18">
-        <v>0.08479948756095546</v>
+        <v>0.08159948756095545</v>
       </c>
       <c r="V18">
         <v>0.27</v>
       </c>
       <c r="W18">
-        <v>0.06190362591949748</v>
+        <v>0.05956762591949748</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.417095280076966</v>
+        <v>9.786395453362191</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2940,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1015270428142022</v>
+        <v>0.1013355914561074</v>
       </c>
       <c r="C19">
-        <v>2949.895701074059</v>
+        <v>2960.6515963633</v>
       </c>
       <c r="D19">
-        <v>3194.371701074059</v>
+        <v>3205.1275963633</v>
       </c>
       <c r="E19">
         <v>-1177.524</v>
@@ -2845,37 +2973,37 @@
         <v>422</v>
       </c>
       <c r="M19">
-        <v>47.61287707777503</v>
+        <v>46.77066307777503</v>
       </c>
       <c r="N19">
-        <v>374.387122922225</v>
+        <v>375.2293369222249</v>
       </c>
       <c r="O19">
-        <v>101.0845231890007</v>
+        <v>101.3119209690007</v>
       </c>
       <c r="P19">
-        <v>273.3025997332243</v>
+        <v>273.9174159532242</v>
       </c>
       <c r="Q19">
-        <v>526.3025997332243</v>
+        <v>526.9174159532242</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1096426824191417</v>
+        <v>0.1096362952407142</v>
       </c>
       <c r="T19">
         <v>0.7647423679366748</v>
       </c>
       <c r="U19">
-        <v>0.08479948756095546</v>
+        <v>0.08329948756095545</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.06190362591949748</v>
+        <v>0.06080862591949748</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.863148498895967</v>
+        <v>9.022749993906549</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +3022,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1015381247171438</v>
+        <v>0.1013357383613202</v>
       </c>
       <c r="C20">
-        <v>2916.232593285083</v>
+        <v>2927.615118039875</v>
       </c>
       <c r="D20">
-        <v>3193.736593285083</v>
+        <v>3205.119118039875</v>
       </c>
       <c r="E20">
         <v>-1144.496</v>
@@ -2927,37 +3055,37 @@
         <v>422</v>
       </c>
       <c r="M20">
-        <v>50.41363455293826</v>
+        <v>49.52187855293826</v>
       </c>
       <c r="N20">
-        <v>371.5863654470617</v>
+        <v>372.4781214470618</v>
       </c>
       <c r="O20">
-        <v>100.3283186707067</v>
+        <v>100.5690927907067</v>
       </c>
       <c r="P20">
-        <v>271.2580467763551</v>
+        <v>271.9090286563551</v>
       </c>
       <c r="Q20">
-        <v>524.2580467763551</v>
+        <v>524.9090286563551</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1102383805507735</v>
+        <v>0.1102319337753788</v>
       </c>
       <c r="T20">
         <v>0.7718779641005192</v>
       </c>
       <c r="U20">
-        <v>0.08479948756095546</v>
+        <v>0.08329948756095545</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.06190362591949748</v>
+        <v>0.06080862591949748</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.370751360068414</v>
+        <v>8.521486105356189</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3104,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1015492066200855</v>
+        <v>0.1013358852665329</v>
       </c>
       <c r="C21">
-        <v>2882.56973799128</v>
+        <v>2894.578639761304</v>
       </c>
       <c r="D21">
-        <v>3193.10173799128</v>
+        <v>3205.110639761304</v>
       </c>
       <c r="E21">
         <v>-1111.468</v>
@@ -3009,37 +3137,37 @@
         <v>422</v>
       </c>
       <c r="M21">
-        <v>53.2143920281015</v>
+        <v>52.2730940281015</v>
       </c>
       <c r="N21">
-        <v>368.7856079718985</v>
+        <v>369.7269059718985</v>
       </c>
       <c r="O21">
-        <v>99.57211415241261</v>
+        <v>99.8262646124126</v>
       </c>
       <c r="P21">
-        <v>269.2134938194859</v>
+        <v>269.9006413594859</v>
       </c>
       <c r="Q21">
-        <v>522.2134938194858</v>
+        <v>522.9006413594859</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1108487872782481</v>
+        <v>0.110842279434356</v>
       </c>
       <c r="T21">
         <v>0.779189747823965</v>
       </c>
       <c r="U21">
-        <v>0.08479948756095546</v>
+        <v>0.08329948756095545</v>
       </c>
       <c r="V21">
         <v>0.27</v>
       </c>
       <c r="W21">
-        <v>0.06190362591949748</v>
+        <v>0.06080862591949748</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.930185499012183</v>
+        <v>8.072986836653229</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3186,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1017792885230271</v>
+        <v>0.1013360321717457</v>
       </c>
       <c r="C22">
-        <v>2836.417689016254</v>
+        <v>2861.542161527588</v>
       </c>
       <c r="D22">
-        <v>3179.977689016254</v>
+        <v>3205.102161527588</v>
       </c>
       <c r="E22">
         <v>-1078.44</v>
@@ -3091,45 +3219,45 @@
         <v>422</v>
       </c>
       <c r="M22">
-        <v>57.00598950326474</v>
+        <v>55.02430950326474</v>
       </c>
       <c r="N22">
-        <v>364.9940104967353</v>
+        <v>366.9756904967352</v>
       </c>
       <c r="O22">
-        <v>98.54838283411853</v>
+        <v>99.08343643411852</v>
       </c>
       <c r="P22">
-        <v>266.4456276626167</v>
+        <v>267.8922540626167</v>
       </c>
       <c r="Q22">
-        <v>519.4456276626167</v>
+        <v>520.8922540626168</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1114744541739095</v>
+        <v>0.1114678837348077</v>
       </c>
       <c r="T22">
         <v>0.7866843261404968</v>
       </c>
       <c r="U22">
-        <v>0.08629948756095546</v>
+        <v>0.08329948756095545</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.06299862591949748</v>
+        <v>0.06080862591949748</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.402730900335166</v>
+        <v>7.669337494820568</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3268,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1018013204259688</v>
+        <v>0.1014588190769584</v>
       </c>
       <c r="C23">
-        <v>2802.138629947144</v>
+        <v>2821.443501714261</v>
       </c>
       <c r="D23">
-        <v>3178.726629947144</v>
+        <v>3198.031501714262</v>
       </c>
       <c r="E23">
         <v>-1045.412</v>
@@ -3173,37 +3301,37 @@
         <v>422</v>
       </c>
       <c r="M23">
-        <v>59.85628897842797</v>
+        <v>58.33039537842797</v>
       </c>
       <c r="N23">
-        <v>362.143711021572</v>
+        <v>363.669604621572</v>
       </c>
       <c r="O23">
-        <v>97.77880197582445</v>
+        <v>98.19079324782446</v>
       </c>
       <c r="P23">
-        <v>264.3649090457476</v>
+        <v>265.4788113737476</v>
       </c>
       <c r="Q23">
-        <v>517.3649090457476</v>
+        <v>518.4788113737476</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1121159607378156</v>
+        <v>0.1121093261188151</v>
       </c>
       <c r="T23">
         <v>0.7943686406169407</v>
       </c>
       <c r="U23">
-        <v>0.08629948756095546</v>
+        <v>0.08409948756095545</v>
       </c>
       <c r="V23">
         <v>0.27</v>
       </c>
       <c r="W23">
-        <v>0.06299862591949748</v>
+        <v>0.06139262591949748</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.050219905081111</v>
+        <v>7.234650087012201</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3350,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1018233523289104</v>
+        <v>0.1014648059821712</v>
       </c>
       <c r="C24">
-        <v>2767.860554868133</v>
+        <v>2788.071544502333</v>
       </c>
       <c r="D24">
-        <v>3177.476554868133</v>
+        <v>3197.687544502333</v>
       </c>
       <c r="E24">
         <v>-1012.384</v>
@@ -3255,37 +3383,37 @@
         <v>422</v>
       </c>
       <c r="M24">
-        <v>62.70658845359122</v>
+        <v>61.10803325359122</v>
       </c>
       <c r="N24">
-        <v>359.2934115464088</v>
+        <v>360.8919667464088</v>
       </c>
       <c r="O24">
-        <v>97.00922111753037</v>
+        <v>97.44083102153039</v>
       </c>
       <c r="P24">
-        <v>262.2841904288784</v>
+        <v>263.4511357248784</v>
       </c>
       <c r="Q24">
-        <v>515.2841904288784</v>
+        <v>516.4511357248784</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1127739161879756</v>
+        <v>0.1127672157434381</v>
       </c>
       <c r="T24">
         <v>0.8022499887979089</v>
       </c>
       <c r="U24">
-        <v>0.08629948756095546</v>
+        <v>0.08409948756095545</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.06299862591949748</v>
+        <v>0.06139262591949748</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.729755363941059</v>
+        <v>6.905802355784373</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3432,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1018453842318521</v>
+        <v>0.1014707928873839</v>
       </c>
       <c r="C25">
-        <v>2733.583462618777</v>
+        <v>2754.699661269565</v>
       </c>
       <c r="D25">
-        <v>3176.227462618777</v>
+        <v>3197.343661269565</v>
       </c>
       <c r="E25">
         <v>-979.3559999999999</v>
@@ -3337,37 +3465,37 @@
         <v>422</v>
       </c>
       <c r="M25">
-        <v>65.55688792875446</v>
+        <v>63.88567112875445</v>
       </c>
       <c r="N25">
-        <v>356.4431120712455</v>
+        <v>358.1143288712456</v>
       </c>
       <c r="O25">
-        <v>96.2396402592363</v>
+        <v>96.69086879523631</v>
       </c>
       <c r="P25">
-        <v>260.2034718120092</v>
+        <v>261.4234600760092</v>
       </c>
       <c r="Q25">
-        <v>513.2034718120092</v>
+        <v>514.4234600760092</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1134489613900878</v>
+        <v>0.1134421934102591</v>
       </c>
       <c r="T25">
         <v>0.8103360473212398</v>
       </c>
       <c r="U25">
-        <v>0.08629948756095546</v>
+        <v>0.08409948756095545</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.06299862591949748</v>
+        <v>0.06139262591949748</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.437157304639274</v>
+        <v>6.605550079445922</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3514,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1018674161347937</v>
+        <v>0.1014767797925966</v>
       </c>
       <c r="C26">
-        <v>2699.307352040455</v>
+        <v>2721.327851992091</v>
       </c>
       <c r="D26">
-        <v>3174.979352040455</v>
+        <v>3196.999851992091</v>
       </c>
       <c r="E26">
         <v>-946.328</v>
@@ -3419,37 +3547,37 @@
         <v>422</v>
       </c>
       <c r="M26">
-        <v>68.40718740391769</v>
+        <v>66.66330900391767</v>
       </c>
       <c r="N26">
-        <v>353.5928125960823</v>
+        <v>355.3366909960823</v>
       </c>
       <c r="O26">
-        <v>95.47005940094223</v>
+        <v>95.94090656894224</v>
       </c>
       <c r="P26">
-        <v>258.12275319514</v>
+        <v>259.3957844271401</v>
       </c>
       <c r="Q26">
-        <v>511.12275319514</v>
+        <v>512.3957844271401</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1141417709396241</v>
+        <v>0.1141349336472595</v>
       </c>
       <c r="T26">
         <v>0.8186348968583427</v>
       </c>
       <c r="U26">
-        <v>0.08629948756095546</v>
+        <v>0.08409948756095545</v>
       </c>
       <c r="V26">
         <v>0.27</v>
       </c>
       <c r="W26">
-        <v>0.06299862591949748</v>
+        <v>0.06139262591949748</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.168942416945971</v>
+        <v>6.330318826135676</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3596,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1021449480377354</v>
+        <v>0.1014827666978094</v>
       </c>
       <c r="C27">
-        <v>2650.640717308161</v>
+        <v>2687.956116646056</v>
       </c>
       <c r="D27">
-        <v>3159.34071730816</v>
+        <v>3196.656116646056</v>
       </c>
       <c r="E27">
         <v>-913.3</v>
@@ -3501,45 +3629,45 @@
         <v>422</v>
       </c>
       <c r="M27">
-        <v>72.41346687908093</v>
+        <v>69.44094687908091</v>
       </c>
       <c r="N27">
-        <v>349.5865331209191</v>
+        <v>352.5590531209191</v>
       </c>
       <c r="O27">
-        <v>94.38836394264816</v>
+        <v>95.19094434264817</v>
       </c>
       <c r="P27">
-        <v>255.1981691782709</v>
+        <v>257.3681087782709</v>
       </c>
       <c r="Q27">
-        <v>508.1981691782709</v>
+        <v>510.3681087782709</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1148530554104813</v>
+        <v>0.1148461469572467</v>
       </c>
       <c r="T27">
         <v>0.8271550490497682</v>
       </c>
       <c r="U27">
-        <v>0.08769948756095546</v>
+        <v>0.08409948756095545</v>
       </c>
       <c r="V27">
         <v>0.27</v>
       </c>
       <c r="W27">
-        <v>0.06402062591949748</v>
+        <v>0.06139262591949748</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>5.827645301179592</v>
+        <v>6.077106073090249</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3678,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.102177199940677</v>
+        <v>0.1016785536030222</v>
       </c>
       <c r="C28">
-        <v>2615.805342158607</v>
+        <v>2643.727694162791</v>
       </c>
       <c r="D28">
-        <v>3157.533342158607</v>
+        <v>3185.455694162791</v>
       </c>
       <c r="E28">
         <v>-880.2719999999999</v>
@@ -3583,37 +3711,37 @@
         <v>422</v>
       </c>
       <c r="M28">
-        <v>75.31000555424416</v>
+        <v>73.07731275424416</v>
       </c>
       <c r="N28">
-        <v>346.6899944457558</v>
+        <v>348.9226872457558</v>
       </c>
       <c r="O28">
-        <v>93.60629850035407</v>
+        <v>94.20912555635408</v>
       </c>
       <c r="P28">
-        <v>253.0836959454018</v>
+        <v>254.7135616894017</v>
       </c>
       <c r="Q28">
-        <v>506.0836959454018</v>
+        <v>507.7135616894017</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1155835637859563</v>
+        <v>0.1155765822485849</v>
       </c>
       <c r="T28">
         <v>0.8359054756247458</v>
       </c>
       <c r="U28">
-        <v>0.08769948756095546</v>
+        <v>0.08509948756095545</v>
       </c>
       <c r="V28">
         <v>0.27</v>
       </c>
       <c r="W28">
-        <v>0.06402062591949748</v>
+        <v>0.06212262591949748</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.603505097288069</v>
+        <v>5.774706048909703</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3760,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1022094518436187</v>
+        <v>0.1016918405082349</v>
       </c>
       <c r="C29">
-        <v>2580.972033729646</v>
+        <v>2609.942430714623</v>
       </c>
       <c r="D29">
-        <v>3155.728033729646</v>
+        <v>3184.698430714623</v>
       </c>
       <c r="E29">
         <v>-847.2439999999999</v>
@@ -3665,37 +3793,37 @@
         <v>422</v>
       </c>
       <c r="M29">
-        <v>78.2065442294074</v>
+        <v>75.8879786294074</v>
       </c>
       <c r="N29">
-        <v>343.7934557705926</v>
+        <v>346.1120213705926</v>
       </c>
       <c r="O29">
-        <v>92.82423305806</v>
+        <v>93.45024577006002</v>
       </c>
       <c r="P29">
-        <v>250.9692227125326</v>
+        <v>252.6617756005326</v>
       </c>
       <c r="Q29">
-        <v>503.9692227125325</v>
+        <v>505.6617756005326</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1163340860895265</v>
+        <v>0.1163270294657131</v>
       </c>
       <c r="T29">
         <v>0.8448956399141064</v>
       </c>
       <c r="U29">
-        <v>0.08769948756095546</v>
+        <v>0.08509948756095545</v>
       </c>
       <c r="V29">
         <v>0.27</v>
       </c>
       <c r="W29">
-        <v>0.06402062591949748</v>
+        <v>0.06212262591949748</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.395967871462585</v>
+        <v>5.560828047098234</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3842,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1022417037465603</v>
+        <v>0.1017051274134477</v>
       </c>
       <c r="C30">
-        <v>2546.140788478385</v>
+        <v>2576.157527222263</v>
       </c>
       <c r="D30">
-        <v>3153.924788478385</v>
+        <v>3183.941527222263</v>
       </c>
       <c r="E30">
         <v>-814.2159999999999</v>
@@ -3747,37 +3875,37 @@
         <v>422</v>
       </c>
       <c r="M30">
-        <v>81.10308290457064</v>
+        <v>78.69864450457064</v>
       </c>
       <c r="N30">
-        <v>340.8969170954293</v>
+        <v>343.3013554954293</v>
       </c>
       <c r="O30">
-        <v>92.04216761576592</v>
+        <v>92.69136598376592</v>
       </c>
       <c r="P30">
-        <v>248.8547494796634</v>
+        <v>250.6099895116634</v>
       </c>
       <c r="Q30">
-        <v>501.8547494796634</v>
+        <v>503.6099895116634</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1171054562348625</v>
+        <v>0.1170983224388727</v>
       </c>
       <c r="T30">
         <v>0.8541355309892825</v>
       </c>
       <c r="U30">
-        <v>0.08769948756095546</v>
+        <v>0.08509948756095545</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.06402062591949748</v>
+        <v>0.06212262591949748</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.203254733196064</v>
+        <v>5.362227045416153</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3924,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.102273955649502</v>
+        <v>0.1017184143186604</v>
       </c>
       <c r="C31">
-        <v>2511.311602870021</v>
+        <v>2542.37298342912</v>
       </c>
       <c r="D31">
-        <v>3152.123602870021</v>
+        <v>3183.18498342912</v>
       </c>
       <c r="E31">
         <v>-781.188</v>
@@ -3829,37 +3957,37 @@
         <v>422</v>
       </c>
       <c r="M31">
-        <v>83.99962157973387</v>
+        <v>81.50931037973386</v>
       </c>
       <c r="N31">
-        <v>338.0003784202661</v>
+        <v>340.4906896202662</v>
       </c>
       <c r="O31">
-        <v>91.26010217347186</v>
+        <v>91.93248619747187</v>
       </c>
       <c r="P31">
-        <v>246.7402762467943</v>
+        <v>248.5582034227943</v>
       </c>
       <c r="Q31">
-        <v>499.7402762467943</v>
+        <v>501.5582034227943</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1178985551166869</v>
+        <v>0.1178913419746565</v>
       </c>
       <c r="T31">
         <v>0.8636357006862946</v>
       </c>
       <c r="U31">
-        <v>0.08769948756095546</v>
+        <v>0.08509948756095545</v>
       </c>
       <c r="V31">
         <v>0.27</v>
       </c>
       <c r="W31">
-        <v>0.06402062591949748</v>
+        <v>0.06212262591949748</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.023832156189305</v>
+        <v>5.177322664539735</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +4006,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1023062075524436</v>
+        <v>0.1017317012238731</v>
       </c>
       <c r="C32">
-        <v>2476.484473377823</v>
+        <v>2508.588799078851</v>
       </c>
       <c r="D32">
-        <v>3150.324473377823</v>
+        <v>3182.428799078851</v>
       </c>
       <c r="E32">
         <v>-748.16</v>
@@ -3911,37 +4039,37 @@
         <v>422</v>
       </c>
       <c r="M32">
-        <v>86.89616025489711</v>
+        <v>84.3199762548971</v>
       </c>
       <c r="N32">
-        <v>335.1038397451029</v>
+        <v>337.6800237451029</v>
       </c>
       <c r="O32">
-        <v>90.4780367311778</v>
+        <v>91.17360641117779</v>
       </c>
       <c r="P32">
-        <v>244.6258030139251</v>
+        <v>246.5064173339251</v>
       </c>
       <c r="Q32">
-        <v>497.6258030139251</v>
+        <v>499.5064173339251</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1187143139665634</v>
+        <v>0.1187070192114627</v>
       </c>
       <c r="T32">
         <v>0.8734073038032214</v>
       </c>
       <c r="U32">
-        <v>0.08769948756095546</v>
+        <v>0.08509948756095545</v>
       </c>
       <c r="V32">
         <v>0.27</v>
       </c>
       <c r="W32">
-        <v>0.06402062591949748</v>
+        <v>0.06212262591949748</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.856371084316327</v>
+        <v>5.00474524238841</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4088,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1023384594553853</v>
+        <v>0.1017449881290859</v>
       </c>
       <c r="C33">
-        <v>2441.659396483108</v>
+        <v>2474.80497391535</v>
       </c>
       <c r="D33">
-        <v>3148.527396483108</v>
+        <v>3181.67297391535</v>
       </c>
       <c r="E33">
         <v>-715.1319999999999</v>
@@ -3993,37 +4121,37 @@
         <v>422</v>
       </c>
       <c r="M33">
-        <v>89.79269893006034</v>
+        <v>87.13064213006034</v>
       </c>
       <c r="N33">
-        <v>332.2073010699397</v>
+        <v>334.8693578699397</v>
       </c>
       <c r="O33">
-        <v>89.69597128888371</v>
+        <v>90.41472662488371</v>
       </c>
       <c r="P33">
-        <v>242.511329781056</v>
+        <v>244.454631245056</v>
       </c>
       <c r="Q33">
-        <v>495.511329781056</v>
+        <v>497.454631245056</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1195537180004943</v>
+        <v>0.1195463392667271</v>
       </c>
       <c r="T33">
         <v>0.8834621417931025</v>
       </c>
       <c r="U33">
-        <v>0.08769948756095546</v>
+        <v>0.08509948756095545</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.06402062591949748</v>
+        <v>0.06212262591949748</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.699713952564188</v>
+        <v>4.843301847472656</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4170,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1023707113583269</v>
+        <v>0.1017582750342987</v>
       </c>
       <c r="C34">
-        <v>2406.836368675215</v>
+        <v>2441.02150768276</v>
       </c>
       <c r="D34">
-        <v>3146.732368675215</v>
+        <v>3180.917507682761</v>
       </c>
       <c r="E34">
         <v>-682.1039999999998</v>
@@ -4075,37 +4203,37 @@
         <v>422</v>
       </c>
       <c r="M34">
-        <v>92.6892376052236</v>
+        <v>89.94130800522359</v>
       </c>
       <c r="N34">
-        <v>329.3107623947764</v>
+        <v>332.0586919947764</v>
       </c>
       <c r="O34">
-        <v>88.91390584658964</v>
+        <v>89.65584683858962</v>
       </c>
       <c r="P34">
-        <v>240.3968565481868</v>
+        <v>242.4028451561867</v>
       </c>
       <c r="Q34">
-        <v>493.3968565481867</v>
+        <v>495.4028451561867</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1204178103883643</v>
+        <v>0.1204103452059698</v>
       </c>
       <c r="T34">
         <v>0.8938127103120977</v>
       </c>
       <c r="U34">
-        <v>0.08769948756095546</v>
+        <v>0.08509948756095545</v>
       </c>
       <c r="V34">
         <v>0.27</v>
       </c>
       <c r="W34">
-        <v>0.06402062591949748</v>
+        <v>0.06212262591949748</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.552847891546556</v>
+        <v>4.691948664739133</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4252,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1030293032612686</v>
+        <v>0.1017715619395114</v>
       </c>
       <c r="C35">
-        <v>2337.595933076047</v>
+        <v>2407.238400125465</v>
       </c>
       <c r="D35">
-        <v>3110.519933076047</v>
+        <v>3180.162400125465</v>
       </c>
       <c r="E35">
         <v>-649.0759999999998</v>
@@ -4157,45 +4285,45 @@
         <v>422</v>
       </c>
       <c r="M35">
-        <v>98.41957868038683</v>
+        <v>92.75197388038683</v>
       </c>
       <c r="N35">
-        <v>323.5804213196132</v>
+        <v>329.2480261196132</v>
       </c>
       <c r="O35">
-        <v>87.36671375629555</v>
+        <v>88.89696705229557</v>
       </c>
       <c r="P35">
-        <v>236.2137075633176</v>
+        <v>240.3510590673176</v>
       </c>
       <c r="Q35">
-        <v>489.2137075633176</v>
+        <v>493.3510590673176</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1213076965788573</v>
+        <v>0.1213001423672795</v>
       </c>
       <c r="T35">
         <v>0.90447225102569</v>
       </c>
       <c r="U35">
-        <v>0.09029948756095546</v>
+        <v>0.08509948756095545</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.06591862591949749</v>
+        <v>0.06212262591949748</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.287764748215658</v>
+        <v>4.549768402171281</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4334,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1030805351642102</v>
+        <v>0.1024053488447241</v>
       </c>
       <c r="C36">
-        <v>2301.785873605887</v>
+        <v>2338.603424339867</v>
       </c>
       <c r="D36">
-        <v>3107.737873605887</v>
+        <v>3144.555424339867</v>
       </c>
       <c r="E36">
         <v>-616.0479999999998</v>
@@ -4239,37 +4367,37 @@
         <v>422</v>
       </c>
       <c r="M36">
-        <v>101.4019901555501</v>
+        <v>98.37001975555006</v>
       </c>
       <c r="N36">
-        <v>320.5980098444499</v>
+        <v>323.6299802444499</v>
       </c>
       <c r="O36">
-        <v>86.56146265800147</v>
+        <v>87.38009466600148</v>
       </c>
       <c r="P36">
-        <v>234.0365471864484</v>
+        <v>236.2498855784485</v>
       </c>
       <c r="Q36">
-        <v>487.0365471864484</v>
+        <v>489.2498855784485</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1222245490175471</v>
+        <v>0.1222169030789318</v>
       </c>
       <c r="T36">
         <v>0.9154548081245424</v>
       </c>
       <c r="U36">
-        <v>0.09029948756095546</v>
+        <v>0.08759948756095545</v>
       </c>
       <c r="V36">
         <v>0.27</v>
       </c>
       <c r="W36">
-        <v>0.06591862591949749</v>
+        <v>0.06394762591949747</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.161654020326962</v>
+        <v>4.289924928841856</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4416,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1031317670671519</v>
+        <v>0.1024368857499369</v>
       </c>
       <c r="C37">
-        <v>2265.980786255305</v>
+        <v>2303.824453306757</v>
       </c>
       <c r="D37">
-        <v>3104.960786255305</v>
+        <v>3142.804453306757</v>
       </c>
       <c r="E37">
         <v>-583.0199999999998</v>
@@ -4321,37 +4449,37 @@
         <v>422</v>
       </c>
       <c r="M37">
-        <v>104.3844016307133</v>
+        <v>101.2632556307133</v>
       </c>
       <c r="N37">
-        <v>317.6155983692867</v>
+        <v>320.7367443692867</v>
       </c>
       <c r="O37">
-        <v>85.75621155970741</v>
+        <v>86.59892097970742</v>
       </c>
       <c r="P37">
-        <v>231.8593868095792</v>
+        <v>234.1378233895793</v>
       </c>
       <c r="Q37">
-        <v>484.8593868095792</v>
+        <v>487.1378233895793</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1231696123005042</v>
+        <v>0.1231618718124812</v>
       </c>
       <c r="T37">
         <v>0.9267752900572057</v>
       </c>
       <c r="U37">
-        <v>0.09029948756095546</v>
+        <v>0.08759948756095545</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.06591862591949749</v>
+        <v>0.06394762591949747</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.042749619746191</v>
+        <v>4.16735564516066</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4498,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1038925589700935</v>
+        <v>0.1024684226551496</v>
       </c>
       <c r="C38">
-        <v>2192.289591742727</v>
+        <v>2269.047431161756</v>
       </c>
       <c r="D38">
-        <v>3064.297591742727</v>
+        <v>3141.055431161757</v>
       </c>
       <c r="E38">
         <v>-549.992</v>
@@ -4403,45 +4531,45 @@
         <v>422</v>
       </c>
       <c r="M38">
-        <v>110.5771347058765</v>
+        <v>104.1564915058765</v>
       </c>
       <c r="N38">
-        <v>311.4228652941235</v>
+        <v>317.8435084941235</v>
       </c>
       <c r="O38">
-        <v>84.08417362941334</v>
+        <v>85.81774729341333</v>
       </c>
       <c r="P38">
-        <v>227.3386916647102</v>
+        <v>232.0257612007101</v>
       </c>
       <c r="Q38">
-        <v>480.3386916647102</v>
+        <v>485.0257612007101</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1241442088110538</v>
+        <v>0.124136370818954</v>
       </c>
       <c r="T38">
         <v>0.9384495370502648</v>
       </c>
       <c r="U38">
-        <v>0.09299948756095545</v>
+        <v>0.08759948756095545</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.06788962591949747</v>
+        <v>0.06394762591949747</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.816340522138463</v>
+        <v>4.051595766128418</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4580,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1039635008730352</v>
+        <v>0.1034453095603624</v>
       </c>
       <c r="C39">
-        <v>2155.524074243354</v>
+        <v>2182.789498966904</v>
       </c>
       <c r="D39">
-        <v>3060.560074243354</v>
+        <v>3087.825498966904</v>
       </c>
       <c r="E39">
         <v>-516.9639999999999</v>
@@ -4485,37 +4613,37 @@
         <v>422</v>
       </c>
       <c r="M39">
-        <v>113.6487217810398</v>
+        <v>111.3268533810398</v>
       </c>
       <c r="N39">
-        <v>308.3512782189603</v>
+        <v>310.6731466189602</v>
       </c>
       <c r="O39">
-        <v>83.25484511911928</v>
+        <v>83.88174958711927</v>
       </c>
       <c r="P39">
-        <v>225.096433099841</v>
+        <v>226.791397031841</v>
       </c>
       <c r="Q39">
-        <v>478.096433099841</v>
+        <v>479.791397031841</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1251497448933668</v>
+        <v>0.1251418063018228</v>
       </c>
       <c r="T39">
         <v>0.9504943950589765</v>
       </c>
       <c r="U39">
-        <v>0.09299948756095545</v>
+        <v>0.09109948756095546</v>
       </c>
       <c r="V39">
         <v>0.27</v>
       </c>
       <c r="W39">
-        <v>0.06788962591949747</v>
+        <v>0.06650262591949749</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.713196183702288</v>
+        <v>3.790639788907133</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4662,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1040344427759768</v>
+        <v>0.1035023964655752</v>
       </c>
       <c r="C40">
-        <v>2118.767662922079</v>
+        <v>2146.706610221023</v>
       </c>
       <c r="D40">
-        <v>3056.831662922079</v>
+        <v>3084.770610221023</v>
       </c>
       <c r="E40">
         <v>-483.9359999999999</v>
@@ -4567,37 +4695,37 @@
         <v>422</v>
       </c>
       <c r="M40">
-        <v>116.720308856203</v>
+        <v>114.335687256203</v>
       </c>
       <c r="N40">
-        <v>305.279691143797</v>
+        <v>307.664312743797</v>
       </c>
       <c r="O40">
-        <v>82.42551660882519</v>
+        <v>83.0693644408252</v>
       </c>
       <c r="P40">
-        <v>222.8541745349718</v>
+        <v>224.5949483029718</v>
       </c>
       <c r="Q40">
-        <v>475.8541745349718</v>
+        <v>477.5949483029718</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1261877176234964</v>
+        <v>0.1261796751873647</v>
       </c>
       <c r="T40">
         <v>0.9629277968744209</v>
       </c>
       <c r="U40">
-        <v>0.09299948756095545</v>
+        <v>0.09109948756095546</v>
       </c>
       <c r="V40">
         <v>0.27</v>
       </c>
       <c r="W40">
-        <v>0.06788962591949747</v>
+        <v>0.06650262591949749</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.615480494657491</v>
+        <v>3.690886110251683</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4744,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1041053846789185</v>
+        <v>0.1035594833707879</v>
       </c>
       <c r="C41">
-        <v>2082.020324539626</v>
+        <v>2110.629760107558</v>
       </c>
       <c r="D41">
-        <v>3053.112324539627</v>
+        <v>3081.721760107559</v>
       </c>
       <c r="E41">
         <v>-450.9079999999999</v>
@@ -4649,37 +4777,37 @@
         <v>422</v>
       </c>
       <c r="M41">
-        <v>119.7918959313662</v>
+        <v>117.3445211313662</v>
       </c>
       <c r="N41">
-        <v>302.2081040686338</v>
+        <v>304.6554788686337</v>
       </c>
       <c r="O41">
-        <v>81.59618809853112</v>
+        <v>82.25697929453112</v>
       </c>
       <c r="P41">
-        <v>220.6119159701026</v>
+        <v>222.3984995741026</v>
       </c>
       <c r="Q41">
-        <v>473.6119159701026</v>
+        <v>475.3984995741026</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1272597222464172</v>
+        <v>0.1272515725609572</v>
       </c>
       <c r="T41">
         <v>0.9757688512084045</v>
       </c>
       <c r="U41">
-        <v>0.09299948756095545</v>
+        <v>0.09109948756095546</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.06788962591949747</v>
+        <v>0.06650262591949749</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.522775866589351</v>
+        <v>3.596248004860614</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4826,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1055487265818601</v>
+        <v>0.1036165702760007</v>
       </c>
       <c r="C42">
-        <v>1975.238703257705</v>
+        <v>2074.558930739237</v>
       </c>
       <c r="D42">
-        <v>2979.358703257705</v>
+        <v>3078.678930739237</v>
       </c>
       <c r="E42">
         <v>-417.8799999999999</v>
@@ -4731,45 +4859,45 @@
         <v>422</v>
       </c>
       <c r="M42">
-        <v>129.0727470065295</v>
+        <v>120.3533550065295</v>
       </c>
       <c r="N42">
-        <v>292.9272529934705</v>
+        <v>301.6466449934705</v>
       </c>
       <c r="O42">
-        <v>79.09035830823704</v>
+        <v>81.44459414823706</v>
       </c>
       <c r="P42">
-        <v>213.8368946852335</v>
+        <v>220.2020508452335</v>
       </c>
       <c r="Q42">
-        <v>466.8368946852335</v>
+        <v>473.2020508452335</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1283674603567685</v>
+        <v>0.1283591998470028</v>
       </c>
       <c r="T42">
         <v>0.9890379406868542</v>
       </c>
       <c r="U42">
-        <v>0.09769948756095545</v>
+        <v>0.09109948756095546</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.07132062591949748</v>
+        <v>0.06650262591949749</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.269474074016973</v>
+        <v>3.506341804739099</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4908,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1056539784848018</v>
+        <v>0.1045116971812134</v>
       </c>
       <c r="C43">
-        <v>1936.971566595414</v>
+        <v>1994.59295286218</v>
       </c>
       <c r="D43">
-        <v>2974.119566595414</v>
+        <v>3031.740952862181</v>
       </c>
       <c r="E43">
         <v>-384.8519999999999</v>
@@ -4813,37 +4941,37 @@
         <v>422</v>
       </c>
       <c r="M43">
-        <v>132.2995656816927</v>
+        <v>127.1538032816927</v>
       </c>
       <c r="N43">
-        <v>289.7004343183073</v>
+        <v>294.8461967183073</v>
       </c>
       <c r="O43">
-        <v>78.21911726594298</v>
+        <v>79.60847311394298</v>
       </c>
       <c r="P43">
-        <v>211.4813170523643</v>
+        <v>215.2377236043643</v>
       </c>
       <c r="Q43">
-        <v>464.4813170523643</v>
+        <v>468.2377236043643</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1295127489115387</v>
+        <v>0.1295043738207109</v>
       </c>
       <c r="T43">
         <v>1.002756829808641</v>
       </c>
       <c r="U43">
-        <v>0.09769948756095545</v>
+        <v>0.09389948756095545</v>
       </c>
       <c r="V43">
         <v>0.27</v>
       </c>
       <c r="W43">
-        <v>0.07132062591949748</v>
+        <v>0.06854662591949748</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.189730803918998</v>
+        <v>3.318815396068916</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4990,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1057592303877434</v>
+        <v>0.1045892240864262</v>
       </c>
       <c r="C44">
-        <v>1898.722823401483</v>
+        <v>1957.56691585566</v>
       </c>
       <c r="D44">
-        <v>2968.898823401483</v>
+        <v>3027.74291585566</v>
       </c>
       <c r="E44">
         <v>-351.8240000000001</v>
@@ -4895,37 +5023,37 @@
         <v>422</v>
       </c>
       <c r="M44">
-        <v>135.5263843568559</v>
+        <v>130.2551155568559</v>
       </c>
       <c r="N44">
-        <v>286.4736156431441</v>
+        <v>291.7448844431441</v>
       </c>
       <c r="O44">
-        <v>77.3478762236489</v>
+        <v>78.7711187996489</v>
       </c>
       <c r="P44">
-        <v>209.1257394194952</v>
+        <v>212.9737656434952</v>
       </c>
       <c r="Q44">
-        <v>462.1257394194952</v>
+        <v>465.9737656434952</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1306975301750939</v>
+        <v>0.1306890365521331</v>
       </c>
       <c r="T44">
         <v>1.016948784072559</v>
       </c>
       <c r="U44">
-        <v>0.09769948756095545</v>
+        <v>0.09389948756095545</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.07132062591949748</v>
+        <v>0.06854662591949748</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.113784832397117</v>
+        <v>3.239795981876799</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5072,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1058644822906851</v>
+        <v>0.1046667509916389</v>
       </c>
       <c r="C45">
-        <v>1860.49237698245</v>
+        <v>1920.55140959632</v>
       </c>
       <c r="D45">
-        <v>2963.69637698245</v>
+        <v>3023.75540959632</v>
       </c>
       <c r="E45">
         <v>-318.796</v>
@@ -4977,37 +5105,37 @@
         <v>422</v>
       </c>
       <c r="M45">
-        <v>138.7532030320192</v>
+        <v>133.3564278320192</v>
       </c>
       <c r="N45">
-        <v>283.2467969679808</v>
+        <v>288.6435721679808</v>
       </c>
       <c r="O45">
-        <v>76.47663518135482</v>
+        <v>77.93376448535483</v>
       </c>
       <c r="P45">
-        <v>206.770161786626</v>
+        <v>210.709807682626</v>
       </c>
       <c r="Q45">
-        <v>459.770161786626</v>
+        <v>463.709807682626</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1319238827110547</v>
+        <v>0.1319152663969386</v>
       </c>
       <c r="T45">
         <v>1.031638701643982</v>
       </c>
       <c r="U45">
-        <v>0.09769948756095545</v>
+        <v>0.09389948756095545</v>
       </c>
       <c r="V45">
         <v>0.27</v>
       </c>
       <c r="W45">
-        <v>0.07132062591949748</v>
+        <v>0.06854662591949748</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.041371231643696</v>
+        <v>3.164451889275013</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5154,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1089568941936267</v>
+        <v>0.1047442778968517</v>
       </c>
       <c r="C46">
-        <v>1682.350053836864</v>
+        <v>1883.546392532229</v>
       </c>
       <c r="D46">
-        <v>2818.582053836864</v>
+        <v>3019.778392532229</v>
       </c>
       <c r="E46">
         <v>-285.7679999999998</v>
@@ -5059,45 +5187,45 @@
         <v>422</v>
       </c>
       <c r="M46">
-        <v>155.4950793071824</v>
+        <v>136.4577401071824</v>
       </c>
       <c r="N46">
-        <v>266.5049206928176</v>
+        <v>285.5422598928176</v>
       </c>
       <c r="O46">
-        <v>71.95632858706075</v>
+        <v>77.09641017106075</v>
       </c>
       <c r="P46">
-        <v>194.5485921057568</v>
+        <v>208.4458497217568</v>
       </c>
       <c r="Q46">
-        <v>447.5485921057568</v>
+        <v>461.4458497217568</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1331940335518711</v>
+        <v>0.1331852901647728</v>
       </c>
       <c r="T46">
         <v>1.046853259128671</v>
       </c>
       <c r="U46">
-        <v>0.1069994875609555</v>
+        <v>0.09389948756095545</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.07810962591949748</v>
+        <v>0.06854662591949748</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.713912246485523</v>
+        <v>3.092532528155126</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5236,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1091300360965684</v>
+        <v>0.1048218048020644</v>
       </c>
       <c r="C47">
-        <v>1641.616158017471</v>
+        <v>1846.551823329772</v>
       </c>
       <c r="D47">
-        <v>2810.876158017471</v>
+        <v>3015.811823329772</v>
       </c>
       <c r="E47">
         <v>-252.7399999999998</v>
@@ -5141,45 +5269,45 @@
         <v>422</v>
       </c>
       <c r="M47">
-        <v>159.0290583823457</v>
+        <v>139.5590523823457</v>
       </c>
       <c r="N47">
-        <v>262.9709416176543</v>
+        <v>282.4409476176543</v>
       </c>
       <c r="O47">
-        <v>71.00215423676667</v>
+        <v>76.25905585676668</v>
       </c>
       <c r="P47">
-        <v>191.9687873808876</v>
+        <v>206.1818917608877</v>
       </c>
       <c r="Q47">
-        <v>444.9687873808876</v>
+        <v>459.1818917608877</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.13451037169599</v>
+        <v>0.1345014966150737</v>
       </c>
       <c r="T47">
         <v>1.062621073249166</v>
       </c>
       <c r="U47">
-        <v>0.1069994875609555</v>
+        <v>0.09389948756095545</v>
       </c>
       <c r="V47">
         <v>0.27</v>
       </c>
       <c r="W47">
-        <v>0.07810962591949748</v>
+        <v>0.06854662591949748</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.653603085452511</v>
+        <v>3.023809583085012</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5318,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.10930317799951</v>
+        <v>0.1075185717072772</v>
       </c>
       <c r="C48">
-        <v>1600.924282566446</v>
+        <v>1681.749200351156</v>
       </c>
       <c r="D48">
-        <v>2803.212282566446</v>
+        <v>2884.037200351156</v>
       </c>
       <c r="E48">
         <v>-219.7119999999998</v>
@@ -5223,37 +5351,37 @@
         <v>422</v>
       </c>
       <c r="M48">
-        <v>162.5630374575089</v>
+        <v>154.5108110575089</v>
       </c>
       <c r="N48">
-        <v>259.4369625424911</v>
+        <v>267.4891889424911</v>
       </c>
       <c r="O48">
-        <v>70.04797988647259</v>
+        <v>72.22208101447259</v>
       </c>
       <c r="P48">
-        <v>189.3889826560185</v>
+        <v>195.2671079280185</v>
       </c>
       <c r="Q48">
-        <v>442.3889826560185</v>
+        <v>448.2671079280185</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1358754631047059</v>
+        <v>0.1358664514524228</v>
       </c>
       <c r="T48">
         <v>1.078972880485235</v>
       </c>
       <c r="U48">
-        <v>0.1069994875609555</v>
+        <v>0.1016994875609555</v>
       </c>
       <c r="V48">
         <v>0.27</v>
       </c>
       <c r="W48">
-        <v>0.07810962591949748</v>
+        <v>0.07424062591949748</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.595916061855717</v>
+        <v>2.731200471421587</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5400,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1094763199024517</v>
+        <v>0.1076530386124899</v>
       </c>
       <c r="C49">
-        <v>1560.274084711789</v>
+        <v>1642.45137811527</v>
       </c>
       <c r="D49">
-        <v>2795.590084711789</v>
+        <v>2877.76737811527</v>
       </c>
       <c r="E49">
         <v>-186.6839999999997</v>
@@ -5305,37 +5433,37 @@
         <v>422</v>
       </c>
       <c r="M49">
-        <v>166.0970165326721</v>
+        <v>157.8697417326721</v>
       </c>
       <c r="N49">
-        <v>255.9029834673279</v>
+        <v>264.1302582673279</v>
       </c>
       <c r="O49">
-        <v>69.09380553617852</v>
+        <v>71.31516973217853</v>
       </c>
       <c r="P49">
-        <v>186.8091779311493</v>
+        <v>192.8150885351493</v>
       </c>
       <c r="Q49">
-        <v>439.8091779311493</v>
+        <v>445.8150885351494</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1372920673967696</v>
+        <v>0.1372829140194832</v>
       </c>
       <c r="T49">
         <v>1.095941737050968</v>
       </c>
       <c r="U49">
-        <v>0.1069994875609555</v>
+        <v>0.1016994875609555</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.07810962591949748</v>
+        <v>0.07424062591949748</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.540683805220489</v>
+        <v>2.673089823093468</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5482,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1112963418053933</v>
+        <v>0.1077875055177027</v>
       </c>
       <c r="C50">
-        <v>1449.561819521226</v>
+        <v>1603.180757606096</v>
       </c>
       <c r="D50">
-        <v>2717.905819521226</v>
+        <v>2871.524757606097</v>
       </c>
       <c r="E50">
         <v>-153.6559999999999</v>
@@ -5387,45 +5515,45 @@
         <v>422</v>
       </c>
       <c r="M50">
-        <v>177.0821124078354</v>
+        <v>161.2286724078354</v>
       </c>
       <c r="N50">
-        <v>244.9178875921646</v>
+        <v>260.7713275921647</v>
       </c>
       <c r="O50">
-        <v>66.12782964988445</v>
+        <v>70.40825844988446</v>
       </c>
       <c r="P50">
-        <v>178.7900579422802</v>
+        <v>190.3630691422802</v>
       </c>
       <c r="Q50">
-        <v>431.7900579422802</v>
+        <v>443.3630691422802</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1387631564692972</v>
+        <v>0.1387538559160459</v>
       </c>
       <c r="T50">
         <v>1.113563241946151</v>
       </c>
       <c r="U50">
-        <v>0.1116994875609555</v>
+        <v>0.1016994875609555</v>
       </c>
       <c r="V50">
         <v>0.27</v>
       </c>
       <c r="W50">
-        <v>0.08154062591949748</v>
+        <v>0.07424062591949748</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.383075253970867</v>
+        <v>2.61740045177902</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5564,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.111503793708335</v>
+        <v>0.1079219724229154</v>
       </c>
       <c r="C51">
-        <v>1407.952355614001</v>
+        <v>1563.937162184103</v>
       </c>
       <c r="D51">
-        <v>2709.324355614001</v>
+        <v>2865.309162184103</v>
       </c>
       <c r="E51">
         <v>-120.6279999999999</v>
@@ -5469,45 +5597,45 @@
         <v>422</v>
       </c>
       <c r="M51">
-        <v>180.7713230829986</v>
+        <v>164.5876030829986</v>
       </c>
       <c r="N51">
-        <v>241.2286769170014</v>
+        <v>257.4123969170014</v>
       </c>
       <c r="O51">
-        <v>65.13174276759037</v>
+        <v>69.50134716759038</v>
       </c>
       <c r="P51">
-        <v>176.096934149411</v>
+        <v>187.911049749411</v>
       </c>
       <c r="Q51">
-        <v>429.096934149411</v>
+        <v>440.911049749411</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1402919353093749</v>
+        <v>0.1402824818085522</v>
       </c>
       <c r="T51">
         <v>1.131875786248989</v>
       </c>
       <c r="U51">
-        <v>0.1116994875609555</v>
+        <v>0.1016994875609555</v>
       </c>
       <c r="V51">
         <v>0.27</v>
       </c>
       <c r="W51">
-        <v>0.08154062591949748</v>
+        <v>0.07424062591949748</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.334441065114319</v>
+        <v>2.563984116028428</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5646,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1117112456112766</v>
+        <v>0.1080564393281282</v>
       </c>
       <c r="C52">
-        <v>1366.396911047514</v>
+        <v>1524.720416735846</v>
       </c>
       <c r="D52">
-        <v>2700.796911047514</v>
+        <v>2859.120416735846</v>
       </c>
       <c r="E52">
         <v>-87.59999999999991</v>
@@ -5551,45 +5679,45 @@
         <v>422</v>
       </c>
       <c r="M52">
-        <v>184.4605337581619</v>
+        <v>167.9465337581618</v>
       </c>
       <c r="N52">
-        <v>237.5394662418381</v>
+        <v>254.0534662418382</v>
       </c>
       <c r="O52">
-        <v>64.1356558852963</v>
+        <v>68.59443588529631</v>
       </c>
       <c r="P52">
-        <v>173.4038103565418</v>
+        <v>185.4590303565419</v>
       </c>
       <c r="Q52">
-        <v>426.4038103565418</v>
+        <v>438.4590303565419</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1418818653030558</v>
+        <v>0.1418722527367588</v>
       </c>
       <c r="T52">
         <v>1.15092083232394</v>
       </c>
       <c r="U52">
-        <v>0.1116994875609555</v>
+        <v>0.1016994875609555</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.08154062591949748</v>
+        <v>0.07424062591949748</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.287752243812033</v>
+        <v>2.51270443370786</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5728,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1119186975142183</v>
+        <v>0.1096428762333409</v>
       </c>
       <c r="C53">
-        <v>1324.894977353715</v>
+        <v>1420.645897324989</v>
       </c>
       <c r="D53">
-        <v>2692.322977353715</v>
+        <v>2788.07389732499</v>
       </c>
       <c r="E53">
         <v>-54.57199999999989</v>
@@ -5633,37 +5761,37 @@
         <v>422</v>
       </c>
       <c r="M53">
-        <v>188.1497444333251</v>
+        <v>177.8747336333251</v>
       </c>
       <c r="N53">
-        <v>233.8502555666749</v>
+        <v>244.1252663666749</v>
       </c>
       <c r="O53">
-        <v>63.13956900300222</v>
+        <v>65.91382191900223</v>
       </c>
       <c r="P53">
-        <v>170.7106865636727</v>
+        <v>178.2114444476727</v>
       </c>
       <c r="Q53">
-        <v>423.7106865636727</v>
+        <v>431.2114444476726</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1435366903985195</v>
+        <v>0.14352691227428</v>
       </c>
       <c r="T53">
         <v>1.170743227218277</v>
       </c>
       <c r="U53">
-        <v>0.1116994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V53">
         <v>0.27</v>
       </c>
       <c r="W53">
-        <v>0.08154062591949748</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.242894356678463</v>
+        <v>2.372456117741377</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5810,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1121261494171599</v>
+        <v>0.1098058131385536</v>
       </c>
       <c r="C54">
-        <v>1283.446052426012</v>
+        <v>1380.520414923646</v>
       </c>
       <c r="D54">
-        <v>2683.902052426012</v>
+        <v>2780.976414923646</v>
       </c>
       <c r="E54">
         <v>-21.54399999999987</v>
@@ -5715,37 +5843,37 @@
         <v>422</v>
       </c>
       <c r="M54">
-        <v>191.8389551084883</v>
+        <v>181.3624735084883</v>
       </c>
       <c r="N54">
-        <v>230.1610448915117</v>
+        <v>240.6375264915117</v>
       </c>
       <c r="O54">
-        <v>62.14348212070816</v>
+        <v>64.97213215270816</v>
       </c>
       <c r="P54">
-        <v>168.0175627708035</v>
+        <v>175.6653943388035</v>
       </c>
       <c r="Q54">
-        <v>421.0175627708035</v>
+        <v>428.6653943388035</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1452604665396276</v>
+        <v>0.1452505159591978</v>
       </c>
       <c r="T54">
         <v>1.191391555233212</v>
       </c>
       <c r="U54">
-        <v>0.1116994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V54">
         <v>0.27</v>
       </c>
       <c r="W54">
-        <v>0.08154062591949748</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.199761772896185</v>
+        <v>2.326831961630966</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5892,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1123336013201016</v>
+        <v>0.1099687500437664</v>
       </c>
       <c r="C55">
-        <v>1242.049640420083</v>
+        <v>1340.430976291784</v>
       </c>
       <c r="D55">
-        <v>2675.533640420083</v>
+        <v>2773.914976291784</v>
       </c>
       <c r="E55">
         <v>11.48400000000015</v>
@@ -5797,37 +5925,37 @@
         <v>422</v>
       </c>
       <c r="M55">
-        <v>195.5281657836516</v>
+        <v>184.8502133836515</v>
       </c>
       <c r="N55">
-        <v>226.4718342163484</v>
+        <v>237.1497866163485</v>
       </c>
       <c r="O55">
-        <v>61.14739523841408</v>
+        <v>64.03044238641408</v>
       </c>
       <c r="P55">
-        <v>165.3244389779343</v>
+        <v>173.1193442299344</v>
       </c>
       <c r="Q55">
-        <v>418.3244389779343</v>
+        <v>426.1193442299344</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.147057594856953</v>
+        <v>0.1470474644817718</v>
       </c>
       <c r="T55">
         <v>1.212918535504101</v>
       </c>
       <c r="U55">
-        <v>0.1116994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V55">
         <v>0.27</v>
       </c>
       <c r="W55">
-        <v>0.08154062591949748</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.158256833784936</v>
+        <v>2.282929471788872</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5974,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1125410532230432</v>
+        <v>0.1101316869489792</v>
       </c>
       <c r="C56">
-        <v>1200.705251656565</v>
+        <v>1300.377307558447</v>
       </c>
       <c r="D56">
-        <v>2667.217251656565</v>
+        <v>2766.889307558447</v>
       </c>
       <c r="E56">
         <v>44.51200000000017</v>
@@ -5879,37 +6007,37 @@
         <v>422</v>
       </c>
       <c r="M56">
-        <v>199.2173764588148</v>
+        <v>188.3379532588148</v>
       </c>
       <c r="N56">
-        <v>222.7826235411852</v>
+        <v>233.6620467411852</v>
       </c>
       <c r="O56">
-        <v>60.15130835612</v>
+        <v>63.08875262012001</v>
       </c>
       <c r="P56">
-        <v>162.6313151850652</v>
+        <v>170.5732941210652</v>
       </c>
       <c r="Q56">
-        <v>415.6313151850652</v>
+        <v>423.5732941210652</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1489328591880752</v>
+        <v>0.1489225412009794</v>
       </c>
       <c r="T56">
         <v>1.235381471438942</v>
       </c>
       <c r="U56">
-        <v>0.1116994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V56">
         <v>0.27</v>
       </c>
       <c r="W56">
-        <v>0.08154062591949748</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.118289114640771</v>
+        <v>2.240653000089079</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6056,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1127485051259849</v>
+        <v>0.1102946238541919</v>
       </c>
       <c r="C57">
-        <v>1159.412402525524</v>
+        <v>1260.359137620266</v>
       </c>
       <c r="D57">
-        <v>2658.952402525524</v>
+        <v>2759.899137620266</v>
       </c>
       <c r="E57">
         <v>77.54000000000019</v>
@@ -5961,37 +6089,37 @@
         <v>422</v>
       </c>
       <c r="M57">
-        <v>202.9065871339781</v>
+        <v>191.825693133978</v>
       </c>
       <c r="N57">
-        <v>219.0934128660219</v>
+        <v>230.174306866022</v>
       </c>
       <c r="O57">
-        <v>59.15522147382593</v>
+        <v>62.14706285382594</v>
       </c>
       <c r="P57">
-        <v>159.938191392196</v>
+        <v>168.027244012196</v>
       </c>
       <c r="Q57">
-        <v>412.938191392196</v>
+        <v>421.027244012196</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1508914686005806</v>
+        <v>0.1508809546632629</v>
       </c>
       <c r="T57">
         <v>1.258842760081998</v>
       </c>
       <c r="U57">
-        <v>0.1116994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V57">
         <v>0.27</v>
       </c>
       <c r="W57">
-        <v>0.08154062591949748</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.079774767101848</v>
+        <v>2.199913854632913</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6138,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1129559570289265</v>
+        <v>0.1104575607594046</v>
       </c>
       <c r="C58">
-        <v>1118.170615392723</v>
+        <v>1220.376198106595</v>
       </c>
       <c r="D58">
-        <v>2650.738615392723</v>
+        <v>2752.944198106596</v>
       </c>
       <c r="E58">
         <v>110.5680000000002</v>
@@ -6043,37 +6171,37 @@
         <v>422</v>
       </c>
       <c r="M58">
-        <v>206.5957978091413</v>
+        <v>195.3134330091413</v>
       </c>
       <c r="N58">
-        <v>215.4042021908587</v>
+        <v>226.6865669908587</v>
       </c>
       <c r="O58">
-        <v>58.15913459153185</v>
+        <v>61.20537308753186</v>
       </c>
       <c r="P58">
-        <v>157.2450675993269</v>
+        <v>165.4811939033269</v>
       </c>
       <c r="Q58">
-        <v>410.2450675993268</v>
+        <v>418.4811939033269</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1529391057136544</v>
+        <v>0.1529283869192865</v>
       </c>
       <c r="T58">
         <v>1.283370470936102</v>
       </c>
       <c r="U58">
-        <v>0.1116994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V58">
         <v>0.27</v>
       </c>
       <c r="W58">
-        <v>0.08154062591949748</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.042635931975029</v>
+        <v>2.160629678657326</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6220,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1131634089318682</v>
+        <v>0.1106204976646174</v>
       </c>
       <c r="C59">
-        <v>1076.979418507596</v>
+        <v>1180.428223345158</v>
       </c>
       <c r="D59">
-        <v>2642.575418507596</v>
+        <v>2746.024223345159</v>
       </c>
       <c r="E59">
         <v>143.5960000000002</v>
@@ -6125,37 +6253,37 @@
         <v>422</v>
       </c>
       <c r="M59">
-        <v>210.2850084843045</v>
+        <v>198.8011728843045</v>
       </c>
       <c r="N59">
-        <v>211.7149915156955</v>
+        <v>223.1988271156955</v>
       </c>
       <c r="O59">
-        <v>57.16304770923778</v>
+        <v>60.26368332123779</v>
       </c>
       <c r="P59">
-        <v>154.5519438064577</v>
+        <v>162.9351437944577</v>
       </c>
       <c r="Q59">
-        <v>407.5519438064576</v>
+        <v>415.9351437944577</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1550819817622201</v>
+        <v>0.1550710485825671</v>
       </c>
       <c r="T59">
         <v>1.309039005550862</v>
       </c>
       <c r="U59">
-        <v>0.1116994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V59">
         <v>0.27</v>
       </c>
       <c r="W59">
-        <v>0.08154062591949748</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.006800213870204</v>
+        <v>2.122723894821232</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6302,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1202722808348098</v>
+        <v>0.1107834345698301</v>
       </c>
       <c r="C60">
-        <v>791.7001119348549</v>
+        <v>1140.514950328229</v>
       </c>
       <c r="D60">
-        <v>2390.324111934855</v>
+        <v>2739.138950328229</v>
       </c>
       <c r="E60">
         <v>176.624</v>
@@ -6207,45 +6335,45 @@
         <v>422</v>
       </c>
       <c r="M60">
-        <v>245.1988903594678</v>
+        <v>202.2889127594677</v>
       </c>
       <c r="N60">
-        <v>176.8011096405322</v>
+        <v>219.7110872405323</v>
       </c>
       <c r="O60">
-        <v>47.73629960294371</v>
+        <v>59.32199355494372</v>
       </c>
       <c r="P60">
-        <v>129.0648100375885</v>
+        <v>160.3890936855885</v>
       </c>
       <c r="Q60">
-        <v>382.0648100375885</v>
+        <v>413.3890936855885</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.157326899527384</v>
+        <v>0.1573157417536229</v>
       </c>
       <c r="T60">
         <v>1.335929851337752</v>
       </c>
       <c r="U60">
-        <v>0.1279994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V60">
         <v>0.27</v>
       </c>
       <c r="W60">
-        <v>0.09343962591949749</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.721051834212371</v>
+        <v>2.086125206979487</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6384,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1205987227377515</v>
+        <v>0.1109463714750429</v>
       </c>
       <c r="C61">
-        <v>748.240089526088</v>
+        <v>1100.636118679298</v>
       </c>
       <c r="D61">
-        <v>2379.892089526088</v>
+        <v>2732.288118679298</v>
       </c>
       <c r="E61">
         <v>209.652</v>
@@ -6289,45 +6417,45 @@
         <v>422</v>
       </c>
       <c r="M61">
-        <v>249.426457434631</v>
+        <v>205.776652634631</v>
       </c>
       <c r="N61">
-        <v>172.573542565369</v>
+        <v>216.223347365369</v>
       </c>
       <c r="O61">
-        <v>46.59485649264963</v>
+        <v>58.38030378864964</v>
       </c>
       <c r="P61">
-        <v>125.9786860727194</v>
+        <v>157.8430435767194</v>
       </c>
       <c r="Q61">
-        <v>378.9786860727194</v>
+        <v>410.8430435767194</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1596813254762146</v>
+        <v>0.1596699321525351</v>
       </c>
       <c r="T61">
         <v>1.364132445699614</v>
       </c>
       <c r="U61">
-        <v>0.1279994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V61">
         <v>0.27</v>
       </c>
       <c r="W61">
-        <v>0.09343962591949749</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.691881464140975</v>
+        <v>2.050767152623902</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6466,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1209251646406931</v>
+        <v>0.1111093083802557</v>
       </c>
       <c r="C62">
-        <v>704.87072779708</v>
+        <v>1060.791470620264</v>
       </c>
       <c r="D62">
-        <v>2369.55072779708</v>
+        <v>2725.471470620264</v>
       </c>
       <c r="E62">
         <v>242.6800000000001</v>
@@ -6371,45 +6499,45 @@
         <v>422</v>
       </c>
       <c r="M62">
-        <v>253.6540245097943</v>
+        <v>209.2643925097942</v>
       </c>
       <c r="N62">
-        <v>168.3459754902057</v>
+        <v>212.7356074902058</v>
       </c>
       <c r="O62">
-        <v>45.45341338235556</v>
+        <v>57.43861402235557</v>
       </c>
       <c r="P62">
-        <v>122.8925621078502</v>
+        <v>155.2969934678502</v>
       </c>
       <c r="Q62">
-        <v>375.8925621078502</v>
+        <v>408.2969934678502</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1621534727224866</v>
+        <v>0.1621418320713929</v>
       </c>
       <c r="T62">
         <v>1.393745169779569</v>
       </c>
       <c r="U62">
-        <v>0.1279994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V62">
         <v>0.27</v>
       </c>
       <c r="W62">
-        <v>0.09343962591949749</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.663683439738625</v>
+        <v>2.016587700080171</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6548,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1212516065436348</v>
+        <v>0.1175955052854684</v>
       </c>
       <c r="C63">
-        <v>661.5908500156374</v>
+        <v>781.537128905793</v>
       </c>
       <c r="D63">
-        <v>2359.298850015638</v>
+        <v>2479.245128905793</v>
       </c>
       <c r="E63">
         <v>275.7080000000001</v>
@@ -6453,37 +6581,37 @@
         <v>422</v>
       </c>
       <c r="M63">
-        <v>257.8815915849575</v>
+        <v>241.3609859849575</v>
       </c>
       <c r="N63">
-        <v>164.1184084150425</v>
+        <v>180.6390140150425</v>
       </c>
       <c r="O63">
-        <v>44.31197027206148</v>
+        <v>48.77253378406149</v>
       </c>
       <c r="P63">
-        <v>119.806438142981</v>
+        <v>131.866480230981</v>
       </c>
       <c r="Q63">
-        <v>372.8064381429811</v>
+        <v>384.866480230981</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1647523967506188</v>
+        <v>0.1647404960886537</v>
       </c>
       <c r="T63">
         <v>1.424876495094394</v>
       </c>
       <c r="U63">
-        <v>0.1279994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V63">
         <v>0.27</v>
       </c>
       <c r="W63">
-        <v>0.09343962591949749</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.636409940726516</v>
+        <v>1.748418445830763</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6630,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1215780484465765</v>
+        <v>0.1178621021906812</v>
       </c>
       <c r="C64">
-        <v>618.3992997263974</v>
+        <v>739.3370528972257</v>
       </c>
       <c r="D64">
-        <v>2349.135299726398</v>
+        <v>2470.073052897226</v>
       </c>
       <c r="E64">
         <v>308.7360000000001</v>
@@ -6535,37 +6663,37 @@
         <v>422</v>
       </c>
       <c r="M64">
-        <v>262.1091586601207</v>
+        <v>245.3177234601207</v>
       </c>
       <c r="N64">
-        <v>159.8908413398793</v>
+        <v>176.6822765398793</v>
       </c>
       <c r="O64">
-        <v>43.17052716176741</v>
+        <v>47.70421466576742</v>
       </c>
       <c r="P64">
-        <v>116.7203141781119</v>
+        <v>128.9780618741119</v>
       </c>
       <c r="Q64">
-        <v>369.7203141781118</v>
+        <v>381.9780618741119</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1674881062539158</v>
+        <v>0.1674759318962966</v>
       </c>
       <c r="T64">
         <v>1.457646311215261</v>
       </c>
       <c r="U64">
-        <v>0.1279994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V64">
         <v>0.27</v>
       </c>
       <c r="W64">
-        <v>0.09343962591949749</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.610016232005121</v>
+        <v>1.720218148317364</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6712,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1219044903495181</v>
+        <v>0.1181286990958939</v>
       </c>
       <c r="C65">
-        <v>575.2949403159578</v>
+        <v>697.2045917388864</v>
       </c>
       <c r="D65">
-        <v>2339.058940315958</v>
+        <v>2460.968591738887</v>
       </c>
       <c r="E65">
         <v>341.7640000000001</v>
@@ -6617,37 +6745,37 @@
         <v>422</v>
       </c>
       <c r="M65">
-        <v>266.3367257352839</v>
+        <v>249.2744609352839</v>
       </c>
       <c r="N65">
-        <v>155.6632742647161</v>
+        <v>172.7255390647161</v>
       </c>
       <c r="O65">
-        <v>42.02908405147333</v>
+        <v>46.63589554747334</v>
       </c>
       <c r="P65">
-        <v>113.6341902132427</v>
+        <v>126.0896435172427</v>
       </c>
       <c r="Q65">
-        <v>366.6341902132427</v>
+        <v>379.0896435172427</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1703716919465802</v>
+        <v>0.1703592290989473</v>
       </c>
       <c r="T65">
         <v>1.492187468748067</v>
       </c>
       <c r="U65">
-        <v>0.1279994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V65">
         <v>0.27</v>
       </c>
       <c r="W65">
-        <v>0.09343962591949749</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.584460418798691</v>
+        <v>1.692913098344073</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6794,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1222309322524598</v>
+        <v>0.1183952960011067</v>
       </c>
       <c r="C66">
-        <v>532.2766545891359</v>
+        <v>655.1390005102012</v>
       </c>
       <c r="D66">
-        <v>2329.068654589136</v>
+        <v>2451.931000510202</v>
       </c>
       <c r="E66">
         <v>374.7920000000004</v>
@@ -6699,37 +6827,37 @@
         <v>422</v>
       </c>
       <c r="M66">
-        <v>270.5642928104472</v>
+        <v>253.2311984104472</v>
       </c>
       <c r="N66">
-        <v>151.4357071895528</v>
+        <v>168.7688015895528</v>
       </c>
       <c r="O66">
-        <v>40.88764094117925</v>
+        <v>45.56757642917925</v>
       </c>
       <c r="P66">
-        <v>110.5480662483735</v>
+        <v>123.2012251603735</v>
       </c>
       <c r="Q66">
-        <v>363.5480662483735</v>
+        <v>376.2012251603736</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1734154768443927</v>
+        <v>0.173402709479523</v>
       </c>
       <c r="T66">
         <v>1.528647579477141</v>
       </c>
       <c r="U66">
-        <v>0.1279994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V66">
         <v>0.27</v>
       </c>
       <c r="W66">
-        <v>0.09343962591949749</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.559703224754961</v>
+        <v>1.666461331182446</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6876,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1225573741554014</v>
+        <v>0.1186618929063194</v>
       </c>
       <c r="C67">
-        <v>489.3433443560566</v>
+        <v>613.1395451930625</v>
       </c>
       <c r="D67">
-        <v>2319.163344356057</v>
+        <v>2442.959545193063</v>
       </c>
       <c r="E67">
         <v>407.8200000000002</v>
@@ -6781,37 +6909,37 @@
         <v>422</v>
       </c>
       <c r="M67">
-        <v>274.7918598856104</v>
+        <v>257.1879358856104</v>
       </c>
       <c r="N67">
-        <v>147.2081401143896</v>
+        <v>164.8120641143896</v>
       </c>
       <c r="O67">
-        <v>39.74619783088518</v>
+        <v>44.49925731088518</v>
       </c>
       <c r="P67">
-        <v>107.4619422835044</v>
+        <v>120.3128068035044</v>
       </c>
       <c r="Q67">
-        <v>360.4619422835044</v>
+        <v>373.3128068035044</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1766331923077944</v>
+        <v>0.176620103024703</v>
       </c>
       <c r="T67">
         <v>1.567191125105019</v>
       </c>
       <c r="U67">
-        <v>0.1279994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V67">
         <v>0.27</v>
       </c>
       <c r="W67">
-        <v>0.09343962591949749</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.535707790527961</v>
+        <v>1.64082346454887</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6958,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1228838160583431</v>
+        <v>0.1189284898115322</v>
       </c>
       <c r="C68">
-        <v>446.4939300297196</v>
+        <v>571.2055024730921</v>
       </c>
       <c r="D68">
-        <v>2309.34193002972</v>
+        <v>2434.053502473093</v>
       </c>
       <c r="E68">
         <v>440.8480000000004</v>
@@ -6863,37 +6991,37 @@
         <v>422</v>
       </c>
       <c r="M68">
-        <v>279.0194269607737</v>
+        <v>261.1446733607737</v>
       </c>
       <c r="N68">
-        <v>142.9805730392263</v>
+        <v>160.8553266392263</v>
       </c>
       <c r="O68">
-        <v>38.6047547205911</v>
+        <v>43.4309381925911</v>
       </c>
       <c r="P68">
-        <v>104.3758183186352</v>
+        <v>117.4243884466352</v>
       </c>
       <c r="Q68">
-        <v>357.3758183186352</v>
+        <v>370.4243884466352</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1800401851513962</v>
+        <v>0.1800267550137171</v>
       </c>
       <c r="T68">
         <v>1.608001938122771</v>
       </c>
       <c r="U68">
-        <v>0.1279994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V68">
         <v>0.27</v>
       </c>
       <c r="W68">
-        <v>0.09343962591949749</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.512439490671477</v>
+        <v>1.615962502964796</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7040,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1558254929499179</v>
+        <v>0.1191950867167449</v>
       </c>
       <c r="C69">
-        <v>-277.9519736903978</v>
+        <v>529.3361595452479</v>
       </c>
       <c r="D69">
-        <v>1617.924026309602</v>
+        <v>2425.212159545248</v>
       </c>
       <c r="E69">
         <v>473.8760000000002</v>
@@ -6945,45 +7073,45 @@
         <v>422</v>
       </c>
       <c r="M69">
-        <v>427.9690844359369</v>
+        <v>265.1014108359369</v>
       </c>
       <c r="N69">
-        <v>-5.969084435936907</v>
+        <v>156.8985891640631</v>
       </c>
       <c r="O69">
-        <v>-1.611652797702965</v>
+        <v>42.36261907429704</v>
       </c>
       <c r="P69">
-        <v>-4.357431638233942</v>
+        <v>114.535970089766</v>
       </c>
       <c r="Q69">
-        <v>248.6425683617661</v>
+        <v>367.535970089766</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1840782969079054</v>
+        <v>0.1836398707596412</v>
       </c>
       <c r="T69">
-        <v>1.656372636684458</v>
+        <v>1.651286133747661</v>
       </c>
       <c r="U69">
-        <v>0.1933994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V69">
-        <v>0.2662341840653581</v>
+        <v>0.27</v>
       </c>
       <c r="W69">
-        <v>0.1419099327915061</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.9860525335754003</v>
+        <v>1.591843659636964</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7122,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1573014878255274</v>
+        <v>0.1194616836219577</v>
       </c>
       <c r="C70">
-        <v>-332.3971549184666</v>
+        <v>487.5308139236449</v>
       </c>
       <c r="D70">
-        <v>1596.506845081534</v>
+        <v>2416.434813923645</v>
       </c>
       <c r="E70">
         <v>506.9040000000005</v>
@@ -7027,45 +7155,45 @@
         <v>422</v>
       </c>
       <c r="M70">
-        <v>434.3566827111002</v>
+        <v>269.0581483111002</v>
       </c>
       <c r="N70">
-        <v>-12.35668271110018</v>
+        <v>152.9418516888998</v>
       </c>
       <c r="O70">
-        <v>-3.336304331997048</v>
+        <v>41.29429995600295</v>
       </c>
       <c r="P70">
-        <v>-9.020378379103128</v>
+        <v>111.6475517328969</v>
       </c>
       <c r="Q70">
-        <v>243.9796216208969</v>
+        <v>364.6475517328969</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1883994936862775</v>
+        <v>0.1874788062396855</v>
       </c>
       <c r="T70">
-        <v>1.708134281580847</v>
+        <v>1.697275591599106</v>
       </c>
       <c r="U70">
-        <v>0.1933994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V70">
-        <v>0.2623189754761616</v>
+        <v>0.27</v>
       </c>
       <c r="W70">
-        <v>0.142667132126351</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.9715517610228208</v>
+        <v>1.568434194054067</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7204,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.158777482701137</v>
+        <v>0.1197282805271704</v>
       </c>
       <c r="C71">
-        <v>-386.2827264086141</v>
+        <v>445.7887732554918</v>
       </c>
       <c r="D71">
-        <v>1575.649273591386</v>
+        <v>2407.720773255492</v>
       </c>
       <c r="E71">
         <v>539.9320000000002</v>
@@ -7109,45 +7237,45 @@
         <v>422</v>
       </c>
       <c r="M71">
-        <v>440.7442809862634</v>
+        <v>273.0148857862634</v>
       </c>
       <c r="N71">
-        <v>-18.74428098626339</v>
+        <v>148.9851142137366</v>
       </c>
       <c r="O71">
-        <v>-5.060955866291116</v>
+        <v>40.22598083770889</v>
       </c>
       <c r="P71">
-        <v>-13.68332511997227</v>
+        <v>108.7591333760277</v>
       </c>
       <c r="Q71">
-        <v>239.3166748800277</v>
+        <v>361.7591333760277</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1929994773535768</v>
+        <v>0.1915654149765069</v>
       </c>
       <c r="T71">
-        <v>1.763235387438294</v>
+        <v>1.746232111247418</v>
       </c>
       <c r="U71">
-        <v>0.1933994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V71">
-        <v>0.2585172511938985</v>
+        <v>0.27</v>
       </c>
       <c r="W71">
-        <v>0.1434023836543887</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.9574713007181423</v>
+        <v>1.545703263705457</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7286,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1602534775767465</v>
+        <v>0.1199948774323832</v>
       </c>
       <c r="C72">
-        <v>-439.6303383838761</v>
+        <v>404.1093551390409</v>
       </c>
       <c r="D72">
-        <v>1555.329661616124</v>
+        <v>2399.069355139041</v>
       </c>
       <c r="E72">
         <v>572.9600000000005</v>
@@ -7191,45 +7319,45 @@
         <v>422</v>
       </c>
       <c r="M72">
-        <v>447.1318792614267</v>
+        <v>276.9716232614267</v>
       </c>
       <c r="N72">
-        <v>-25.13187926142666</v>
+        <v>145.0283767385733</v>
       </c>
       <c r="O72">
-        <v>-6.785607400585199</v>
+        <v>39.1576617194148</v>
       </c>
       <c r="P72">
-        <v>-18.34627186084146</v>
+        <v>105.8707150191585</v>
       </c>
       <c r="Q72">
-        <v>234.6537281391585</v>
+        <v>358.8707150191585</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.197906126598696</v>
+        <v>0.1959244642957831</v>
       </c>
       <c r="T72">
-        <v>1.822009900352904</v>
+        <v>1.798452398872285</v>
       </c>
       <c r="U72">
-        <v>0.1933994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V72">
-        <v>0.2548241476054142</v>
+        <v>0.27</v>
       </c>
       <c r="W72">
-        <v>0.1441166279959111</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.9437931392793116</v>
+        <v>1.523621788509665</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7368,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1617294724523561</v>
+        <v>0.1202614743375959</v>
       </c>
       <c r="C73">
-        <v>-492.4605384790441</v>
+        <v>362.4918869454491</v>
       </c>
       <c r="D73">
-        <v>1535.527461520956</v>
+        <v>2390.479886945449</v>
       </c>
       <c r="E73">
         <v>605.9879999999998</v>
@@ -7273,45 +7401,45 @@
         <v>422</v>
       </c>
       <c r="M73">
-        <v>453.5194775365898</v>
+        <v>280.9283607365898</v>
       </c>
       <c r="N73">
-        <v>-31.51947753658976</v>
+        <v>141.0716392634102</v>
       </c>
       <c r="O73">
-        <v>-8.510258934879236</v>
+        <v>38.08934260112076</v>
       </c>
       <c r="P73">
-        <v>-23.00921860171053</v>
+        <v>102.9822966622894</v>
       </c>
       <c r="Q73">
-        <v>229.9907813982895</v>
+        <v>355.9822966622894</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2031511654469268</v>
+        <v>0.2005841377060438</v>
       </c>
       <c r="T73">
-        <v>1.884837827951279</v>
+        <v>1.854274085643693</v>
       </c>
       <c r="U73">
-        <v>0.1933994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V73">
-        <v>0.2512350751039295</v>
+        <v>0.27</v>
       </c>
       <c r="W73">
-        <v>0.1448107527785173</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.9305002781627019</v>
+        <v>1.50216232669967</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7450,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1632054673279656</v>
+        <v>0.1503821512428087</v>
       </c>
       <c r="C74">
-        <v>-544.7928410481195</v>
+        <v>-359.0175744458368</v>
       </c>
       <c r="D74">
-        <v>1516.223158951881</v>
+        <v>1701.998425554163</v>
       </c>
       <c r="E74">
         <v>639.0160000000001</v>
@@ -7355,37 +7483,37 @@
         <v>422</v>
       </c>
       <c r="M74">
-        <v>459.9070758117531</v>
+        <v>419.9564070117531</v>
       </c>
       <c r="N74">
-        <v>-37.90707581175309</v>
+        <v>2.043592988246871</v>
       </c>
       <c r="O74">
-        <v>-10.23491046917333</v>
+        <v>0.5517701068266553</v>
       </c>
       <c r="P74">
-        <v>-27.67216534257975</v>
+        <v>1.491822881420216</v>
       </c>
       <c r="Q74">
-        <v>225.3278346574203</v>
+        <v>254.4918228814202</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2087708499271742</v>
+        <v>0.2055766449313231</v>
       </c>
       <c r="T74">
-        <v>1.952153464663825</v>
+        <v>1.914083035755917</v>
       </c>
       <c r="U74">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V74">
-        <v>0.2477456990608193</v>
+        <v>0.27</v>
       </c>
       <c r="W74">
-        <v>0.1454855963171623</v>
+        <v>0.1289176259194975</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9175766631882197</v>
+        <v>1.004866202668006</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7532,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1646814622035752</v>
+        <v>0.151470551064261</v>
       </c>
       <c r="C75">
-        <v>-596.6457913087511</v>
+        <v>-409.5760478258683</v>
       </c>
       <c r="D75">
-        <v>1497.398208691249</v>
+        <v>1684.467952174132</v>
       </c>
       <c r="E75">
         <v>672.0439999999999</v>
@@ -7437,37 +7565,37 @@
         <v>422</v>
       </c>
       <c r="M75">
-        <v>466.2946740869162</v>
+        <v>425.7891348869163</v>
       </c>
       <c r="N75">
-        <v>-44.29467408691625</v>
+        <v>-3.789134886916315</v>
       </c>
       <c r="O75">
-        <v>-11.95956200346739</v>
+        <v>-1.023066419467405</v>
       </c>
       <c r="P75">
-        <v>-32.33511208344886</v>
+        <v>-2.76606846744891</v>
       </c>
       <c r="Q75">
-        <v>220.6648879165512</v>
+        <v>250.2339315325511</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2148068073318843</v>
+        <v>0.211299729038128</v>
       </c>
       <c r="T75">
-        <v>2.024455444836559</v>
+        <v>1.98264410865708</v>
       </c>
       <c r="U75">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V75">
-        <v>0.2443519223613561</v>
+        <v>0.2675972462995349</v>
       </c>
       <c r="W75">
-        <v>0.1461419509917348</v>
+        <v>0.1293419509917348</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9050071198568744</v>
+        <v>0.9911009122204993</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7614,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1661574570791848</v>
+        <v>0.1527785459398706</v>
       </c>
       <c r="C76">
-        <v>-648.0370247669089</v>
+        <v>-463.1995366709937</v>
       </c>
       <c r="D76">
-        <v>1479.034975233091</v>
+        <v>1663.872463329006</v>
       </c>
       <c r="E76">
         <v>705.0720000000001</v>
@@ -7519,37 +7647,37 @@
         <v>422</v>
       </c>
       <c r="M76">
-        <v>472.6822723620796</v>
+        <v>431.6218627620796</v>
       </c>
       <c r="N76">
-        <v>-50.68227236207957</v>
+        <v>-9.621862762079616</v>
       </c>
       <c r="O76">
-        <v>-13.68421353776148</v>
+        <v>-2.597902945761496</v>
       </c>
       <c r="P76">
-        <v>-36.99805882431809</v>
+        <v>-7.023959816318119</v>
       </c>
       <c r="Q76">
-        <v>216.0019411756819</v>
+        <v>245.9760401836819</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2213070691523415</v>
+        <v>0.2176651032319022</v>
       </c>
       <c r="T76">
-        <v>2.102319115791811</v>
+        <v>2.058899651297737</v>
       </c>
       <c r="U76">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V76">
-        <v>0.2410498693564729</v>
+        <v>0.263981067295487</v>
       </c>
       <c r="W76">
-        <v>0.1467805663507784</v>
+        <v>0.1299805663507784</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8927772939128624</v>
+        <v>0.977707656649952</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7696,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1676334519547943</v>
+        <v>0.1540865408154801</v>
       </c>
       <c r="C77">
-        <v>-698.9833223220121</v>
+        <v>-516.325479031261</v>
       </c>
       <c r="D77">
-        <v>1461.116677677988</v>
+        <v>1643.774520968739</v>
       </c>
       <c r="E77">
         <v>738.1000000000004</v>
@@ -7601,37 +7729,37 @@
         <v>422</v>
       </c>
       <c r="M77">
-        <v>479.0698706372428</v>
+        <v>437.4545906372429</v>
       </c>
       <c r="N77">
-        <v>-57.06987063724284</v>
+        <v>-15.45459063724286</v>
       </c>
       <c r="O77">
-        <v>-15.40886507205557</v>
+        <v>-4.172739472055572</v>
       </c>
       <c r="P77">
-        <v>-41.66100556518727</v>
+        <v>-11.28185116518729</v>
       </c>
       <c r="Q77">
-        <v>211.3389944348127</v>
+        <v>241.7181488348127</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2283273519184352</v>
+        <v>0.2245397073611783</v>
       </c>
       <c r="T77">
-        <v>2.186411880423484</v>
+        <v>2.141255637349647</v>
       </c>
       <c r="U77">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V77">
-        <v>0.2378358710983866</v>
+        <v>0.2604613197315472</v>
       </c>
       <c r="W77">
-        <v>0.147402151966914</v>
+        <v>0.1306021519669141</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8808735966606909</v>
+        <v>0.9646715545612858</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7778,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1691094468304039</v>
+        <v>0.1553945356910897</v>
       </c>
       <c r="C78">
-        <v>-749.5006614144702</v>
+        <v>-568.9716893418995</v>
       </c>
       <c r="D78">
-        <v>1443.62733858553</v>
+        <v>1624.156310658101</v>
       </c>
       <c r="E78">
         <v>771.1280000000002</v>
@@ -7683,37 +7811,37 @@
         <v>422</v>
       </c>
       <c r="M78">
-        <v>485.4574689124061</v>
+        <v>443.2873185124061</v>
       </c>
       <c r="N78">
-        <v>-63.45746891240606</v>
+        <v>-21.2873185124061</v>
       </c>
       <c r="O78">
-        <v>-17.13351660634964</v>
+        <v>-5.747575998349648</v>
       </c>
       <c r="P78">
-        <v>-46.32395230605642</v>
+        <v>-15.53974251405645</v>
       </c>
       <c r="Q78">
-        <v>206.6760476939436</v>
+        <v>237.4602574859435</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.23593265824837</v>
+        <v>0.2319871951678941</v>
       </c>
       <c r="T78">
-        <v>2.277512375441129</v>
+        <v>2.230474622239215</v>
       </c>
       <c r="U78">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V78">
-        <v>0.2347064517418288</v>
+        <v>0.2570341971035006</v>
       </c>
       <c r="W78">
-        <v>0.1480073800668356</v>
+        <v>0.1312073800668356</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.869283154599366</v>
+        <v>0.9519785077907427</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7860,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1705854417060134</v>
+        <v>0.1567025305666992</v>
       </c>
       <c r="C79">
-        <v>-799.6042635432996</v>
+        <v>-621.1551416176446</v>
       </c>
       <c r="D79">
-        <v>1426.551736456701</v>
+        <v>1605.000858382356</v>
       </c>
       <c r="E79">
         <v>804.1560000000004</v>
@@ -7765,37 +7893,37 @@
         <v>422</v>
       </c>
       <c r="M79">
-        <v>491.8450671875693</v>
+        <v>449.1200463875693</v>
       </c>
       <c r="N79">
-        <v>-69.84506718756933</v>
+        <v>-27.12004638756935</v>
       </c>
       <c r="O79">
-        <v>-18.85816814064372</v>
+        <v>-7.322412524643724</v>
       </c>
       <c r="P79">
-        <v>-50.98689904692561</v>
+        <v>-19.79763386292562</v>
       </c>
       <c r="Q79">
-        <v>202.0131009530744</v>
+        <v>233.2023661370744</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2441992955635165</v>
+        <v>0.2400822906099764</v>
       </c>
       <c r="T79">
-        <v>2.376534652634222</v>
+        <v>2.327451779727876</v>
       </c>
       <c r="U79">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V79">
-        <v>0.231658316004922</v>
+        <v>0.2536960906476109</v>
       </c>
       <c r="W79">
-        <v>0.1485968879563697</v>
+        <v>0.1317968879563697</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8579937629811923</v>
+        <v>0.939615150546707</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7942,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.172061436581623</v>
+        <v>0.1580105254423088</v>
       </c>
       <c r="C80">
-        <v>-849.3086384508572</v>
+        <v>-672.8920184350193</v>
       </c>
       <c r="D80">
-        <v>1409.875361549143</v>
+        <v>1586.291981564981</v>
       </c>
       <c r="E80">
         <v>837.1840000000002</v>
@@ -7847,37 +7975,37 @@
         <v>422</v>
       </c>
       <c r="M80">
-        <v>498.2326654627325</v>
+        <v>454.9527742627325</v>
       </c>
       <c r="N80">
-        <v>-76.23266546273248</v>
+        <v>-32.95277426273253</v>
       </c>
       <c r="O80">
-        <v>-20.58281967493777</v>
+        <v>-8.897249050937784</v>
       </c>
       <c r="P80">
-        <v>-55.64984578779471</v>
+        <v>-24.05552521179475</v>
       </c>
       <c r="Q80">
-        <v>197.3501542122053</v>
+        <v>228.9444747882052</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2532174453618581</v>
+        <v>0.2489133038195208</v>
       </c>
       <c r="T80">
-        <v>2.484558955026687</v>
+        <v>2.43324504244278</v>
       </c>
       <c r="U80">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V80">
-        <v>0.2286883375946025</v>
+        <v>0.2504435766649493</v>
       </c>
       <c r="W80">
-        <v>0.1491712802589925</v>
+        <v>0.1323712802589926</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8469938429429721</v>
+        <v>0.927568802462775</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8024,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1735374314572325</v>
+        <v>0.1593185203179183</v>
       </c>
       <c r="C81">
-        <v>-898.627625244274</v>
+        <v>-724.1977565282991</v>
       </c>
       <c r="D81">
-        <v>1393.584374755726</v>
+        <v>1568.014243471701</v>
       </c>
       <c r="E81">
         <v>870.2120000000004</v>
@@ -7929,37 +8057,37 @@
         <v>422</v>
       </c>
       <c r="M81">
-        <v>504.6202637378958</v>
+        <v>460.7855021378958</v>
       </c>
       <c r="N81">
-        <v>-82.62026373789581</v>
+        <v>-38.78550213789583</v>
       </c>
       <c r="O81">
-        <v>-22.30747120923187</v>
+        <v>-10.47208557723188</v>
       </c>
       <c r="P81">
-        <v>-60.31279252866394</v>
+        <v>-28.31341656066396</v>
       </c>
       <c r="Q81">
-        <v>192.6872074713361</v>
+        <v>224.686583439336</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2630944665695656</v>
+        <v>0.2585853659061647</v>
       </c>
       <c r="T81">
-        <v>2.602871286218434</v>
+        <v>2.549113853987675</v>
       </c>
       <c r="U81">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V81">
-        <v>0.2257935485111265</v>
+        <v>0.2472734048084309</v>
       </c>
       <c r="W81">
-        <v>0.1497311309843339</v>
+        <v>0.1329311309843339</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.836272401893061</v>
+        <v>0.9158274252164106</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8106,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1750134263328421</v>
+        <v>0.1606265151935279</v>
       </c>
       <c r="C82">
-        <v>-947.5744306985196</v>
+        <v>-775.0870892691482</v>
       </c>
       <c r="D82">
-        <v>1377.665569301481</v>
+        <v>1550.152910730852</v>
       </c>
       <c r="E82">
         <v>903.2400000000002</v>
@@ -8011,37 +8139,37 @@
         <v>422</v>
       </c>
       <c r="M82">
-        <v>511.007862013059</v>
+        <v>466.618230013059</v>
       </c>
       <c r="N82">
-        <v>-89.00786201305897</v>
+        <v>-44.61823001305902</v>
       </c>
       <c r="O82">
-        <v>-24.03212274352592</v>
+        <v>-12.04692210352594</v>
       </c>
       <c r="P82">
-        <v>-64.97573926953305</v>
+        <v>-32.57130790953308</v>
       </c>
       <c r="Q82">
-        <v>188.0242607304669</v>
+        <v>220.4286920904669</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.273959189898044</v>
+        <v>0.269224634201473</v>
       </c>
       <c r="T82">
-        <v>2.733014850529356</v>
+        <v>2.676569546687059</v>
       </c>
       <c r="U82">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V82">
-        <v>0.2229711291547374</v>
+        <v>0.2441824872483255</v>
       </c>
       <c r="W82">
-        <v>0.1502769854415416</v>
+        <v>0.1334769854415417</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8258189968693977</v>
+        <v>0.9043795824012055</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8188,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1764894212084516</v>
+        <v>0.1619345100691374</v>
       </c>
       <c r="C83">
-        <v>-996.1616649639259</v>
+        <v>-825.5740862756377</v>
       </c>
       <c r="D83">
-        <v>1362.106335036075</v>
+        <v>1532.693913724363</v>
       </c>
       <c r="E83">
         <v>936.2680000000005</v>
@@ -8093,37 +8221,37 @@
         <v>422</v>
       </c>
       <c r="M83">
-        <v>517.3954602882222</v>
+        <v>472.4509578882223</v>
       </c>
       <c r="N83">
-        <v>-95.39546028822224</v>
+        <v>-50.45095788822232</v>
       </c>
       <c r="O83">
-        <v>-25.75677427782001</v>
+        <v>-13.62175862982003</v>
       </c>
       <c r="P83">
-        <v>-69.63868601040224</v>
+        <v>-36.82919925840229</v>
       </c>
       <c r="Q83">
-        <v>183.3613139895978</v>
+        <v>216.1708007415977</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2859675683137305</v>
+        <v>0.2809838254752346</v>
       </c>
       <c r="T83">
-        <v>2.876857737399322</v>
+        <v>2.817441628091641</v>
       </c>
       <c r="U83">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V83">
-        <v>0.2202183991651727</v>
+        <v>0.2411678886403215</v>
       </c>
       <c r="W83">
-        <v>0.1508093620109171</v>
+        <v>0.1340093620109171</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8156237006117508</v>
+        <v>0.8932144023715609</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8270,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1779654160840612</v>
+        <v>0.163242504944747</v>
       </c>
       <c r="C84">
-        <v>-1044.401374881064</v>
+        <v>-875.6721903744267</v>
       </c>
       <c r="D84">
-        <v>1346.894625118936</v>
+        <v>1515.623809625574</v>
       </c>
       <c r="E84">
         <v>969.2960000000003</v>
@@ -8175,37 +8303,37 @@
         <v>422</v>
       </c>
       <c r="M84">
-        <v>523.7830585633855</v>
+        <v>478.2836857633855</v>
       </c>
       <c r="N84">
-        <v>-101.7830585633855</v>
+        <v>-56.28368576338551</v>
       </c>
       <c r="O84">
-        <v>-27.48142581211408</v>
+        <v>-15.19659515611409</v>
       </c>
       <c r="P84">
-        <v>-74.30163275127137</v>
+        <v>-41.08709060727142</v>
       </c>
       <c r="Q84">
-        <v>178.6983672487286</v>
+        <v>211.9129093927286</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2993102109978266</v>
+        <v>0.2940495935571921</v>
       </c>
       <c r="T84">
-        <v>3.036683167254839</v>
+        <v>2.97396616298562</v>
       </c>
       <c r="U84">
-        <v>0.1933994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V84">
-        <v>0.2175328089314511</v>
+        <v>0.2382268168276347</v>
       </c>
       <c r="W84">
-        <v>0.1513287537859176</v>
+        <v>0.1345287537859176</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8056770701164856</v>
+        <v>0.8823215438060542</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8352,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2248730163777888</v>
+        <v>0.1645504998203566</v>
       </c>
       <c r="C85">
-        <v>-1430.244086951138</v>
+        <v>-925.3942521201973</v>
       </c>
       <c r="D85">
-        <v>994.0799130488629</v>
+        <v>1498.929747879803</v>
       </c>
       <c r="E85">
         <v>1002.324000000001</v>
@@ -8257,45 +8385,45 @@
         <v>422</v>
       </c>
       <c r="M85">
-        <v>673.2677696385489</v>
+        <v>484.1164136385488</v>
       </c>
       <c r="N85">
-        <v>-251.2677696385489</v>
+        <v>-62.11641363854881</v>
       </c>
       <c r="O85">
-        <v>-67.8422978024082</v>
+        <v>-16.77143168240818</v>
       </c>
       <c r="P85">
-        <v>-183.4254718361407</v>
+        <v>-45.34498195614063</v>
       </c>
       <c r="Q85">
-        <v>69.57452816385933</v>
+        <v>207.6550180438594</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3266084905748636</v>
+        <v>0.3086525108252623</v>
       </c>
       <c r="T85">
-        <v>3.363676804948255</v>
+        <v>3.148905349043599</v>
       </c>
       <c r="U85">
-        <v>0.2455994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V85">
-        <v>0.1692343004346843</v>
+        <v>0.2353566142152535</v>
       </c>
       <c r="W85">
-        <v>0.2040356300964602</v>
+        <v>0.1350356300964602</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.6267937053136455</v>
+        <v>0.8716911637601981</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8434,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2268710112533983</v>
+        <v>0.1658584946959661</v>
       </c>
       <c r="C86">
-        <v>-1474.241079494281</v>
+        <v>-974.7525620586187</v>
       </c>
       <c r="D86">
-        <v>983.1109205057192</v>
+        <v>1482.599437941381</v>
       </c>
       <c r="E86">
         <v>1035.352</v>
@@ -8339,45 +8467,45 @@
         <v>422</v>
       </c>
       <c r="M86">
-        <v>681.3794295137119</v>
+        <v>489.9491415137119</v>
       </c>
       <c r="N86">
-        <v>-259.3794295137119</v>
+        <v>-67.94914151371194</v>
       </c>
       <c r="O86">
-        <v>-70.03244596870222</v>
+        <v>-18.34626820870222</v>
       </c>
       <c r="P86">
-        <v>-189.3469835450097</v>
+        <v>-49.60287330500971</v>
       </c>
       <c r="Q86">
-        <v>63.65301645499034</v>
+        <v>203.3971266949903</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3441590212357924</v>
+        <v>0.3250807927518411</v>
       </c>
       <c r="T86">
-        <v>3.573906605257519</v>
+        <v>3.345711933358822</v>
       </c>
       <c r="U86">
-        <v>0.2455994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V86">
-        <v>0.1672196063818905</v>
+        <v>0.23255474976031</v>
       </c>
       <c r="W86">
-        <v>0.2045304379234185</v>
+        <v>0.1355304379234185</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.6193318754884833</v>
+        <v>0.8613138880011482</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8516,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2288690061290079</v>
+        <v>0.1671664895715756</v>
       </c>
       <c r="C87">
-        <v>-1517.998643295714</v>
+        <v>-1023.75888090309</v>
       </c>
       <c r="D87">
-        <v>972.3813567042857</v>
+        <v>1466.62111909691</v>
       </c>
       <c r="E87">
         <v>1068.38</v>
@@ -8421,45 +8549,45 @@
         <v>422</v>
       </c>
       <c r="M87">
-        <v>689.4910893888753</v>
+        <v>495.7818693888752</v>
       </c>
       <c r="N87">
-        <v>-267.4910893888753</v>
+        <v>-73.78186938887518</v>
       </c>
       <c r="O87">
-        <v>-72.22259413499633</v>
+        <v>-19.9211047349963</v>
       </c>
       <c r="P87">
-        <v>-195.2684952538789</v>
+        <v>-53.86076465387888</v>
       </c>
       <c r="Q87">
-        <v>57.73150474612106</v>
+        <v>199.1392353461211</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3640496226515119</v>
+        <v>0.3436995122686305</v>
       </c>
       <c r="T87">
-        <v>3.812167045608021</v>
+        <v>3.568759395582744</v>
       </c>
       <c r="U87">
-        <v>0.2455994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V87">
-        <v>0.1652523168950447</v>
+        <v>0.2298188115278358</v>
       </c>
       <c r="W87">
-        <v>0.2050136032132719</v>
+        <v>0.1360136032132719</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.6120456181297951</v>
+        <v>0.8511807834364288</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8598,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2308670010046174</v>
+        <v>0.1684744844471852</v>
       </c>
       <c r="C88">
-        <v>-1561.524533018285</v>
+        <v>-1072.42446778095</v>
       </c>
       <c r="D88">
-        <v>961.8834669817148</v>
+        <v>1450.983532219049</v>
       </c>
       <c r="E88">
         <v>1101.408</v>
@@ -8503,45 +8631,45 @@
         <v>422</v>
       </c>
       <c r="M88">
-        <v>697.6027492640384</v>
+        <v>501.6145972640384</v>
       </c>
       <c r="N88">
-        <v>-275.6027492640384</v>
+        <v>-79.61459726403842</v>
       </c>
       <c r="O88">
-        <v>-74.41274230129036</v>
+        <v>-21.49594126129038</v>
       </c>
       <c r="P88">
-        <v>-201.190006962748</v>
+        <v>-58.11865600274805</v>
       </c>
       <c r="Q88">
-        <v>51.80999303725199</v>
+        <v>194.8813439972519</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3867817385551913</v>
+        <v>0.364978048859247</v>
       </c>
       <c r="T88">
-        <v>4.08446469172288</v>
+        <v>3.823670780981511</v>
       </c>
       <c r="U88">
-        <v>0.2455994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V88">
-        <v>0.1633307783264977</v>
+        <v>0.2271464997658842</v>
       </c>
       <c r="W88">
-        <v>0.2054855321010357</v>
+        <v>0.1364855321010356</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.6049288086166581</v>
+        <v>0.8412833324662378</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8680,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.232864995880227</v>
+        <v>0.1697824793227948</v>
       </c>
       <c r="C89">
-        <v>-1604.826172022311</v>
+        <v>-1120.760106691729</v>
       </c>
       <c r="D89">
-        <v>951.609827977689</v>
+        <v>1435.675893308271</v>
       </c>
       <c r="E89">
         <v>1134.436</v>
@@ -8585,45 +8713,45 @@
         <v>422</v>
       </c>
       <c r="M89">
-        <v>705.7144091392017</v>
+        <v>507.4473251392017</v>
       </c>
       <c r="N89">
-        <v>-283.7144091392017</v>
+        <v>-85.44732513920167</v>
       </c>
       <c r="O89">
-        <v>-76.60289046758447</v>
+        <v>-23.07077778758445</v>
       </c>
       <c r="P89">
-        <v>-207.1115186716173</v>
+        <v>-62.37654735161722</v>
       </c>
       <c r="Q89">
-        <v>45.88848132838274</v>
+        <v>190.6234526483828</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4130111030594369</v>
+        <v>0.3895302064638044</v>
       </c>
       <c r="T89">
-        <v>4.398654283393871</v>
+        <v>4.117799302595473</v>
       </c>
       <c r="U89">
-        <v>0.2455994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V89">
-        <v>0.161453413058377</v>
+        <v>0.2245356204582304</v>
       </c>
       <c r="W89">
-        <v>0.2059466120488508</v>
+        <v>0.1369466120488508</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5979756039199148</v>
+        <v>0.8316134091045568</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8762,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2348629907558366</v>
+        <v>0.1710904741984043</v>
       </c>
       <c r="C90">
-        <v>-1647.910669871404</v>
+        <v>-1168.776131308107</v>
       </c>
       <c r="D90">
-        <v>941.5533301285964</v>
+        <v>1420.687868691893</v>
       </c>
       <c r="E90">
         <v>1167.464</v>
@@ -8667,45 +8795,45 @@
         <v>422</v>
       </c>
       <c r="M90">
-        <v>713.826069014365</v>
+        <v>513.280053014365</v>
       </c>
       <c r="N90">
-        <v>-291.826069014365</v>
+        <v>-91.28005301436497</v>
       </c>
       <c r="O90">
-        <v>-78.79303863387855</v>
+        <v>-24.64561431387854</v>
       </c>
       <c r="P90">
-        <v>-213.0330303804864</v>
+        <v>-66.63443870048643</v>
       </c>
       <c r="Q90">
-        <v>39.96696961951358</v>
+        <v>186.3655612995136</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.44361202831439</v>
+        <v>0.4181743903357882</v>
       </c>
       <c r="T90">
-        <v>4.765208807010027</v>
+        <v>4.460949244478431</v>
       </c>
       <c r="U90">
-        <v>0.2455994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V90">
-        <v>0.1596187151827136</v>
+        <v>0.2219840793166596</v>
       </c>
       <c r="W90">
-        <v>0.2063972129069429</v>
+        <v>0.1373972129069429</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.591180426602643</v>
+        <v>0.8221632567283687</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8844,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2368609856314461</v>
+        <v>0.1723984690740139</v>
       </c>
       <c r="C91">
-        <v>-1690.784838739908</v>
+        <v>-1216.482448239438</v>
       </c>
       <c r="D91">
-        <v>931.7071612600922</v>
+        <v>1406.009551760563</v>
       </c>
       <c r="E91">
         <v>1200.492</v>
@@ -8749,45 +8877,45 @@
         <v>422</v>
       </c>
       <c r="M91">
-        <v>721.9377288895282</v>
+        <v>519.1127808895282</v>
       </c>
       <c r="N91">
-        <v>-299.9377288895282</v>
+        <v>-97.11278088952815</v>
       </c>
       <c r="O91">
-        <v>-80.98318680017262</v>
+        <v>-26.2204508401726</v>
       </c>
       <c r="P91">
-        <v>-218.9545420893556</v>
+        <v>-70.89233004935555</v>
       </c>
       <c r="Q91">
-        <v>34.04545791064442</v>
+        <v>182.1076699506444</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4797767581611527</v>
+        <v>0.4520266076390416</v>
       </c>
       <c r="T91">
-        <v>5.198409607647302</v>
+        <v>4.86649008488556</v>
       </c>
       <c r="U91">
-        <v>0.2455994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V91">
-        <v>0.1578252464727955</v>
+        <v>0.2194898761782701</v>
       </c>
       <c r="W91">
-        <v>0.2068376879030554</v>
+        <v>0.1378376879030554</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.5845379498992426</v>
+        <v>0.8129254673269264</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8926,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2388589805070557</v>
+        <v>0.1737064639496234</v>
       </c>
       <c r="C92">
-        <v>-1733.455208801519</v>
+        <v>-1263.888558867883</v>
       </c>
       <c r="D92">
-        <v>922.0647911984811</v>
+        <v>1391.631441132118</v>
       </c>
       <c r="E92">
         <v>1233.52</v>
@@ -8831,45 +8959,45 @@
         <v>422</v>
       </c>
       <c r="M92">
-        <v>730.0493887646915</v>
+        <v>524.9455087646915</v>
       </c>
       <c r="N92">
-        <v>-308.0493887646915</v>
+        <v>-102.9455087646915</v>
       </c>
       <c r="O92">
-        <v>-83.1733349664667</v>
+        <v>-27.7952873664667</v>
       </c>
       <c r="P92">
-        <v>-224.8760537982247</v>
+        <v>-75.15022139822476</v>
       </c>
       <c r="Q92">
-        <v>28.12394620177525</v>
+        <v>177.8497786017753</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.523174433977268</v>
+        <v>0.4926492684029458</v>
       </c>
       <c r="T92">
-        <v>5.718250568412033</v>
+        <v>5.353139093374117</v>
       </c>
       <c r="U92">
-        <v>0.2455994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V92">
-        <v>0.1560716326230978</v>
+        <v>0.2170510997762893</v>
       </c>
       <c r="W92">
-        <v>0.207268374565921</v>
+        <v>0.1382683745659209</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.578043083789251</v>
+        <v>0.8038929621344049</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +9008,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2408569753826652</v>
+        <v>0.226694798513168</v>
       </c>
       <c r="C93">
-        <v>-1775.928042672137</v>
+        <v>-1704.55808862966</v>
       </c>
       <c r="D93">
-        <v>912.6199573278631</v>
+        <v>983.9899113703398</v>
       </c>
       <c r="E93">
         <v>1266.548</v>
@@ -8913,37 +9041,37 @@
         <v>422</v>
       </c>
       <c r="M93">
-        <v>738.1610486398547</v>
+        <v>693.0778286398546</v>
       </c>
       <c r="N93">
-        <v>-316.1610486398547</v>
+        <v>-271.0778286398546</v>
       </c>
       <c r="O93">
-        <v>-85.36348313276078</v>
+        <v>-73.19101373276075</v>
       </c>
       <c r="P93">
-        <v>-230.7975655070939</v>
+        <v>-197.8868149070939</v>
       </c>
       <c r="Q93">
-        <v>22.20243449290609</v>
+        <v>55.11318509290615</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5762160377525199</v>
+        <v>0.5705251836469962</v>
       </c>
       <c r="T93">
-        <v>6.353611742680036</v>
+        <v>6.286072491285141</v>
       </c>
       <c r="U93">
-        <v>0.2455994875609555</v>
+        <v>0.2305994875609555</v>
       </c>
       <c r="V93">
-        <v>0.1543565597371297</v>
+        <v>0.1643971214944273</v>
       </c>
       <c r="W93">
-        <v>0.2076895955878444</v>
+        <v>0.1926895955878444</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5716909619893691</v>
+        <v>0.6088782277571378</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9090,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2428549702582748</v>
+        <v>0.2285427933887776</v>
       </c>
       <c r="C94">
-        <v>-1818.209348974081</v>
+        <v>-1747.536731717377</v>
       </c>
       <c r="D94">
-        <v>903.3666510259194</v>
+        <v>974.0392682826239</v>
       </c>
       <c r="E94">
         <v>1299.576</v>
@@ -8995,37 +9123,37 @@
         <v>422</v>
       </c>
       <c r="M94">
-        <v>746.2727085150179</v>
+        <v>700.694068515018</v>
       </c>
       <c r="N94">
-        <v>-324.2727085150179</v>
+        <v>-278.694068515018</v>
       </c>
       <c r="O94">
-        <v>-87.55363129905484</v>
+        <v>-75.24739849905487</v>
       </c>
       <c r="P94">
-        <v>-236.7190772159631</v>
+        <v>-203.4466700159631</v>
       </c>
       <c r="Q94">
-        <v>16.2809227840369</v>
+        <v>49.55332998403688</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.6425180424715852</v>
+        <v>0.636115831602871</v>
       </c>
       <c r="T94">
-        <v>7.147813210515044</v>
+        <v>7.071831552695787</v>
       </c>
       <c r="U94">
-        <v>0.2455994875609555</v>
+        <v>0.2305994875609555</v>
       </c>
       <c r="V94">
-        <v>0.1526787710443348</v>
+        <v>0.1626101962607921</v>
       </c>
       <c r="W94">
-        <v>0.2081016596310304</v>
+        <v>0.1931016596310304</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5654769297938325</v>
+        <v>0.602259986151082</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9172,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2448529651338843</v>
+        <v>0.2303907882643872</v>
       </c>
       <c r="C95">
-        <v>-1860.30489508339</v>
+        <v>-1790.316136938371</v>
       </c>
       <c r="D95">
-        <v>894.29910491661</v>
+        <v>964.2878630616298</v>
       </c>
       <c r="E95">
         <v>1332.604</v>
@@ -9077,37 +9205,37 @@
         <v>422</v>
       </c>
       <c r="M95">
-        <v>754.3843683901812</v>
+        <v>708.3103083901811</v>
       </c>
       <c r="N95">
-        <v>-332.3843683901812</v>
+        <v>-286.3103083901811</v>
       </c>
       <c r="O95">
-        <v>-89.74377946534892</v>
+        <v>-77.30378326534891</v>
       </c>
       <c r="P95">
-        <v>-242.6405889248323</v>
+        <v>-209.0065251248323</v>
       </c>
       <c r="Q95">
-        <v>10.35941107516774</v>
+        <v>43.99347487516775</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.7277634771103833</v>
+        <v>0.7204466646889957</v>
       </c>
       <c r="T95">
-        <v>8.168929383445766</v>
+        <v>8.082093203080902</v>
       </c>
       <c r="U95">
-        <v>0.2455994875609555</v>
+        <v>0.2305994875609555</v>
       </c>
       <c r="V95">
-        <v>0.1510370638288043</v>
+        <v>0.1608616995268051</v>
       </c>
       <c r="W95">
-        <v>0.2085048620818898</v>
+        <v>0.1935048620818898</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5593965326992751</v>
+        <v>0.5957840723215004</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9254,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2468509600094939</v>
+        <v>0.2322387831399967</v>
       </c>
       <c r="C96">
-        <v>-1902.220219117065</v>
+        <v>-1832.902228873632</v>
       </c>
       <c r="D96">
-        <v>885.4117808829354</v>
+        <v>954.7297711263686</v>
       </c>
       <c r="E96">
         <v>1365.632000000001</v>
@@ -9159,37 +9287,37 @@
         <v>422</v>
       </c>
       <c r="M96">
-        <v>762.4960282653444</v>
+        <v>715.9265482653444</v>
       </c>
       <c r="N96">
-        <v>-340.4960282653444</v>
+        <v>-293.9265482653444</v>
       </c>
       <c r="O96">
-        <v>-91.933927631643</v>
+        <v>-79.360168031643</v>
       </c>
       <c r="P96">
-        <v>-248.5621006337014</v>
+        <v>-214.5663802337014</v>
       </c>
       <c r="Q96">
-        <v>4.437899366298581</v>
+        <v>38.43361976629859</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.8414240566287805</v>
+        <v>0.832887775470495</v>
       </c>
       <c r="T96">
-        <v>9.530417614020061</v>
+        <v>9.42910873692772</v>
       </c>
       <c r="U96">
-        <v>0.2455994875609555</v>
+        <v>0.2305994875609555</v>
       </c>
       <c r="V96">
-        <v>0.1494302865540298</v>
+        <v>0.1591504048509881</v>
       </c>
       <c r="W96">
-        <v>0.208899485757199</v>
+        <v>0.193899485757199</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5534455057556658</v>
+        <v>0.5894459438925483</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9336,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2488489548851034</v>
+        <v>0.2340867780156063</v>
       </c>
       <c r="C97">
-        <v>-1943.960641212561</v>
+        <v>-1875.300699510116</v>
       </c>
       <c r="D97">
-        <v>876.6993587874397</v>
+        <v>945.3593004898843</v>
       </c>
       <c r="E97">
         <v>1398.66</v>
@@ -9241,37 +9369,37 @@
         <v>422</v>
       </c>
       <c r="M97">
-        <v>770.6076881405077</v>
+        <v>723.5427881405076</v>
       </c>
       <c r="N97">
-        <v>-348.6076881405077</v>
+        <v>-301.5427881405076</v>
       </c>
       <c r="O97">
-        <v>-94.12407579793708</v>
+        <v>-81.41655279793706</v>
       </c>
       <c r="P97">
-        <v>-254.4836123425706</v>
+        <v>-220.1262353425705</v>
       </c>
       <c r="Q97">
-        <v>-1.483612342570581</v>
+        <v>32.87376465742949</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.000548867954537</v>
+        <v>0.9903053305645944</v>
       </c>
       <c r="T97">
-        <v>11.43650113682408</v>
+        <v>11.31493048431327</v>
       </c>
       <c r="U97">
-        <v>0.2455994875609555</v>
+        <v>0.2305994875609555</v>
       </c>
       <c r="V97">
-        <v>0.1478573361692505</v>
+        <v>0.157475137431504</v>
       </c>
       <c r="W97">
-        <v>0.2092858015656596</v>
+        <v>0.1942858015656596</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5476197635898167</v>
+        <v>0.5832412497463111</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9418,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.250846949760713</v>
+        <v>0.2359347728912158</v>
       </c>
       <c r="C98">
-        <v>-1985.531274147855</v>
+        <v>-1917.517019544109</v>
       </c>
       <c r="D98">
-        <v>868.1567258521453</v>
+        <v>936.1709804558909</v>
       </c>
       <c r="E98">
         <v>1431.688</v>
@@ -9323,37 +9451,37 @@
         <v>422</v>
       </c>
       <c r="M98">
-        <v>778.7193480156708</v>
+        <v>731.1590280156707</v>
       </c>
       <c r="N98">
-        <v>-356.7193480156708</v>
+        <v>-309.1590280156707</v>
       </c>
       <c r="O98">
-        <v>-96.31422396423112</v>
+        <v>-83.4729375642311</v>
       </c>
       <c r="P98">
-        <v>-260.4051240514397</v>
+        <v>-225.6860904514396</v>
       </c>
       <c r="Q98">
-        <v>-7.405124051439657</v>
+        <v>27.31390954856036</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.239236084943169</v>
+        <v>1.22643166320574</v>
       </c>
       <c r="T98">
-        <v>14.29562642103007</v>
+        <v>14.14366310539155</v>
       </c>
       <c r="U98">
-        <v>0.2455994875609555</v>
+        <v>0.2305994875609555</v>
       </c>
       <c r="V98">
-        <v>0.1463171555841542</v>
+        <v>0.1558347714165925</v>
       </c>
       <c r="W98">
-        <v>0.2096640691281106</v>
+        <v>0.1946640691281106</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5419153910524228</v>
+        <v>0.5771658200614537</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9500,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2528449446363226</v>
+        <v>0.2377827677668254</v>
       </c>
       <c r="C99">
-        <v>-2026.93703334659</v>
+        <v>-1959.55644903177</v>
       </c>
       <c r="D99">
-        <v>859.7789666534102</v>
+        <v>927.1595509682296</v>
       </c>
       <c r="E99">
         <v>1464.716</v>
@@ -9405,37 +9533,37 @@
         <v>422</v>
       </c>
       <c r="M99">
-        <v>786.831007890834</v>
+        <v>738.775267890834</v>
       </c>
       <c r="N99">
-        <v>-364.831007890834</v>
+        <v>-316.775267890834</v>
       </c>
       <c r="O99">
-        <v>-98.5043721305252</v>
+        <v>-85.52932233052519</v>
       </c>
       <c r="P99">
-        <v>-266.3266357603088</v>
+        <v>-231.2459455603088</v>
       </c>
       <c r="Q99">
-        <v>-13.32663576030882</v>
+        <v>21.75405443969117</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.637048113257559</v>
+        <v>1.619975550940987</v>
       </c>
       <c r="T99">
-        <v>19.06083522804009</v>
+        <v>18.85821747385541</v>
       </c>
       <c r="U99">
-        <v>0.2455994875609555</v>
+        <v>0.2305994875609555</v>
       </c>
       <c r="V99">
-        <v>0.1448087312997814</v>
+        <v>0.1542282273813699</v>
       </c>
       <c r="W99">
-        <v>0.2100345373593771</v>
+        <v>0.1950345373593771</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.536328634443635</v>
+        <v>0.5712156569680367</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9582,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.254842939511932</v>
+        <v>0.2396307626424349</v>
       </c>
       <c r="C100">
-        <v>-2068.182646309463</v>
+        <v>-2001.424047430413</v>
       </c>
       <c r="D100">
-        <v>851.5613536905373</v>
+        <v>918.3199525695873</v>
       </c>
       <c r="E100">
         <v>1497.744</v>
@@ -9487,37 +9615,37 @@
         <v>422</v>
       </c>
       <c r="M100">
-        <v>794.9426677659973</v>
+        <v>746.3915077659973</v>
       </c>
       <c r="N100">
-        <v>-372.9426677659973</v>
+        <v>-324.3915077659973</v>
       </c>
       <c r="O100">
-        <v>-100.6945202968193</v>
+        <v>-87.58570709681928</v>
       </c>
       <c r="P100">
-        <v>-272.248147469178</v>
+        <v>-236.805800669178</v>
       </c>
       <c r="Q100">
-        <v>-19.24814746917798</v>
+        <v>16.19419933082199</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.432672169886337</v>
+        <v>2.40706332641148</v>
       </c>
       <c r="T100">
-        <v>28.59125284206013</v>
+        <v>28.28732621078311</v>
       </c>
       <c r="U100">
-        <v>0.2455994875609555</v>
+        <v>0.2305994875609555</v>
       </c>
       <c r="V100">
-        <v>0.1433310911844776</v>
+        <v>0.152654469959111</v>
       </c>
       <c r="W100">
-        <v>0.2103974450144952</v>
+        <v>0.1953974450144952</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9653,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5308558932758428</v>
+        <v>0.5653869257744852</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9664,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2568409343875416</v>
+        <v>0.2414787575180445</v>
       </c>
       <c r="C101">
-        <v>-2109.272661509872</v>
+        <v>-2043.124683070805</v>
       </c>
       <c r="D101">
-        <v>843.4993384901283</v>
+        <v>909.6473169291951</v>
       </c>
       <c r="E101">
         <v>1530.772</v>
@@ -9569,37 +9697,37 @@
         <v>422</v>
       </c>
       <c r="M101">
-        <v>803.0543276411605</v>
+        <v>754.0077476411604</v>
       </c>
       <c r="N101">
-        <v>-381.0543276411605</v>
+        <v>-332.0077476411604</v>
       </c>
       <c r="O101">
-        <v>-102.8846684631133</v>
+        <v>-89.64209186311332</v>
       </c>
       <c r="P101">
-        <v>-278.1696591780471</v>
+        <v>-242.3656557780471</v>
       </c>
       <c r="Q101">
-        <v>-25.16965917804714</v>
+        <v>10.63434422195286</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.819544339772674</v>
+        <v>4.768326652822961</v>
       </c>
       <c r="T101">
-        <v>57.18250568412027</v>
+        <v>56.57465242156621</v>
       </c>
       <c r="U101">
-        <v>0.2455994875609555</v>
+        <v>0.2305994875609555</v>
       </c>
       <c r="V101">
-        <v>0.1418833023846344</v>
+        <v>0.1511125056160897</v>
       </c>
       <c r="W101">
-        <v>0.2107530212018332</v>
+        <v>0.1957530212018332</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9735,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.5254937125356828</v>
+        <v>0.5596759467262582</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/south_africa/south_africa_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_paper_forest_products.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1013330940674907</v>
+        <v>0.1013098809727034</v>
       </c>
       <c r="C2">
-        <v>3522.271734724556</v>
+        <v>3490.584113685801</v>
       </c>
       <c r="D2">
-        <v>3205.271734724556</v>
+        <v>3206.612113685801</v>
       </c>
       <c r="E2">
-        <v>-1739</v>
+        <v>-1705.972</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33.02800000000001</v>
       </c>
       <c r="G2">
         <v>317</v>
@@ -1579,28 +1579,28 @@
         <v>422</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.645525875163237</v>
       </c>
       <c r="N2">
-        <v>422</v>
+        <v>419.3544741248368</v>
       </c>
       <c r="O2">
-        <v>113.94</v>
+        <v>113.2257080137059</v>
       </c>
       <c r="P2">
-        <v>308.06</v>
+        <v>306.1287661111309</v>
       </c>
       <c r="Q2">
-        <v>561.0599999999999</v>
+        <v>559.1287661111309</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1013330940674907</v>
+        <v>0.1017425805186954</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.670177699583503</v>
       </c>
       <c r="U2">
         <v>0.08009948756095545</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>159.5145993323393</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1013098809727034</v>
+        <v>0.1012866678779162</v>
       </c>
       <c r="C3">
-        <v>3490.584113685801</v>
+        <v>3458.89761415407</v>
       </c>
       <c r="D3">
-        <v>3206.612113685801</v>
+        <v>3207.95361415407</v>
       </c>
       <c r="E3">
-        <v>-1705.972</v>
+        <v>-1672.944</v>
       </c>
       <c r="F3">
-        <v>33.02800000000001</v>
+        <v>66.05600000000001</v>
       </c>
       <c r="G3">
         <v>317</v>
@@ -1661,28 +1661,28 @@
         <v>422</v>
       </c>
       <c r="M3">
-        <v>2.645525875163237</v>
+        <v>5.291051750326474</v>
       </c>
       <c r="N3">
-        <v>419.3544741248368</v>
+        <v>416.7089482496735</v>
       </c>
       <c r="O3">
-        <v>113.2257080137059</v>
+        <v>112.5114160274119</v>
       </c>
       <c r="P3">
-        <v>306.1287661111309</v>
+        <v>304.1975322222617</v>
       </c>
       <c r="Q3">
-        <v>559.1287661111309</v>
+        <v>557.1975322222617</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1017425805186954</v>
+        <v>0.1021604238362512</v>
       </c>
       <c r="T3">
-        <v>0.670177699583503</v>
+        <v>0.6751833548598508</v>
       </c>
       <c r="U3">
         <v>0.08009948756095545</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>159.5145993323393</v>
+        <v>79.75729966616964</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1012866678779162</v>
+        <v>0.1012634547831289</v>
       </c>
       <c r="C4">
-        <v>3458.89761415407</v>
+        <v>3427.212237537516</v>
       </c>
       <c r="D4">
-        <v>3207.95361415407</v>
+        <v>3209.296237537515</v>
       </c>
       <c r="E4">
-        <v>-1672.944</v>
+        <v>-1639.916</v>
       </c>
       <c r="F4">
-        <v>66.05600000000001</v>
+        <v>99.084</v>
       </c>
       <c r="G4">
         <v>317</v>
@@ -1743,28 +1743,28 @@
         <v>422</v>
       </c>
       <c r="M4">
-        <v>5.291051750326474</v>
+        <v>7.93657762548971</v>
       </c>
       <c r="N4">
-        <v>416.7089482496735</v>
+        <v>414.0634223745103</v>
       </c>
       <c r="O4">
-        <v>112.5114160274119</v>
+        <v>111.7971240411178</v>
       </c>
       <c r="P4">
-        <v>304.1975322222617</v>
+        <v>302.2662983333925</v>
       </c>
       <c r="Q4">
-        <v>557.1975322222617</v>
+        <v>555.2662983333926</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1021604238362512</v>
+        <v>0.1025868824799422</v>
       </c>
       <c r="T4">
-        <v>0.6751833548598508</v>
+        <v>0.6802922195233396</v>
       </c>
       <c r="U4">
         <v>0.08009948756095545</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>79.75729966616964</v>
+        <v>53.17153311077978</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1012634547831289</v>
+        <v>0.1012402416883417</v>
       </c>
       <c r="C5">
-        <v>3427.212237537516</v>
+        <v>3395.527985246646</v>
       </c>
       <c r="D5">
-        <v>3209.296237537515</v>
+        <v>3210.639985246646</v>
       </c>
       <c r="E5">
-        <v>-1639.916</v>
+        <v>-1606.888</v>
       </c>
       <c r="F5">
-        <v>99.084</v>
+        <v>132.112</v>
       </c>
       <c r="G5">
         <v>317</v>
@@ -1825,28 +1825,28 @@
         <v>422</v>
       </c>
       <c r="M5">
-        <v>7.93657762548971</v>
+        <v>10.58210350065295</v>
       </c>
       <c r="N5">
-        <v>414.0634223745103</v>
+        <v>411.4178964993471</v>
       </c>
       <c r="O5">
-        <v>111.7971240411178</v>
+        <v>111.0828320548237</v>
       </c>
       <c r="P5">
-        <v>302.2662983333925</v>
+        <v>300.3350644445234</v>
       </c>
       <c r="Q5">
-        <v>555.2662983333926</v>
+        <v>553.3350644445234</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1025868824799422</v>
+        <v>0.1030222256787102</v>
       </c>
       <c r="T5">
-        <v>0.6802922195233396</v>
+        <v>0.685507518867318</v>
       </c>
       <c r="U5">
         <v>0.08009948756095545</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>53.17153311077978</v>
+        <v>39.87864983308482</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1012402416883417</v>
+        <v>0.1012170285935544</v>
       </c>
       <c r="C6">
-        <v>3395.527985246646</v>
+        <v>3363.844858694334</v>
       </c>
       <c r="D6">
-        <v>3210.639985246646</v>
+        <v>3211.984858694334</v>
       </c>
       <c r="E6">
-        <v>-1606.888</v>
+        <v>-1573.86</v>
       </c>
       <c r="F6">
-        <v>132.112</v>
+        <v>165.14</v>
       </c>
       <c r="G6">
         <v>317</v>
@@ -1907,28 +1907,28 @@
         <v>422</v>
       </c>
       <c r="M6">
-        <v>10.58210350065295</v>
+        <v>13.22762937581618</v>
       </c>
       <c r="N6">
-        <v>411.4178964993471</v>
+        <v>408.7723706241838</v>
       </c>
       <c r="O6">
-        <v>111.0828320548237</v>
+        <v>110.3685400685296</v>
       </c>
       <c r="P6">
-        <v>300.3350644445234</v>
+        <v>298.4038305556542</v>
       </c>
       <c r="Q6">
-        <v>553.3350644445234</v>
+        <v>551.4038305556542</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1030222256787102</v>
+        <v>0.1034667339974521</v>
       </c>
       <c r="T6">
-        <v>0.685507518867318</v>
+        <v>0.6908326139869589</v>
       </c>
       <c r="U6">
         <v>0.08009948756095545</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.87864983308482</v>
+        <v>31.90291986646786</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1012170285935544</v>
+        <v>0.1011938154987671</v>
       </c>
       <c r="C7">
-        <v>3363.844858694334</v>
+        <v>3332.162859295823</v>
       </c>
       <c r="D7">
-        <v>3211.984858694334</v>
+        <v>3213.330859295823</v>
       </c>
       <c r="E7">
-        <v>-1573.86</v>
+        <v>-1540.832</v>
       </c>
       <c r="F7">
-        <v>165.14</v>
+        <v>198.168</v>
       </c>
       <c r="G7">
         <v>317</v>
@@ -1989,28 +1989,28 @@
         <v>422</v>
       </c>
       <c r="M7">
-        <v>13.22762937581618</v>
+        <v>15.87315525097942</v>
       </c>
       <c r="N7">
-        <v>408.7723706241838</v>
+        <v>406.1268447490206</v>
       </c>
       <c r="O7">
-        <v>110.3685400685296</v>
+        <v>109.6542480822356</v>
       </c>
       <c r="P7">
-        <v>298.4038305556542</v>
+        <v>296.472596666785</v>
       </c>
       <c r="Q7">
-        <v>551.4038305556542</v>
+        <v>549.472596666785</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1034667339974521</v>
+        <v>0.1039206999399971</v>
       </c>
       <c r="T7">
-        <v>0.6908326139869589</v>
+        <v>0.6962710090027625</v>
       </c>
       <c r="U7">
         <v>0.08009948756095545</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.90291986646786</v>
+        <v>26.58576655538988</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1011938154987671</v>
+        <v>0.1011706024039799</v>
       </c>
       <c r="C8">
-        <v>3332.162859295823</v>
+        <v>3300.481988468726</v>
       </c>
       <c r="D8">
-        <v>3213.330859295823</v>
+        <v>3214.677988468726</v>
       </c>
       <c r="E8">
-        <v>-1540.832</v>
+        <v>-1507.804</v>
       </c>
       <c r="F8">
-        <v>198.168</v>
+        <v>231.196</v>
       </c>
       <c r="G8">
         <v>317</v>
@@ -2071,28 +2071,28 @@
         <v>422</v>
       </c>
       <c r="M8">
-        <v>15.87315525097942</v>
+        <v>18.51868112614266</v>
       </c>
       <c r="N8">
-        <v>406.1268447490206</v>
+        <v>403.4813188738573</v>
       </c>
       <c r="O8">
-        <v>109.6542480822356</v>
+        <v>108.9399560959415</v>
       </c>
       <c r="P8">
-        <v>296.472596666785</v>
+        <v>294.5413627779159</v>
       </c>
       <c r="Q8">
-        <v>549.472596666785</v>
+        <v>547.5413627779159</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1039206999399971</v>
+        <v>0.104384428590984</v>
       </c>
       <c r="T8">
-        <v>0.6962710090027625</v>
+        <v>0.7018263587500887</v>
       </c>
       <c r="U8">
         <v>0.08009948756095545</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.58576655538988</v>
+        <v>22.7877999046199</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1011706024039799</v>
+        <v>0.1011473893091926</v>
       </c>
       <c r="C9">
-        <v>3300.481988468726</v>
+        <v>3268.802247633037</v>
       </c>
       <c r="D9">
-        <v>3214.677988468726</v>
+        <v>3216.026247633037</v>
       </c>
       <c r="E9">
-        <v>-1507.804</v>
+        <v>-1474.776</v>
       </c>
       <c r="F9">
-        <v>231.196</v>
+        <v>264.224</v>
       </c>
       <c r="G9">
         <v>317</v>
@@ -2153,28 +2153,28 @@
         <v>422</v>
       </c>
       <c r="M9">
-        <v>18.51868112614266</v>
+        <v>21.1642070013059</v>
       </c>
       <c r="N9">
-        <v>403.4813188738573</v>
+        <v>400.8357929986941</v>
       </c>
       <c r="O9">
-        <v>108.9399560959415</v>
+        <v>108.2256641096474</v>
       </c>
       <c r="P9">
-        <v>294.5413627779159</v>
+        <v>292.6101288890467</v>
       </c>
       <c r="Q9">
-        <v>547.5413627779159</v>
+        <v>545.6101288890467</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.104384428590984</v>
+        <v>0.1048582382996009</v>
       </c>
       <c r="T9">
-        <v>0.7018263587500887</v>
+        <v>0.7075024769701829</v>
       </c>
       <c r="U9">
         <v>0.08009948756095545</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.7877999046199</v>
+        <v>19.93932491654241</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1011473893091926</v>
+        <v>0.1011241762144054</v>
       </c>
       <c r="C10">
-        <v>3268.802247633037</v>
+        <v>3237.123638211132</v>
       </c>
       <c r="D10">
-        <v>3216.026247633037</v>
+        <v>3217.375638211132</v>
       </c>
       <c r="E10">
-        <v>-1474.776</v>
+        <v>-1441.748</v>
       </c>
       <c r="F10">
-        <v>264.224</v>
+        <v>297.252</v>
       </c>
       <c r="G10">
         <v>317</v>
@@ -2235,28 +2235,28 @@
         <v>422</v>
       </c>
       <c r="M10">
-        <v>21.1642070013059</v>
+        <v>23.80973287646913</v>
       </c>
       <c r="N10">
-        <v>400.8357929986941</v>
+        <v>398.1902671235309</v>
       </c>
       <c r="O10">
-        <v>108.2256641096474</v>
+        <v>107.5113721233533</v>
       </c>
       <c r="P10">
-        <v>292.6101288890467</v>
+        <v>290.6788950001775</v>
       </c>
       <c r="Q10">
-        <v>545.6101288890467</v>
+        <v>543.6788950001776</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1048582382996009</v>
+        <v>0.1053424614084073</v>
       </c>
       <c r="T10">
-        <v>0.7075024769701829</v>
+        <v>0.7133033450412682</v>
       </c>
       <c r="U10">
         <v>0.08009948756095545</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.93932491654241</v>
+        <v>17.72384437025992</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1011241762144054</v>
+        <v>0.1011009631196182</v>
       </c>
       <c r="C11">
-        <v>3237.123638211132</v>
+        <v>3205.446161627776</v>
       </c>
       <c r="D11">
-        <v>3217.375638211132</v>
+        <v>3218.726161627776</v>
       </c>
       <c r="E11">
-        <v>-1441.748</v>
+        <v>-1408.72</v>
       </c>
       <c r="F11">
-        <v>297.252</v>
+        <v>330.28</v>
       </c>
       <c r="G11">
         <v>317</v>
@@ -2317,28 +2317,28 @@
         <v>422</v>
       </c>
       <c r="M11">
-        <v>23.80973287646913</v>
+        <v>26.45525875163236</v>
       </c>
       <c r="N11">
-        <v>398.1902671235309</v>
+        <v>395.5447412483676</v>
       </c>
       <c r="O11">
-        <v>107.5113721233533</v>
+        <v>106.7970801370593</v>
       </c>
       <c r="P11">
-        <v>290.6788950001775</v>
+        <v>288.7476611113084</v>
       </c>
       <c r="Q11">
-        <v>543.6788950001776</v>
+        <v>541.7476611113084</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1053424614084073</v>
+        <v>0.1058374450307427</v>
       </c>
       <c r="T11">
-        <v>0.7133033450412682</v>
+        <v>0.7192331212917109</v>
       </c>
       <c r="U11">
         <v>0.08009948756095545</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.72384437025992</v>
+        <v>15.95145993323393</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1011009631196182</v>
+        <v>0.1010777500248309</v>
       </c>
       <c r="C12">
-        <v>3205.446161627775</v>
+        <v>3173.769819310124</v>
       </c>
       <c r="D12">
-        <v>3218.726161627776</v>
+        <v>3220.077819310124</v>
       </c>
       <c r="E12">
-        <v>-1408.72</v>
+        <v>-1375.692</v>
       </c>
       <c r="F12">
-        <v>330.28</v>
+        <v>363.308</v>
       </c>
       <c r="G12">
         <v>317</v>
@@ -2399,28 +2399,28 @@
         <v>422</v>
       </c>
       <c r="M12">
-        <v>26.45525875163237</v>
+        <v>29.1007846267956</v>
       </c>
       <c r="N12">
-        <v>395.5447412483676</v>
+        <v>392.8992153732044</v>
       </c>
       <c r="O12">
-        <v>106.7970801370593</v>
+        <v>106.0827881507652</v>
       </c>
       <c r="P12">
-        <v>288.7476611113084</v>
+        <v>286.8164272224392</v>
       </c>
       <c r="Q12">
-        <v>541.7476611113084</v>
+        <v>539.8164272224392</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1058374450307427</v>
+        <v>0.1063435518805463</v>
       </c>
       <c r="T12">
-        <v>0.7192331212917109</v>
+        <v>0.7252961509410399</v>
       </c>
       <c r="U12">
         <v>0.08009948756095545</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.95145993323393</v>
+        <v>14.50132721203085</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1010777500248309</v>
+        <v>0.1010545369300437</v>
       </c>
       <c r="C13">
-        <v>3173.769819310124</v>
+        <v>3142.094612687737</v>
       </c>
       <c r="D13">
-        <v>3220.077819310124</v>
+        <v>3221.430612687737</v>
       </c>
       <c r="E13">
-        <v>-1375.692</v>
+        <v>-1342.664</v>
       </c>
       <c r="F13">
-        <v>363.308</v>
+        <v>396.336</v>
       </c>
       <c r="G13">
         <v>317</v>
@@ -2481,28 +2481,28 @@
         <v>422</v>
       </c>
       <c r="M13">
-        <v>29.1007846267956</v>
+        <v>31.74631050195884</v>
       </c>
       <c r="N13">
-        <v>392.8992153732044</v>
+        <v>390.2536894980412</v>
       </c>
       <c r="O13">
-        <v>106.0827881507652</v>
+        <v>105.3684961644711</v>
       </c>
       <c r="P13">
-        <v>286.8164272224392</v>
+        <v>284.88519333357</v>
       </c>
       <c r="Q13">
-        <v>539.8164272224392</v>
+        <v>537.88519333357</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1063435518805463</v>
+        <v>0.1068611611587545</v>
       </c>
       <c r="T13">
-        <v>0.7252961509410399</v>
+        <v>0.7314969767187629</v>
       </c>
       <c r="U13">
         <v>0.08009948756095545</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.50132721203085</v>
+        <v>13.29288327769494</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1010545369300437</v>
+        <v>0.1011736738352564</v>
       </c>
       <c r="C14">
-        <v>3142.094612687737</v>
+        <v>3102.135678780498</v>
       </c>
       <c r="D14">
-        <v>3221.430612687737</v>
+        <v>3214.499678780498</v>
       </c>
       <c r="E14">
-        <v>-1342.664</v>
+        <v>-1309.636</v>
       </c>
       <c r="F14">
-        <v>396.336</v>
+        <v>429.364</v>
       </c>
       <c r="G14">
         <v>317</v>
@@ -2563,45 +2563,45 @@
         <v>422</v>
       </c>
       <c r="M14">
-        <v>31.74631050195884</v>
+        <v>35.03588237712208</v>
       </c>
       <c r="N14">
-        <v>390.2536894980412</v>
+        <v>386.9641176228779</v>
       </c>
       <c r="O14">
-        <v>105.3684961644711</v>
+        <v>104.480311758177</v>
       </c>
       <c r="P14">
-        <v>284.88519333357</v>
+        <v>282.4838058647009</v>
       </c>
       <c r="Q14">
-        <v>537.88519333357</v>
+        <v>535.4838058647008</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1068611611587545</v>
+        <v>0.1073906695008296</v>
       </c>
       <c r="T14">
-        <v>0.7314969767187629</v>
+        <v>0.7378403502155139</v>
       </c>
       <c r="U14">
-        <v>0.08009948756095545</v>
+        <v>0.08159948756095545</v>
       </c>
       <c r="V14">
         <v>0.27</v>
       </c>
       <c r="W14">
-        <v>0.05847262591949747</v>
+        <v>0.05956762591949748</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.29288327769494</v>
+        <v>12.04479440413808</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1011736738352564</v>
+        <v>0.1011614107404691</v>
       </c>
       <c r="C15">
-        <v>3102.135678780498</v>
+        <v>3069.819721947882</v>
       </c>
       <c r="D15">
-        <v>3214.499678780498</v>
+        <v>3215.211721947881</v>
       </c>
       <c r="E15">
-        <v>-1309.636</v>
+        <v>-1276.608</v>
       </c>
       <c r="F15">
-        <v>429.364</v>
+        <v>462.3920000000001</v>
       </c>
       <c r="G15">
         <v>317</v>
@@ -2645,28 +2645,28 @@
         <v>422</v>
       </c>
       <c r="M15">
-        <v>35.03588237712208</v>
+        <v>37.73095025228532</v>
       </c>
       <c r="N15">
-        <v>386.9641176228779</v>
+        <v>384.2690497477147</v>
       </c>
       <c r="O15">
-        <v>104.480311758177</v>
+        <v>103.752643431883</v>
       </c>
       <c r="P15">
-        <v>282.4838058647009</v>
+        <v>280.5164063158317</v>
       </c>
       <c r="Q15">
-        <v>535.4838058647008</v>
+        <v>533.5164063158318</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1073906695008296</v>
+        <v>0.1079324919903948</v>
       </c>
       <c r="T15">
-        <v>0.7378403502155139</v>
+        <v>0.7443312440261428</v>
       </c>
       <c r="U15">
         <v>0.08159948756095545</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.04479440413808</v>
+        <v>11.18445194669965</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1011614107404691</v>
+        <v>0.1011491476456819</v>
       </c>
       <c r="C16">
-        <v>3069.819721947882</v>
+        <v>3037.504080634227</v>
       </c>
       <c r="D16">
-        <v>3215.211721947881</v>
+        <v>3215.924080634227</v>
       </c>
       <c r="E16">
-        <v>-1276.608</v>
+        <v>-1243.58</v>
       </c>
       <c r="F16">
-        <v>462.3920000000001</v>
+        <v>495.4200000000001</v>
       </c>
       <c r="G16">
         <v>317</v>
@@ -2727,28 +2727,28 @@
         <v>422</v>
       </c>
       <c r="M16">
-        <v>37.73095025228532</v>
+        <v>40.42601812744855</v>
       </c>
       <c r="N16">
-        <v>384.2690497477147</v>
+        <v>381.5739818725514</v>
       </c>
       <c r="O16">
-        <v>103.752643431883</v>
+        <v>103.0249751055889</v>
       </c>
       <c r="P16">
-        <v>280.5164063158317</v>
+        <v>278.5490067669625</v>
       </c>
       <c r="Q16">
-        <v>533.5164063158318</v>
+        <v>531.5490067669625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1079324919903948</v>
+        <v>0.1084870632444203</v>
       </c>
       <c r="T16">
-        <v>0.7443312440261428</v>
+        <v>0.7509748647499631</v>
       </c>
       <c r="U16">
         <v>0.08159948756095545</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.18445194669965</v>
+        <v>10.43882181691967</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1011491476456819</v>
+        <v>0.1011368845508946</v>
       </c>
       <c r="C17">
-        <v>3037.504080634227</v>
+        <v>3005.188755049304</v>
       </c>
       <c r="D17">
-        <v>3215.924080634227</v>
+        <v>3216.636755049304</v>
       </c>
       <c r="E17">
-        <v>-1243.58</v>
+        <v>-1210.552</v>
       </c>
       <c r="F17">
-        <v>495.42</v>
+        <v>528.4480000000001</v>
       </c>
       <c r="G17">
         <v>317</v>
@@ -2809,28 +2809,28 @@
         <v>422</v>
       </c>
       <c r="M17">
-        <v>40.42601812744855</v>
+        <v>43.12108600261179</v>
       </c>
       <c r="N17">
-        <v>381.5739818725514</v>
+        <v>378.8789139973882</v>
       </c>
       <c r="O17">
-        <v>103.0249751055889</v>
+        <v>102.2973067792948</v>
       </c>
       <c r="P17">
-        <v>278.5490067669625</v>
+        <v>276.5816072180934</v>
       </c>
       <c r="Q17">
-        <v>531.5490067669625</v>
+        <v>529.5816072180934</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1084870632444203</v>
+        <v>0.1090548385759227</v>
       </c>
       <c r="T17">
-        <v>0.7509748647499631</v>
+        <v>0.7577766669195886</v>
       </c>
       <c r="U17">
         <v>0.08159948756095545</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.43882181691967</v>
+        <v>9.786395453362191</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1011368845508946</v>
+        <v>0.1013355914561074</v>
       </c>
       <c r="C18">
-        <v>3005.188755049304</v>
+        <v>2960.6515963633</v>
       </c>
       <c r="D18">
-        <v>3216.636755049304</v>
+        <v>3205.1275963633</v>
       </c>
       <c r="E18">
-        <v>-1210.552</v>
+        <v>-1177.524</v>
       </c>
       <c r="F18">
-        <v>528.4480000000001</v>
+        <v>561.4760000000001</v>
       </c>
       <c r="G18">
         <v>317</v>
@@ -2891,45 +2891,45 @@
         <v>422</v>
       </c>
       <c r="M18">
-        <v>43.12108600261179</v>
+        <v>46.77066307777503</v>
       </c>
       <c r="N18">
-        <v>378.8789139973882</v>
+        <v>375.2293369222249</v>
       </c>
       <c r="O18">
-        <v>102.2973067792948</v>
+        <v>101.3119209690007</v>
       </c>
       <c r="P18">
-        <v>276.5816072180934</v>
+        <v>273.9174159532242</v>
       </c>
       <c r="Q18">
-        <v>529.5816072180934</v>
+        <v>526.9174159532242</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1090548385759227</v>
+        <v>0.1096362952407142</v>
       </c>
       <c r="T18">
-        <v>0.7577766669195886</v>
+        <v>0.7647423679366748</v>
       </c>
       <c r="U18">
-        <v>0.08159948756095545</v>
+        <v>0.08329948756095545</v>
       </c>
       <c r="V18">
         <v>0.27</v>
       </c>
       <c r="W18">
-        <v>0.05956762591949748</v>
+        <v>0.06080862591949748</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.786395453362191</v>
+        <v>9.022749993906549</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1013355914561074</v>
+        <v>0.1013357383613201</v>
       </c>
       <c r="C19">
-        <v>2960.6515963633</v>
+        <v>2927.615118039875</v>
       </c>
       <c r="D19">
-        <v>3205.1275963633</v>
+        <v>3205.119118039875</v>
       </c>
       <c r="E19">
-        <v>-1177.524</v>
+        <v>-1144.496</v>
       </c>
       <c r="F19">
-        <v>561.4760000000001</v>
+        <v>594.5040000000001</v>
       </c>
       <c r="G19">
         <v>317</v>
@@ -2973,28 +2973,28 @@
         <v>422</v>
       </c>
       <c r="M19">
-        <v>46.77066307777503</v>
+        <v>49.52187855293828</v>
       </c>
       <c r="N19">
-        <v>375.2293369222249</v>
+        <v>372.4781214470617</v>
       </c>
       <c r="O19">
-        <v>101.3119209690007</v>
+        <v>100.5690927907067</v>
       </c>
       <c r="P19">
-        <v>273.9174159532242</v>
+        <v>271.9090286563551</v>
       </c>
       <c r="Q19">
-        <v>526.9174159532242</v>
+        <v>524.9090286563551</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1096362952407142</v>
+        <v>0.1102319337753788</v>
       </c>
       <c r="T19">
-        <v>0.7647423679366748</v>
+        <v>0.7718779641005192</v>
       </c>
       <c r="U19">
         <v>0.08329948756095545</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.022749993906549</v>
+        <v>8.521486105356185</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1013357383613202</v>
+        <v>0.1013358852665329</v>
       </c>
       <c r="C20">
-        <v>2927.615118039875</v>
+        <v>2894.578639761304</v>
       </c>
       <c r="D20">
-        <v>3205.119118039875</v>
+        <v>3205.110639761304</v>
       </c>
       <c r="E20">
-        <v>-1144.496</v>
+        <v>-1111.468</v>
       </c>
       <c r="F20">
-        <v>594.504</v>
+        <v>627.532</v>
       </c>
       <c r="G20">
         <v>317</v>
@@ -3055,28 +3055,28 @@
         <v>422</v>
       </c>
       <c r="M20">
-        <v>49.52187855293826</v>
+        <v>52.2730940281015</v>
       </c>
       <c r="N20">
-        <v>372.4781214470618</v>
+        <v>369.7269059718985</v>
       </c>
       <c r="O20">
-        <v>100.5690927907067</v>
+        <v>99.8262646124126</v>
       </c>
       <c r="P20">
-        <v>271.9090286563551</v>
+        <v>269.9006413594859</v>
       </c>
       <c r="Q20">
-        <v>524.9090286563551</v>
+        <v>522.9006413594859</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1102319337753788</v>
+        <v>0.110842279434356</v>
       </c>
       <c r="T20">
-        <v>0.7718779641005192</v>
+        <v>0.779189747823965</v>
       </c>
       <c r="U20">
         <v>0.08329948756095545</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.521486105356189</v>
+        <v>8.072986836653229</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1013358852665329</v>
+        <v>0.1013360321717457</v>
       </c>
       <c r="C21">
-        <v>2894.578639761304</v>
+        <v>2861.542161527588</v>
       </c>
       <c r="D21">
-        <v>3205.110639761304</v>
+        <v>3205.102161527588</v>
       </c>
       <c r="E21">
-        <v>-1111.468</v>
+        <v>-1078.44</v>
       </c>
       <c r="F21">
-        <v>627.532</v>
+        <v>660.5600000000001</v>
       </c>
       <c r="G21">
         <v>317</v>
@@ -3137,28 +3137,28 @@
         <v>422</v>
       </c>
       <c r="M21">
-        <v>52.2730940281015</v>
+        <v>55.02430950326474</v>
       </c>
       <c r="N21">
-        <v>369.7269059718985</v>
+        <v>366.9756904967352</v>
       </c>
       <c r="O21">
-        <v>99.8262646124126</v>
+        <v>99.08343643411852</v>
       </c>
       <c r="P21">
-        <v>269.9006413594859</v>
+        <v>267.8922540626167</v>
       </c>
       <c r="Q21">
-        <v>522.9006413594859</v>
+        <v>520.8922540626168</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.110842279434356</v>
+        <v>0.1114678837348077</v>
       </c>
       <c r="T21">
-        <v>0.779189747823965</v>
+        <v>0.7866843261404968</v>
       </c>
       <c r="U21">
         <v>0.08329948756095545</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.072986836653229</v>
+        <v>7.669337494820568</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1013360321717457</v>
+        <v>0.1014588190769584</v>
       </c>
       <c r="C22">
-        <v>2861.542161527588</v>
+        <v>2821.443501714261</v>
       </c>
       <c r="D22">
-        <v>3205.102161527588</v>
+        <v>3198.031501714262</v>
       </c>
       <c r="E22">
-        <v>-1078.44</v>
+        <v>-1045.412</v>
       </c>
       <c r="F22">
-        <v>660.5600000000001</v>
+        <v>693.5880000000001</v>
       </c>
       <c r="G22">
         <v>317</v>
@@ -3219,45 +3219,45 @@
         <v>422</v>
       </c>
       <c r="M22">
-        <v>55.02430950326474</v>
+        <v>58.33039537842797</v>
       </c>
       <c r="N22">
-        <v>366.9756904967352</v>
+        <v>363.669604621572</v>
       </c>
       <c r="O22">
-        <v>99.08343643411852</v>
+        <v>98.19079324782446</v>
       </c>
       <c r="P22">
-        <v>267.8922540626167</v>
+        <v>265.4788113737476</v>
       </c>
       <c r="Q22">
-        <v>520.8922540626168</v>
+        <v>518.4788113737476</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1114678837348077</v>
+        <v>0.1121093261188151</v>
       </c>
       <c r="T22">
-        <v>0.7866843261404968</v>
+        <v>0.7943686406169407</v>
       </c>
       <c r="U22">
-        <v>0.08329948756095545</v>
+        <v>0.08409948756095545</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.06080862591949748</v>
+        <v>0.06139262591949748</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.669337494820568</v>
+        <v>7.2346500870122</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1014588190769584</v>
+        <v>0.1014648059821712</v>
       </c>
       <c r="C23">
-        <v>2821.443501714261</v>
+        <v>2788.071544502333</v>
       </c>
       <c r="D23">
-        <v>3198.031501714262</v>
+        <v>3197.687544502333</v>
       </c>
       <c r="E23">
-        <v>-1045.412</v>
+        <v>-1012.384</v>
       </c>
       <c r="F23">
-        <v>693.588</v>
+        <v>726.6160000000001</v>
       </c>
       <c r="G23">
         <v>317</v>
@@ -3301,28 +3301,28 @@
         <v>422</v>
       </c>
       <c r="M23">
-        <v>58.33039537842797</v>
+        <v>61.10803325359122</v>
       </c>
       <c r="N23">
-        <v>363.669604621572</v>
+        <v>360.8919667464088</v>
       </c>
       <c r="O23">
-        <v>98.19079324782446</v>
+        <v>97.44083102153039</v>
       </c>
       <c r="P23">
-        <v>265.4788113737476</v>
+        <v>263.4511357248784</v>
       </c>
       <c r="Q23">
-        <v>518.4788113737476</v>
+        <v>516.4511357248784</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1121093261188151</v>
+        <v>0.1127672157434381</v>
       </c>
       <c r="T23">
-        <v>0.7943686406169407</v>
+        <v>0.8022499887979089</v>
       </c>
       <c r="U23">
         <v>0.08409948756095545</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.234650087012201</v>
+        <v>6.905802355784373</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1014648059821712</v>
+        <v>0.1014707928873839</v>
       </c>
       <c r="C24">
-        <v>2788.071544502333</v>
+        <v>2754.699661269565</v>
       </c>
       <c r="D24">
-        <v>3197.687544502333</v>
+        <v>3197.343661269565</v>
       </c>
       <c r="E24">
-        <v>-1012.384</v>
+        <v>-979.3559999999999</v>
       </c>
       <c r="F24">
-        <v>726.6160000000001</v>
+        <v>759.6440000000001</v>
       </c>
       <c r="G24">
         <v>317</v>
@@ -3383,28 +3383,28 @@
         <v>422</v>
       </c>
       <c r="M24">
-        <v>61.10803325359122</v>
+        <v>63.88567112875445</v>
       </c>
       <c r="N24">
-        <v>360.8919667464088</v>
+        <v>358.1143288712456</v>
       </c>
       <c r="O24">
-        <v>97.44083102153039</v>
+        <v>96.69086879523631</v>
       </c>
       <c r="P24">
-        <v>263.4511357248784</v>
+        <v>261.4234600760092</v>
       </c>
       <c r="Q24">
-        <v>516.4511357248784</v>
+        <v>514.4234600760092</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1127672157434381</v>
+        <v>0.1134421934102591</v>
       </c>
       <c r="T24">
-        <v>0.8022499887979089</v>
+        <v>0.8103360473212398</v>
       </c>
       <c r="U24">
         <v>0.08409948756095545</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.905802355784373</v>
+        <v>6.605550079445922</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1014707928873839</v>
+        <v>0.1014767797925966</v>
       </c>
       <c r="C25">
-        <v>2754.699661269565</v>
+        <v>2721.327851992091</v>
       </c>
       <c r="D25">
-        <v>3197.343661269565</v>
+        <v>3196.999851992091</v>
       </c>
       <c r="E25">
-        <v>-979.3559999999999</v>
+        <v>-946.3279999999999</v>
       </c>
       <c r="F25">
-        <v>759.6440000000001</v>
+        <v>792.6720000000001</v>
       </c>
       <c r="G25">
         <v>317</v>
@@ -3465,28 +3465,28 @@
         <v>422</v>
       </c>
       <c r="M25">
-        <v>63.88567112875445</v>
+        <v>66.66330900391769</v>
       </c>
       <c r="N25">
-        <v>358.1143288712456</v>
+        <v>355.3366909960823</v>
       </c>
       <c r="O25">
-        <v>96.69086879523631</v>
+        <v>95.94090656894224</v>
       </c>
       <c r="P25">
-        <v>261.4234600760092</v>
+        <v>259.3957844271401</v>
       </c>
       <c r="Q25">
-        <v>514.4234600760092</v>
+        <v>512.3957844271401</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1134421934102591</v>
+        <v>0.1141349336472595</v>
       </c>
       <c r="T25">
-        <v>0.8103360473212398</v>
+        <v>0.8186348968583427</v>
       </c>
       <c r="U25">
         <v>0.08409948756095545</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.605550079445922</v>
+        <v>6.330318826135676</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1014767797925966</v>
+        <v>0.1014827666978094</v>
       </c>
       <c r="C26">
-        <v>2721.327851992091</v>
+        <v>2687.956116646056</v>
       </c>
       <c r="D26">
-        <v>3196.999851992091</v>
+        <v>3196.656116646056</v>
       </c>
       <c r="E26">
-        <v>-946.328</v>
+        <v>-913.3</v>
       </c>
       <c r="F26">
-        <v>792.672</v>
+        <v>825.7</v>
       </c>
       <c r="G26">
         <v>317</v>
@@ -3547,28 +3547,28 @@
         <v>422</v>
       </c>
       <c r="M26">
-        <v>66.66330900391767</v>
+        <v>69.44094687908091</v>
       </c>
       <c r="N26">
-        <v>355.3366909960823</v>
+        <v>352.5590531209191</v>
       </c>
       <c r="O26">
-        <v>95.94090656894224</v>
+        <v>95.19094434264817</v>
       </c>
       <c r="P26">
-        <v>259.3957844271401</v>
+        <v>257.3681087782709</v>
       </c>
       <c r="Q26">
-        <v>512.3957844271401</v>
+        <v>510.3681087782709</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1141349336472595</v>
+        <v>0.1148461469572467</v>
       </c>
       <c r="T26">
-        <v>0.8186348968583427</v>
+        <v>0.8271550490497682</v>
       </c>
       <c r="U26">
         <v>0.08409948756095545</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.330318826135676</v>
+        <v>6.077106073090249</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1014827666978094</v>
+        <v>0.1016785536030222</v>
       </c>
       <c r="C27">
-        <v>2687.956116646056</v>
+        <v>2643.727694162791</v>
       </c>
       <c r="D27">
-        <v>3196.656116646056</v>
+        <v>3185.455694162791</v>
       </c>
       <c r="E27">
-        <v>-913.3</v>
+        <v>-880.2719999999999</v>
       </c>
       <c r="F27">
-        <v>825.7</v>
+        <v>858.7280000000001</v>
       </c>
       <c r="G27">
         <v>317</v>
@@ -3629,45 +3629,45 @@
         <v>422</v>
       </c>
       <c r="M27">
-        <v>69.44094687908091</v>
+        <v>73.07731275424416</v>
       </c>
       <c r="N27">
-        <v>352.5590531209191</v>
+        <v>348.9226872457558</v>
       </c>
       <c r="O27">
-        <v>95.19094434264817</v>
+        <v>94.20912555635408</v>
       </c>
       <c r="P27">
-        <v>257.3681087782709</v>
+        <v>254.7135616894017</v>
       </c>
       <c r="Q27">
-        <v>510.3681087782709</v>
+        <v>507.7135616894017</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1148461469572467</v>
+        <v>0.1155765822485849</v>
       </c>
       <c r="T27">
-        <v>0.8271550490497682</v>
+        <v>0.8359054756247458</v>
       </c>
       <c r="U27">
-        <v>0.08409948756095545</v>
+        <v>0.08509948756095545</v>
       </c>
       <c r="V27">
         <v>0.27</v>
       </c>
       <c r="W27">
-        <v>0.06139262591949748</v>
+        <v>0.06212262591949748</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.077106073090249</v>
+        <v>5.774706048909703</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1016785536030222</v>
+        <v>0.1016918405082349</v>
       </c>
       <c r="C28">
-        <v>2643.727694162791</v>
+        <v>2609.942430714623</v>
       </c>
       <c r="D28">
-        <v>3185.455694162791</v>
+        <v>3184.698430714623</v>
       </c>
       <c r="E28">
-        <v>-880.2719999999999</v>
+        <v>-847.2439999999999</v>
       </c>
       <c r="F28">
-        <v>858.7280000000001</v>
+        <v>891.7560000000001</v>
       </c>
       <c r="G28">
         <v>317</v>
@@ -3711,28 +3711,28 @@
         <v>422</v>
       </c>
       <c r="M28">
-        <v>73.07731275424416</v>
+        <v>75.8879786294074</v>
       </c>
       <c r="N28">
-        <v>348.9226872457558</v>
+        <v>346.1120213705926</v>
       </c>
       <c r="O28">
-        <v>94.20912555635408</v>
+        <v>93.45024577006002</v>
       </c>
       <c r="P28">
-        <v>254.7135616894017</v>
+        <v>252.6617756005326</v>
       </c>
       <c r="Q28">
-        <v>507.7135616894017</v>
+        <v>505.6617756005326</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1155765822485849</v>
+        <v>0.1163270294657131</v>
       </c>
       <c r="T28">
-        <v>0.8359054756247458</v>
+        <v>0.8448956399141064</v>
       </c>
       <c r="U28">
         <v>0.08509948756095545</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.774706048909703</v>
+        <v>5.560828047098234</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1016918405082349</v>
+        <v>0.1017051274134477</v>
       </c>
       <c r="C29">
-        <v>2609.942430714623</v>
+        <v>2576.157527222263</v>
       </c>
       <c r="D29">
-        <v>3184.698430714623</v>
+        <v>3183.941527222263</v>
       </c>
       <c r="E29">
-        <v>-847.2439999999999</v>
+        <v>-814.2159999999999</v>
       </c>
       <c r="F29">
-        <v>891.7560000000001</v>
+        <v>924.7840000000001</v>
       </c>
       <c r="G29">
         <v>317</v>
@@ -3793,28 +3793,28 @@
         <v>422</v>
       </c>
       <c r="M29">
-        <v>75.8879786294074</v>
+        <v>78.69864450457064</v>
       </c>
       <c r="N29">
-        <v>346.1120213705926</v>
+        <v>343.3013554954293</v>
       </c>
       <c r="O29">
-        <v>93.45024577006002</v>
+        <v>92.69136598376592</v>
       </c>
       <c r="P29">
-        <v>252.6617756005326</v>
+        <v>250.6099895116634</v>
       </c>
       <c r="Q29">
-        <v>505.6617756005326</v>
+        <v>503.6099895116634</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1163270294657131</v>
+        <v>0.1170983224388727</v>
       </c>
       <c r="T29">
-        <v>0.8448956399141064</v>
+        <v>0.8541355309892825</v>
       </c>
       <c r="U29">
         <v>0.08509948756095545</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.560828047098234</v>
+        <v>5.362227045416153</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1017051274134477</v>
+        <v>0.1017184143186604</v>
       </c>
       <c r="C30">
-        <v>2576.157527222263</v>
+        <v>2542.37298342912</v>
       </c>
       <c r="D30">
-        <v>3183.941527222263</v>
+        <v>3183.18498342912</v>
       </c>
       <c r="E30">
-        <v>-814.2159999999999</v>
+        <v>-781.1879999999999</v>
       </c>
       <c r="F30">
-        <v>924.7840000000001</v>
+        <v>957.8120000000001</v>
       </c>
       <c r="G30">
         <v>317</v>
@@ -3875,28 +3875,28 @@
         <v>422</v>
       </c>
       <c r="M30">
-        <v>78.69864450457064</v>
+        <v>81.50931037973388</v>
       </c>
       <c r="N30">
-        <v>343.3013554954293</v>
+        <v>340.4906896202662</v>
       </c>
       <c r="O30">
-        <v>92.69136598376592</v>
+        <v>91.93248619747187</v>
       </c>
       <c r="P30">
-        <v>250.6099895116634</v>
+        <v>248.5582034227943</v>
       </c>
       <c r="Q30">
-        <v>503.6099895116634</v>
+        <v>501.5582034227943</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1170983224388727</v>
+        <v>0.1178913419746565</v>
       </c>
       <c r="T30">
-        <v>0.8541355309892825</v>
+        <v>0.8636357006862946</v>
       </c>
       <c r="U30">
         <v>0.08509948756095545</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.362227045416153</v>
+        <v>5.177322664539735</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1017184143186604</v>
+        <v>0.1017317012238731</v>
       </c>
       <c r="C31">
-        <v>2542.37298342912</v>
+        <v>2508.588799078851</v>
       </c>
       <c r="D31">
-        <v>3183.18498342912</v>
+        <v>3182.428799078851</v>
       </c>
       <c r="E31">
-        <v>-781.188</v>
+        <v>-748.16</v>
       </c>
       <c r="F31">
-        <v>957.812</v>
+        <v>990.84</v>
       </c>
       <c r="G31">
         <v>317</v>
@@ -3957,28 +3957,28 @@
         <v>422</v>
       </c>
       <c r="M31">
-        <v>81.50931037973386</v>
+        <v>84.3199762548971</v>
       </c>
       <c r="N31">
-        <v>340.4906896202662</v>
+        <v>337.6800237451029</v>
       </c>
       <c r="O31">
-        <v>91.93248619747187</v>
+        <v>91.17360641117779</v>
       </c>
       <c r="P31">
-        <v>248.5582034227943</v>
+        <v>246.5064173339251</v>
       </c>
       <c r="Q31">
-        <v>501.5582034227943</v>
+        <v>499.5064173339251</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1178913419746565</v>
+        <v>0.1187070192114627</v>
       </c>
       <c r="T31">
-        <v>0.8636357006862946</v>
+        <v>0.8734073038032214</v>
       </c>
       <c r="U31">
         <v>0.08509948756095545</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.177322664539735</v>
+        <v>5.00474524238841</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1017317012238731</v>
+        <v>0.1017449881290859</v>
       </c>
       <c r="C32">
-        <v>2508.588799078851</v>
+        <v>2474.80497391535</v>
       </c>
       <c r="D32">
-        <v>3182.428799078851</v>
+        <v>3181.67297391535</v>
       </c>
       <c r="E32">
-        <v>-748.16</v>
+        <v>-715.1319999999999</v>
       </c>
       <c r="F32">
-        <v>990.84</v>
+        <v>1023.868</v>
       </c>
       <c r="G32">
         <v>317</v>
@@ -4039,28 +4039,28 @@
         <v>422</v>
       </c>
       <c r="M32">
-        <v>84.3199762548971</v>
+        <v>87.13064213006034</v>
       </c>
       <c r="N32">
-        <v>337.6800237451029</v>
+        <v>334.8693578699397</v>
       </c>
       <c r="O32">
-        <v>91.17360641117779</v>
+        <v>90.41472662488371</v>
       </c>
       <c r="P32">
-        <v>246.5064173339251</v>
+        <v>244.454631245056</v>
       </c>
       <c r="Q32">
-        <v>499.5064173339251</v>
+        <v>497.454631245056</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1187070192114627</v>
+        <v>0.1195463392667271</v>
       </c>
       <c r="T32">
-        <v>0.8734073038032214</v>
+        <v>0.8834621417931025</v>
       </c>
       <c r="U32">
         <v>0.08509948756095545</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.00474524238841</v>
+        <v>4.843301847472656</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1017449881290859</v>
+        <v>0.1017582750342987</v>
       </c>
       <c r="C33">
-        <v>2474.80497391535</v>
+        <v>2441.02150768276</v>
       </c>
       <c r="D33">
-        <v>3181.67297391535</v>
+        <v>3180.917507682761</v>
       </c>
       <c r="E33">
-        <v>-715.1319999999999</v>
+        <v>-682.1039999999998</v>
       </c>
       <c r="F33">
-        <v>1023.868</v>
+        <v>1056.896</v>
       </c>
       <c r="G33">
         <v>317</v>
@@ -4121,28 +4121,28 @@
         <v>422</v>
       </c>
       <c r="M33">
-        <v>87.13064213006034</v>
+        <v>89.94130800522359</v>
       </c>
       <c r="N33">
-        <v>334.8693578699397</v>
+        <v>332.0586919947764</v>
       </c>
       <c r="O33">
-        <v>90.41472662488371</v>
+        <v>89.65584683858962</v>
       </c>
       <c r="P33">
-        <v>244.454631245056</v>
+        <v>242.4028451561867</v>
       </c>
       <c r="Q33">
-        <v>497.454631245056</v>
+        <v>495.4028451561867</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1195463392667271</v>
+        <v>0.1204103452059698</v>
       </c>
       <c r="T33">
-        <v>0.8834621417931025</v>
+        <v>0.8938127103120977</v>
       </c>
       <c r="U33">
         <v>0.08509948756095545</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.843301847472656</v>
+        <v>4.691948664739133</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1017582750342987</v>
+        <v>0.1017715619395114</v>
       </c>
       <c r="C34">
-        <v>2441.02150768276</v>
+        <v>2407.238400125465</v>
       </c>
       <c r="D34">
-        <v>3180.917507682761</v>
+        <v>3180.162400125465</v>
       </c>
       <c r="E34">
-        <v>-682.1039999999998</v>
+        <v>-649.0759999999998</v>
       </c>
       <c r="F34">
-        <v>1056.896</v>
+        <v>1089.924</v>
       </c>
       <c r="G34">
         <v>317</v>
@@ -4203,28 +4203,28 @@
         <v>422</v>
       </c>
       <c r="M34">
-        <v>89.94130800522359</v>
+        <v>92.75197388038683</v>
       </c>
       <c r="N34">
-        <v>332.0586919947764</v>
+        <v>329.2480261196132</v>
       </c>
       <c r="O34">
-        <v>89.65584683858962</v>
+        <v>88.89696705229557</v>
       </c>
       <c r="P34">
-        <v>242.4028451561867</v>
+        <v>240.3510590673176</v>
       </c>
       <c r="Q34">
-        <v>495.4028451561867</v>
+        <v>493.3510590673176</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1204103452059698</v>
+        <v>0.1213001423672795</v>
       </c>
       <c r="T34">
-        <v>0.8938127103120977</v>
+        <v>0.90447225102569</v>
       </c>
       <c r="U34">
         <v>0.08509948756095545</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.691948664739133</v>
+        <v>4.549768402171281</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1017715619395114</v>
+        <v>0.1024053488447241</v>
       </c>
       <c r="C35">
-        <v>2407.238400125465</v>
+        <v>2338.603424339867</v>
       </c>
       <c r="D35">
-        <v>3180.162400125465</v>
+        <v>3144.555424339867</v>
       </c>
       <c r="E35">
-        <v>-649.0759999999998</v>
+        <v>-616.0479999999998</v>
       </c>
       <c r="F35">
-        <v>1089.924</v>
+        <v>1122.952</v>
       </c>
       <c r="G35">
         <v>317</v>
@@ -4285,45 +4285,45 @@
         <v>422</v>
       </c>
       <c r="M35">
-        <v>92.75197388038683</v>
+        <v>98.37001975555006</v>
       </c>
       <c r="N35">
-        <v>329.2480261196132</v>
+        <v>323.6299802444499</v>
       </c>
       <c r="O35">
-        <v>88.89696705229557</v>
+        <v>87.38009466600148</v>
       </c>
       <c r="P35">
-        <v>240.3510590673176</v>
+        <v>236.2498855784485</v>
       </c>
       <c r="Q35">
-        <v>493.3510590673176</v>
+        <v>489.2498855784485</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1213001423672795</v>
+        <v>0.1222169030789318</v>
       </c>
       <c r="T35">
-        <v>0.90447225102569</v>
+        <v>0.9154548081245424</v>
       </c>
       <c r="U35">
-        <v>0.08509948756095545</v>
+        <v>0.08759948756095545</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.06212262591949748</v>
+        <v>0.06394762591949747</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.549768402171281</v>
+        <v>4.289924928841856</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1024053488447241</v>
+        <v>0.1024368857499369</v>
       </c>
       <c r="C36">
-        <v>2338.603424339867</v>
+        <v>2303.824453306757</v>
       </c>
       <c r="D36">
-        <v>3144.555424339867</v>
+        <v>3142.804453306757</v>
       </c>
       <c r="E36">
-        <v>-616.0479999999998</v>
+        <v>-583.0199999999998</v>
       </c>
       <c r="F36">
-        <v>1122.952</v>
+        <v>1155.98</v>
       </c>
       <c r="G36">
         <v>317</v>
@@ -4367,28 +4367,28 @@
         <v>422</v>
       </c>
       <c r="M36">
-        <v>98.37001975555006</v>
+        <v>101.2632556307133</v>
       </c>
       <c r="N36">
-        <v>323.6299802444499</v>
+        <v>320.7367443692867</v>
       </c>
       <c r="O36">
-        <v>87.38009466600148</v>
+        <v>86.59892097970742</v>
       </c>
       <c r="P36">
-        <v>236.2498855784485</v>
+        <v>234.1378233895793</v>
       </c>
       <c r="Q36">
-        <v>489.2498855784485</v>
+        <v>487.1378233895793</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1222169030789318</v>
+        <v>0.1231618718124812</v>
       </c>
       <c r="T36">
-        <v>0.9154548081245424</v>
+        <v>0.9267752900572057</v>
       </c>
       <c r="U36">
         <v>0.08759948756095545</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.289924928841856</v>
+        <v>4.16735564516066</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1024368857499369</v>
+        <v>0.1024684226551496</v>
       </c>
       <c r="C37">
-        <v>2303.824453306757</v>
+        <v>2269.047431161757</v>
       </c>
       <c r="D37">
-        <v>3142.804453306757</v>
+        <v>3141.055431161757</v>
       </c>
       <c r="E37">
-        <v>-583.0199999999998</v>
+        <v>-549.9919999999997</v>
       </c>
       <c r="F37">
-        <v>1155.98</v>
+        <v>1189.008</v>
       </c>
       <c r="G37">
         <v>317</v>
@@ -4449,28 +4449,28 @@
         <v>422</v>
       </c>
       <c r="M37">
-        <v>101.2632556307133</v>
+        <v>104.1564915058765</v>
       </c>
       <c r="N37">
-        <v>320.7367443692867</v>
+        <v>317.8435084941235</v>
       </c>
       <c r="O37">
-        <v>86.59892097970742</v>
+        <v>85.81774729341333</v>
       </c>
       <c r="P37">
-        <v>234.1378233895793</v>
+        <v>232.0257612007101</v>
       </c>
       <c r="Q37">
-        <v>487.1378233895793</v>
+        <v>485.0257612007101</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1231618718124812</v>
+        <v>0.124136370818954</v>
       </c>
       <c r="T37">
-        <v>0.9267752900572057</v>
+        <v>0.9384495370502648</v>
       </c>
       <c r="U37">
         <v>0.08759948756095545</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.16735564516066</v>
+        <v>4.051595766128418</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1024684226551496</v>
+        <v>0.1034453095603624</v>
       </c>
       <c r="C38">
-        <v>2269.047431161756</v>
+        <v>2182.789498966904</v>
       </c>
       <c r="D38">
-        <v>3141.055431161757</v>
+        <v>3087.825498966904</v>
       </c>
       <c r="E38">
-        <v>-549.992</v>
+        <v>-516.9639999999999</v>
       </c>
       <c r="F38">
-        <v>1189.008</v>
+        <v>1222.036</v>
       </c>
       <c r="G38">
         <v>317</v>
@@ -4531,45 +4531,45 @@
         <v>422</v>
       </c>
       <c r="M38">
-        <v>104.1564915058765</v>
+        <v>111.3268533810398</v>
       </c>
       <c r="N38">
-        <v>317.8435084941235</v>
+        <v>310.6731466189602</v>
       </c>
       <c r="O38">
-        <v>85.81774729341333</v>
+        <v>83.88174958711927</v>
       </c>
       <c r="P38">
-        <v>232.0257612007101</v>
+        <v>226.791397031841</v>
       </c>
       <c r="Q38">
-        <v>485.0257612007101</v>
+        <v>479.791397031841</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.124136370818954</v>
+        <v>0.1251418063018228</v>
       </c>
       <c r="T38">
-        <v>0.9384495370502648</v>
+        <v>0.9504943950589765</v>
       </c>
       <c r="U38">
-        <v>0.08759948756095545</v>
+        <v>0.09109948756095546</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.06394762591949747</v>
+        <v>0.06650262591949749</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.051595766128418</v>
+        <v>3.790639788907133</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1034453095603624</v>
+        <v>0.1035023964655752</v>
       </c>
       <c r="C39">
-        <v>2182.789498966904</v>
+        <v>2146.706610221023</v>
       </c>
       <c r="D39">
-        <v>3087.825498966904</v>
+        <v>3084.770610221023</v>
       </c>
       <c r="E39">
-        <v>-516.9639999999999</v>
+        <v>-483.9359999999999</v>
       </c>
       <c r="F39">
-        <v>1222.036</v>
+        <v>1255.064</v>
       </c>
       <c r="G39">
         <v>317</v>
@@ -4613,28 +4613,28 @@
         <v>422</v>
       </c>
       <c r="M39">
-        <v>111.3268533810398</v>
+        <v>114.335687256203</v>
       </c>
       <c r="N39">
-        <v>310.6731466189602</v>
+        <v>307.664312743797</v>
       </c>
       <c r="O39">
-        <v>83.88174958711927</v>
+        <v>83.0693644408252</v>
       </c>
       <c r="P39">
-        <v>226.791397031841</v>
+        <v>224.5949483029718</v>
       </c>
       <c r="Q39">
-        <v>479.791397031841</v>
+        <v>477.5949483029718</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1251418063018228</v>
+        <v>0.1261796751873647</v>
       </c>
       <c r="T39">
-        <v>0.9504943950589765</v>
+        <v>0.9629277968744209</v>
       </c>
       <c r="U39">
         <v>0.09109948756095546</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.790639788907133</v>
+        <v>3.690886110251683</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1035023964655752</v>
+        <v>0.1035594833707879</v>
       </c>
       <c r="C40">
-        <v>2146.706610221023</v>
+        <v>2110.629760107558</v>
       </c>
       <c r="D40">
-        <v>3084.770610221023</v>
+        <v>3081.721760107559</v>
       </c>
       <c r="E40">
-        <v>-483.9359999999999</v>
+        <v>-450.9079999999999</v>
       </c>
       <c r="F40">
-        <v>1255.064</v>
+        <v>1288.092</v>
       </c>
       <c r="G40">
         <v>317</v>
@@ -4695,28 +4695,28 @@
         <v>422</v>
       </c>
       <c r="M40">
-        <v>114.335687256203</v>
+        <v>117.3445211313662</v>
       </c>
       <c r="N40">
-        <v>307.664312743797</v>
+        <v>304.6554788686337</v>
       </c>
       <c r="O40">
-        <v>83.0693644408252</v>
+        <v>82.25697929453112</v>
       </c>
       <c r="P40">
-        <v>224.5949483029718</v>
+        <v>222.3984995741026</v>
       </c>
       <c r="Q40">
-        <v>477.5949483029718</v>
+        <v>475.3984995741026</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1261796751873647</v>
+        <v>0.1272515725609572</v>
       </c>
       <c r="T40">
-        <v>0.9629277968744209</v>
+        <v>0.9757688512084045</v>
       </c>
       <c r="U40">
         <v>0.09109948756095546</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.690886110251683</v>
+        <v>3.596248004860614</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1035594833707879</v>
+        <v>0.1036165702760007</v>
       </c>
       <c r="C41">
-        <v>2110.629760107558</v>
+        <v>2074.558930739237</v>
       </c>
       <c r="D41">
-        <v>3081.721760107559</v>
+        <v>3078.678930739237</v>
       </c>
       <c r="E41">
-        <v>-450.9079999999999</v>
+        <v>-417.8799999999999</v>
       </c>
       <c r="F41">
-        <v>1288.092</v>
+        <v>1321.12</v>
       </c>
       <c r="G41">
         <v>317</v>
@@ -4777,28 +4777,28 @@
         <v>422</v>
       </c>
       <c r="M41">
-        <v>117.3445211313662</v>
+        <v>120.3533550065295</v>
       </c>
       <c r="N41">
-        <v>304.6554788686337</v>
+        <v>301.6466449934705</v>
       </c>
       <c r="O41">
-        <v>82.25697929453112</v>
+        <v>81.44459414823706</v>
       </c>
       <c r="P41">
-        <v>222.3984995741026</v>
+        <v>220.2020508452335</v>
       </c>
       <c r="Q41">
-        <v>475.3984995741026</v>
+        <v>473.2020508452335</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1272515725609572</v>
+        <v>0.1283591998470028</v>
       </c>
       <c r="T41">
-        <v>0.9757688512084045</v>
+        <v>0.9890379406868542</v>
       </c>
       <c r="U41">
         <v>0.09109948756095546</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.596248004860614</v>
+        <v>3.506341804739099</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1036165702760007</v>
+        <v>0.1045116971812134</v>
       </c>
       <c r="C42">
-        <v>2074.558930739237</v>
+        <v>1994.59295286218</v>
       </c>
       <c r="D42">
-        <v>3078.678930739237</v>
+        <v>3031.740952862181</v>
       </c>
       <c r="E42">
-        <v>-417.8799999999999</v>
+        <v>-384.8519999999999</v>
       </c>
       <c r="F42">
-        <v>1321.12</v>
+        <v>1354.148</v>
       </c>
       <c r="G42">
         <v>317</v>
@@ -4859,45 +4859,45 @@
         <v>422</v>
       </c>
       <c r="M42">
-        <v>120.3533550065295</v>
+        <v>127.1538032816927</v>
       </c>
       <c r="N42">
-        <v>301.6466449934705</v>
+        <v>294.8461967183073</v>
       </c>
       <c r="O42">
-        <v>81.44459414823706</v>
+        <v>79.60847311394298</v>
       </c>
       <c r="P42">
-        <v>220.2020508452335</v>
+        <v>215.2377236043643</v>
       </c>
       <c r="Q42">
-        <v>473.2020508452335</v>
+        <v>468.2377236043643</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1283591998470028</v>
+        <v>0.1295043738207109</v>
       </c>
       <c r="T42">
-        <v>0.9890379406868542</v>
+        <v>1.002756829808641</v>
       </c>
       <c r="U42">
-        <v>0.09109948756095546</v>
+        <v>0.09389948756095545</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.06650262591949749</v>
+        <v>0.06854662591949748</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.506341804739099</v>
+        <v>3.318815396068916</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1045116971812134</v>
+        <v>0.1045892240864262</v>
       </c>
       <c r="C43">
-        <v>1994.59295286218</v>
+        <v>1957.56691585566</v>
       </c>
       <c r="D43">
-        <v>3031.740952862181</v>
+        <v>3027.74291585566</v>
       </c>
       <c r="E43">
-        <v>-384.8519999999999</v>
+        <v>-351.8239999999998</v>
       </c>
       <c r="F43">
-        <v>1354.148</v>
+        <v>1387.176</v>
       </c>
       <c r="G43">
         <v>317</v>
@@ -4941,28 +4941,28 @@
         <v>422</v>
       </c>
       <c r="M43">
-        <v>127.1538032816927</v>
+        <v>130.255115556856</v>
       </c>
       <c r="N43">
-        <v>294.8461967183073</v>
+        <v>291.744884443144</v>
       </c>
       <c r="O43">
-        <v>79.60847311394298</v>
+        <v>78.77111879964889</v>
       </c>
       <c r="P43">
-        <v>215.2377236043643</v>
+        <v>212.9737656434951</v>
       </c>
       <c r="Q43">
-        <v>468.2377236043643</v>
+        <v>465.9737656434951</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1295043738207109</v>
+        <v>0.1306890365521331</v>
       </c>
       <c r="T43">
-        <v>1.002756829808641</v>
+        <v>1.016948784072559</v>
       </c>
       <c r="U43">
         <v>0.09389948756095545</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.318815396068916</v>
+        <v>3.239795981876798</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1045892240864262</v>
+        <v>0.1046667509916389</v>
       </c>
       <c r="C44">
-        <v>1957.56691585566</v>
+        <v>1920.55140959632</v>
       </c>
       <c r="D44">
-        <v>3027.74291585566</v>
+        <v>3023.75540959632</v>
       </c>
       <c r="E44">
-        <v>-351.8240000000001</v>
+        <v>-318.796</v>
       </c>
       <c r="F44">
-        <v>1387.176</v>
+        <v>1420.204</v>
       </c>
       <c r="G44">
         <v>317</v>
@@ -5023,28 +5023,28 @@
         <v>422</v>
       </c>
       <c r="M44">
-        <v>130.2551155568559</v>
+        <v>133.3564278320192</v>
       </c>
       <c r="N44">
-        <v>291.7448844431441</v>
+        <v>288.6435721679808</v>
       </c>
       <c r="O44">
-        <v>78.7711187996489</v>
+        <v>77.93376448535483</v>
       </c>
       <c r="P44">
-        <v>212.9737656434952</v>
+        <v>210.709807682626</v>
       </c>
       <c r="Q44">
-        <v>465.9737656434952</v>
+        <v>463.709807682626</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1306890365521331</v>
+        <v>0.1319152663969386</v>
       </c>
       <c r="T44">
-        <v>1.016948784072559</v>
+        <v>1.031638701643982</v>
       </c>
       <c r="U44">
         <v>0.09389948756095545</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.239795981876799</v>
+        <v>3.164451889275013</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1046667509916389</v>
+        <v>0.1047442778968517</v>
       </c>
       <c r="C45">
-        <v>1920.55140959632</v>
+        <v>1883.546392532229</v>
       </c>
       <c r="D45">
-        <v>3023.75540959632</v>
+        <v>3019.778392532229</v>
       </c>
       <c r="E45">
-        <v>-318.796</v>
+        <v>-285.7679999999998</v>
       </c>
       <c r="F45">
-        <v>1420.204</v>
+        <v>1453.232</v>
       </c>
       <c r="G45">
         <v>317</v>
@@ -5105,28 +5105,28 @@
         <v>422</v>
       </c>
       <c r="M45">
-        <v>133.3564278320192</v>
+        <v>136.4577401071824</v>
       </c>
       <c r="N45">
-        <v>288.6435721679808</v>
+        <v>285.5422598928176</v>
       </c>
       <c r="O45">
-        <v>77.93376448535483</v>
+        <v>77.09641017106075</v>
       </c>
       <c r="P45">
-        <v>210.709807682626</v>
+        <v>208.4458497217568</v>
       </c>
       <c r="Q45">
-        <v>463.709807682626</v>
+        <v>461.4458497217568</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1319152663969386</v>
+        <v>0.1331852901647728</v>
       </c>
       <c r="T45">
-        <v>1.031638701643982</v>
+        <v>1.046853259128671</v>
       </c>
       <c r="U45">
         <v>0.09389948756095545</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.164451889275013</v>
+        <v>3.092532528155126</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1047442778968517</v>
+        <v>0.1048218048020644</v>
       </c>
       <c r="C46">
-        <v>1883.546392532229</v>
+        <v>1846.551823329772</v>
       </c>
       <c r="D46">
-        <v>3019.778392532229</v>
+        <v>3015.811823329772</v>
       </c>
       <c r="E46">
-        <v>-285.7679999999998</v>
+        <v>-252.7399999999998</v>
       </c>
       <c r="F46">
-        <v>1453.232</v>
+        <v>1486.26</v>
       </c>
       <c r="G46">
         <v>317</v>
@@ -5187,28 +5187,28 @@
         <v>422</v>
       </c>
       <c r="M46">
-        <v>136.4577401071824</v>
+        <v>139.5590523823457</v>
       </c>
       <c r="N46">
-        <v>285.5422598928176</v>
+        <v>282.4409476176543</v>
       </c>
       <c r="O46">
-        <v>77.09641017106075</v>
+        <v>76.25905585676668</v>
       </c>
       <c r="P46">
-        <v>208.4458497217568</v>
+        <v>206.1818917608877</v>
       </c>
       <c r="Q46">
-        <v>461.4458497217568</v>
+        <v>459.1818917608877</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1331852901647728</v>
+        <v>0.1345014966150737</v>
       </c>
       <c r="T46">
-        <v>1.046853259128671</v>
+        <v>1.062621073249166</v>
       </c>
       <c r="U46">
         <v>0.09389948756095545</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.092532528155126</v>
+        <v>3.023809583085012</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1048218048020644</v>
+        <v>0.1075185717072772</v>
       </c>
       <c r="C47">
-        <v>1846.551823329772</v>
+        <v>1681.749200351156</v>
       </c>
       <c r="D47">
-        <v>3015.811823329772</v>
+        <v>2884.037200351156</v>
       </c>
       <c r="E47">
-        <v>-252.7399999999998</v>
+        <v>-219.7119999999998</v>
       </c>
       <c r="F47">
-        <v>1486.26</v>
+        <v>1519.288</v>
       </c>
       <c r="G47">
         <v>317</v>
@@ -5269,45 +5269,45 @@
         <v>422</v>
       </c>
       <c r="M47">
-        <v>139.5590523823457</v>
+        <v>154.5108110575089</v>
       </c>
       <c r="N47">
-        <v>282.4409476176543</v>
+        <v>267.4891889424911</v>
       </c>
       <c r="O47">
-        <v>76.25905585676668</v>
+        <v>72.22208101447259</v>
       </c>
       <c r="P47">
-        <v>206.1818917608877</v>
+        <v>195.2671079280185</v>
       </c>
       <c r="Q47">
-        <v>459.1818917608877</v>
+        <v>448.2671079280185</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1345014966150737</v>
+        <v>0.1358664514524228</v>
       </c>
       <c r="T47">
-        <v>1.062621073249166</v>
+        <v>1.078972880485235</v>
       </c>
       <c r="U47">
-        <v>0.09389948756095545</v>
+        <v>0.1016994875609555</v>
       </c>
       <c r="V47">
         <v>0.27</v>
       </c>
       <c r="W47">
-        <v>0.06854662591949748</v>
+        <v>0.07424062591949748</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.023809583085012</v>
+        <v>2.731200471421587</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1075185717072772</v>
+        <v>0.1076530386124899</v>
       </c>
       <c r="C48">
-        <v>1681.749200351156</v>
+        <v>1642.45137811527</v>
       </c>
       <c r="D48">
-        <v>2884.037200351156</v>
+        <v>2877.76737811527</v>
       </c>
       <c r="E48">
-        <v>-219.7119999999998</v>
+        <v>-186.6839999999997</v>
       </c>
       <c r="F48">
-        <v>1519.288</v>
+        <v>1552.316</v>
       </c>
       <c r="G48">
         <v>317</v>
@@ -5351,28 +5351,28 @@
         <v>422</v>
       </c>
       <c r="M48">
-        <v>154.5108110575089</v>
+        <v>157.8697417326721</v>
       </c>
       <c r="N48">
-        <v>267.4891889424911</v>
+        <v>264.1302582673279</v>
       </c>
       <c r="O48">
-        <v>72.22208101447259</v>
+        <v>71.31516973217853</v>
       </c>
       <c r="P48">
-        <v>195.2671079280185</v>
+        <v>192.8150885351493</v>
       </c>
       <c r="Q48">
-        <v>448.2671079280185</v>
+        <v>445.8150885351494</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1358664514524228</v>
+        <v>0.1372829140194832</v>
       </c>
       <c r="T48">
-        <v>1.078972880485235</v>
+        <v>1.095941737050968</v>
       </c>
       <c r="U48">
         <v>0.1016994875609555</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.731200471421587</v>
+        <v>2.673089823093468</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1076530386124899</v>
+        <v>0.1077875055177027</v>
       </c>
       <c r="C49">
-        <v>1642.45137811527</v>
+        <v>1603.180757606096</v>
       </c>
       <c r="D49">
-        <v>2877.76737811527</v>
+        <v>2871.524757606097</v>
       </c>
       <c r="E49">
-        <v>-186.6839999999997</v>
+        <v>-153.6559999999997</v>
       </c>
       <c r="F49">
-        <v>1552.316</v>
+        <v>1585.344</v>
       </c>
       <c r="G49">
         <v>317</v>
@@ -5433,28 +5433,28 @@
         <v>422</v>
       </c>
       <c r="M49">
-        <v>157.8697417326721</v>
+        <v>161.2286724078354</v>
       </c>
       <c r="N49">
-        <v>264.1302582673279</v>
+        <v>260.7713275921646</v>
       </c>
       <c r="O49">
-        <v>71.31516973217853</v>
+        <v>70.40825844988444</v>
       </c>
       <c r="P49">
-        <v>192.8150885351493</v>
+        <v>190.3630691422802</v>
       </c>
       <c r="Q49">
-        <v>445.8150885351494</v>
+        <v>443.3630691422802</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1372829140194832</v>
+        <v>0.1387538559160459</v>
       </c>
       <c r="T49">
-        <v>1.095941737050968</v>
+        <v>1.113563241946151</v>
       </c>
       <c r="U49">
         <v>0.1016994875609555</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.673089823093468</v>
+        <v>2.61740045177902</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1077875055177027</v>
+        <v>0.1079219724229154</v>
       </c>
       <c r="C50">
-        <v>1603.180757606096</v>
+        <v>1563.937162184103</v>
       </c>
       <c r="D50">
-        <v>2871.524757606097</v>
+        <v>2865.309162184103</v>
       </c>
       <c r="E50">
-        <v>-153.6559999999999</v>
+        <v>-120.6279999999999</v>
       </c>
       <c r="F50">
-        <v>1585.344</v>
+        <v>1618.372</v>
       </c>
       <c r="G50">
         <v>317</v>
@@ -5515,28 +5515,28 @@
         <v>422</v>
       </c>
       <c r="M50">
-        <v>161.2286724078354</v>
+        <v>164.5876030829986</v>
       </c>
       <c r="N50">
-        <v>260.7713275921647</v>
+        <v>257.4123969170014</v>
       </c>
       <c r="O50">
-        <v>70.40825844988446</v>
+        <v>69.50134716759038</v>
       </c>
       <c r="P50">
-        <v>190.3630691422802</v>
+        <v>187.911049749411</v>
       </c>
       <c r="Q50">
-        <v>443.3630691422802</v>
+        <v>440.911049749411</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1387538559160459</v>
+        <v>0.1402824818085522</v>
       </c>
       <c r="T50">
-        <v>1.113563241946151</v>
+        <v>1.131875786248989</v>
       </c>
       <c r="U50">
         <v>0.1016994875609555</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.61740045177902</v>
+        <v>2.563984116028428</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1079219724229154</v>
+        <v>0.1080564393281282</v>
       </c>
       <c r="C51">
-        <v>1563.937162184103</v>
+        <v>1524.720416735846</v>
       </c>
       <c r="D51">
-        <v>2865.309162184103</v>
+        <v>2859.120416735846</v>
       </c>
       <c r="E51">
-        <v>-120.6279999999999</v>
+        <v>-87.59999999999991</v>
       </c>
       <c r="F51">
-        <v>1618.372</v>
+        <v>1651.4</v>
       </c>
       <c r="G51">
         <v>317</v>
@@ -5597,28 +5597,28 @@
         <v>422</v>
       </c>
       <c r="M51">
-        <v>164.5876030829986</v>
+        <v>167.9465337581618</v>
       </c>
       <c r="N51">
-        <v>257.4123969170014</v>
+        <v>254.0534662418382</v>
       </c>
       <c r="O51">
-        <v>69.50134716759038</v>
+        <v>68.59443588529631</v>
       </c>
       <c r="P51">
-        <v>187.911049749411</v>
+        <v>185.4590303565419</v>
       </c>
       <c r="Q51">
-        <v>440.911049749411</v>
+        <v>438.4590303565419</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1402824818085522</v>
+        <v>0.1418722527367588</v>
       </c>
       <c r="T51">
-        <v>1.131875786248989</v>
+        <v>1.15092083232394</v>
       </c>
       <c r="U51">
         <v>0.1016994875609555</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.563984116028428</v>
+        <v>2.51270443370786</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1080564393281282</v>
+        <v>0.1096428762333409</v>
       </c>
       <c r="C52">
-        <v>1524.720416735846</v>
+        <v>1420.645897324989</v>
       </c>
       <c r="D52">
-        <v>2859.120416735846</v>
+        <v>2788.07389732499</v>
       </c>
       <c r="E52">
-        <v>-87.59999999999991</v>
+        <v>-54.57199999999989</v>
       </c>
       <c r="F52">
-        <v>1651.4</v>
+        <v>1684.428</v>
       </c>
       <c r="G52">
         <v>317</v>
@@ -5679,45 +5679,45 @@
         <v>422</v>
       </c>
       <c r="M52">
-        <v>167.9465337581618</v>
+        <v>177.8747336333251</v>
       </c>
       <c r="N52">
-        <v>254.0534662418382</v>
+        <v>244.1252663666749</v>
       </c>
       <c r="O52">
-        <v>68.59443588529631</v>
+        <v>65.91382191900223</v>
       </c>
       <c r="P52">
-        <v>185.4590303565419</v>
+        <v>178.2114444476727</v>
       </c>
       <c r="Q52">
-        <v>438.4590303565419</v>
+        <v>431.2114444476726</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1418722527367588</v>
+        <v>0.14352691227428</v>
       </c>
       <c r="T52">
-        <v>1.15092083232394</v>
+        <v>1.170743227218277</v>
       </c>
       <c r="U52">
-        <v>0.1016994875609555</v>
+        <v>0.1055994875609555</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.07424062591949748</v>
+        <v>0.07708762591949748</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.51270443370786</v>
+        <v>2.372456117741377</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1096428762333409</v>
+        <v>0.1098058131385536</v>
       </c>
       <c r="C53">
-        <v>1420.645897324989</v>
+        <v>1380.520414923646</v>
       </c>
       <c r="D53">
-        <v>2788.07389732499</v>
+        <v>2780.976414923646</v>
       </c>
       <c r="E53">
-        <v>-54.57199999999989</v>
+        <v>-21.54399999999987</v>
       </c>
       <c r="F53">
-        <v>1684.428</v>
+        <v>1717.456</v>
       </c>
       <c r="G53">
         <v>317</v>
@@ -5761,28 +5761,28 @@
         <v>422</v>
       </c>
       <c r="M53">
-        <v>177.8747336333251</v>
+        <v>181.3624735084883</v>
       </c>
       <c r="N53">
-        <v>244.1252663666749</v>
+        <v>240.6375264915117</v>
       </c>
       <c r="O53">
-        <v>65.91382191900223</v>
+        <v>64.97213215270816</v>
       </c>
       <c r="P53">
-        <v>178.2114444476727</v>
+        <v>175.6653943388035</v>
       </c>
       <c r="Q53">
-        <v>431.2114444476726</v>
+        <v>428.6653943388035</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.14352691227428</v>
+        <v>0.1452505159591978</v>
       </c>
       <c r="T53">
-        <v>1.170743227218277</v>
+        <v>1.191391555233212</v>
       </c>
       <c r="U53">
         <v>0.1055994875609555</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.372456117741377</v>
+        <v>2.326831961630966</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1098058131385536</v>
+        <v>0.1099687500437664</v>
       </c>
       <c r="C54">
-        <v>1380.520414923646</v>
+        <v>1340.430976291784</v>
       </c>
       <c r="D54">
-        <v>2780.976414923646</v>
+        <v>2773.914976291784</v>
       </c>
       <c r="E54">
-        <v>-21.54399999999987</v>
+        <v>11.48400000000015</v>
       </c>
       <c r="F54">
-        <v>1717.456</v>
+        <v>1750.484</v>
       </c>
       <c r="G54">
         <v>317</v>
@@ -5843,28 +5843,28 @@
         <v>422</v>
       </c>
       <c r="M54">
-        <v>181.3624735084883</v>
+        <v>184.8502133836515</v>
       </c>
       <c r="N54">
-        <v>240.6375264915117</v>
+        <v>237.1497866163485</v>
       </c>
       <c r="O54">
-        <v>64.97213215270816</v>
+        <v>64.03044238641408</v>
       </c>
       <c r="P54">
-        <v>175.6653943388035</v>
+        <v>173.1193442299344</v>
       </c>
       <c r="Q54">
-        <v>428.6653943388035</v>
+        <v>426.1193442299344</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1452505159591978</v>
+        <v>0.1470474644817718</v>
       </c>
       <c r="T54">
-        <v>1.191391555233212</v>
+        <v>1.212918535504101</v>
       </c>
       <c r="U54">
         <v>0.1055994875609555</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.326831961630966</v>
+        <v>2.282929471788872</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1099687500437664</v>
+        <v>0.1101316869489792</v>
       </c>
       <c r="C55">
-        <v>1340.430976291784</v>
+        <v>1300.377307558447</v>
       </c>
       <c r="D55">
-        <v>2773.914976291784</v>
+        <v>2766.889307558447</v>
       </c>
       <c r="E55">
-        <v>11.48400000000015</v>
+        <v>44.51200000000017</v>
       </c>
       <c r="F55">
-        <v>1750.484</v>
+        <v>1783.512</v>
       </c>
       <c r="G55">
         <v>317</v>
@@ -5925,28 +5925,28 @@
         <v>422</v>
       </c>
       <c r="M55">
-        <v>184.8502133836515</v>
+        <v>188.3379532588148</v>
       </c>
       <c r="N55">
-        <v>237.1497866163485</v>
+        <v>233.6620467411852</v>
       </c>
       <c r="O55">
-        <v>64.03044238641408</v>
+        <v>63.08875262012001</v>
       </c>
       <c r="P55">
-        <v>173.1193442299344</v>
+        <v>170.5732941210652</v>
       </c>
       <c r="Q55">
-        <v>426.1193442299344</v>
+        <v>423.5732941210652</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1470474644817718</v>
+        <v>0.1489225412009794</v>
       </c>
       <c r="T55">
-        <v>1.212918535504101</v>
+        <v>1.235381471438942</v>
       </c>
       <c r="U55">
         <v>0.1055994875609555</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.282929471788872</v>
+        <v>2.240653000089079</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1101316869489792</v>
+        <v>0.1102946238541919</v>
       </c>
       <c r="C56">
-        <v>1300.377307558447</v>
+        <v>1260.359137620266</v>
       </c>
       <c r="D56">
-        <v>2766.889307558447</v>
+        <v>2759.899137620266</v>
       </c>
       <c r="E56">
-        <v>44.51200000000017</v>
+        <v>77.54000000000019</v>
       </c>
       <c r="F56">
-        <v>1783.512</v>
+        <v>1816.54</v>
       </c>
       <c r="G56">
         <v>317</v>
@@ -6007,28 +6007,28 @@
         <v>422</v>
       </c>
       <c r="M56">
-        <v>188.3379532588148</v>
+        <v>191.825693133978</v>
       </c>
       <c r="N56">
-        <v>233.6620467411852</v>
+        <v>230.174306866022</v>
       </c>
       <c r="O56">
-        <v>63.08875262012001</v>
+        <v>62.14706285382594</v>
       </c>
       <c r="P56">
-        <v>170.5732941210652</v>
+        <v>168.027244012196</v>
       </c>
       <c r="Q56">
-        <v>423.5732941210652</v>
+        <v>421.027244012196</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1489225412009794</v>
+        <v>0.1508809546632629</v>
       </c>
       <c r="T56">
-        <v>1.235381471438942</v>
+        <v>1.258842760081998</v>
       </c>
       <c r="U56">
         <v>0.1055994875609555</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.240653000089079</v>
+        <v>2.199913854632913</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1102946238541919</v>
+        <v>0.1104575607594046</v>
       </c>
       <c r="C57">
-        <v>1260.359137620266</v>
+        <v>1220.376198106595</v>
       </c>
       <c r="D57">
-        <v>2759.899137620266</v>
+        <v>2752.944198106596</v>
       </c>
       <c r="E57">
-        <v>77.54000000000019</v>
+        <v>110.5680000000002</v>
       </c>
       <c r="F57">
-        <v>1816.54</v>
+        <v>1849.568</v>
       </c>
       <c r="G57">
         <v>317</v>
@@ -6089,28 +6089,28 @@
         <v>422</v>
       </c>
       <c r="M57">
-        <v>191.825693133978</v>
+        <v>195.3134330091413</v>
       </c>
       <c r="N57">
-        <v>230.174306866022</v>
+        <v>226.6865669908587</v>
       </c>
       <c r="O57">
-        <v>62.14706285382594</v>
+        <v>61.20537308753186</v>
       </c>
       <c r="P57">
-        <v>168.027244012196</v>
+        <v>165.4811939033269</v>
       </c>
       <c r="Q57">
-        <v>421.027244012196</v>
+        <v>418.4811939033269</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1508809546632629</v>
+        <v>0.1529283869192865</v>
       </c>
       <c r="T57">
-        <v>1.258842760081998</v>
+        <v>1.283370470936102</v>
       </c>
       <c r="U57">
         <v>0.1055994875609555</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.199913854632913</v>
+        <v>2.160629678657326</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1104575607594046</v>
+        <v>0.1106204976646174</v>
       </c>
       <c r="C58">
-        <v>1220.376198106595</v>
+        <v>1180.428223345158</v>
       </c>
       <c r="D58">
-        <v>2752.944198106596</v>
+        <v>2746.024223345159</v>
       </c>
       <c r="E58">
-        <v>110.5680000000002</v>
+        <v>143.5960000000002</v>
       </c>
       <c r="F58">
-        <v>1849.568</v>
+        <v>1882.596</v>
       </c>
       <c r="G58">
         <v>317</v>
@@ -6171,28 +6171,28 @@
         <v>422</v>
       </c>
       <c r="M58">
-        <v>195.3134330091413</v>
+        <v>198.8011728843045</v>
       </c>
       <c r="N58">
-        <v>226.6865669908587</v>
+        <v>223.1988271156955</v>
       </c>
       <c r="O58">
-        <v>61.20537308753186</v>
+        <v>60.26368332123779</v>
       </c>
       <c r="P58">
-        <v>165.4811939033269</v>
+        <v>162.9351437944577</v>
       </c>
       <c r="Q58">
-        <v>418.4811939033269</v>
+        <v>415.9351437944577</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1529283869192865</v>
+        <v>0.1550710485825671</v>
       </c>
       <c r="T58">
-        <v>1.283370470936102</v>
+        <v>1.309039005550862</v>
       </c>
       <c r="U58">
         <v>0.1055994875609555</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.160629678657326</v>
+        <v>2.122723894821232</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1106204976646174</v>
+        <v>0.1107834345698302</v>
       </c>
       <c r="C59">
-        <v>1180.428223345158</v>
+        <v>1140.514950328228</v>
       </c>
       <c r="D59">
-        <v>2746.024223345159</v>
+        <v>2739.138950328228</v>
       </c>
       <c r="E59">
-        <v>143.5960000000002</v>
+        <v>176.6240000000003</v>
       </c>
       <c r="F59">
-        <v>1882.596</v>
+        <v>1915.624</v>
       </c>
       <c r="G59">
         <v>317</v>
@@ -6253,28 +6253,28 @@
         <v>422</v>
       </c>
       <c r="M59">
-        <v>198.8011728843045</v>
+        <v>202.2889127594678</v>
       </c>
       <c r="N59">
-        <v>223.1988271156955</v>
+        <v>219.7110872405322</v>
       </c>
       <c r="O59">
-        <v>60.26368332123779</v>
+        <v>59.32199355494371</v>
       </c>
       <c r="P59">
-        <v>162.9351437944577</v>
+        <v>160.3890936855885</v>
       </c>
       <c r="Q59">
-        <v>415.9351437944577</v>
+        <v>413.3890936855885</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1550710485825671</v>
+        <v>0.1573157417536229</v>
       </c>
       <c r="T59">
-        <v>1.309039005550862</v>
+        <v>1.335929851337753</v>
       </c>
       <c r="U59">
         <v>0.1055994875609555</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.122723894821232</v>
+        <v>2.086125206979487</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1107834345698301</v>
+        <v>0.1109463714750429</v>
       </c>
       <c r="C60">
-        <v>1140.514950328229</v>
+        <v>1100.636118679298</v>
       </c>
       <c r="D60">
-        <v>2739.138950328229</v>
+        <v>2732.288118679298</v>
       </c>
       <c r="E60">
-        <v>176.624</v>
+        <v>209.652</v>
       </c>
       <c r="F60">
-        <v>1915.624</v>
+        <v>1948.652</v>
       </c>
       <c r="G60">
         <v>317</v>
@@ -6335,28 +6335,28 @@
         <v>422</v>
       </c>
       <c r="M60">
-        <v>202.2889127594677</v>
+        <v>205.776652634631</v>
       </c>
       <c r="N60">
-        <v>219.7110872405323</v>
+        <v>216.223347365369</v>
       </c>
       <c r="O60">
-        <v>59.32199355494372</v>
+        <v>58.38030378864964</v>
       </c>
       <c r="P60">
-        <v>160.3890936855885</v>
+        <v>157.8430435767194</v>
       </c>
       <c r="Q60">
-        <v>413.3890936855885</v>
+        <v>410.8430435767194</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1573157417536229</v>
+        <v>0.1596699321525351</v>
       </c>
       <c r="T60">
-        <v>1.335929851337752</v>
+        <v>1.364132445699614</v>
       </c>
       <c r="U60">
         <v>0.1055994875609555</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.086125206979487</v>
+        <v>2.050767152623902</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1109463714750429</v>
+        <v>0.1111093083802557</v>
       </c>
       <c r="C61">
-        <v>1100.636118679298</v>
+        <v>1060.791470620264</v>
       </c>
       <c r="D61">
-        <v>2732.288118679298</v>
+        <v>2725.471470620264</v>
       </c>
       <c r="E61">
-        <v>209.652</v>
+        <v>242.6800000000001</v>
       </c>
       <c r="F61">
-        <v>1948.652</v>
+        <v>1981.68</v>
       </c>
       <c r="G61">
         <v>317</v>
@@ -6417,28 +6417,28 @@
         <v>422</v>
       </c>
       <c r="M61">
-        <v>205.776652634631</v>
+        <v>209.2643925097942</v>
       </c>
       <c r="N61">
-        <v>216.223347365369</v>
+        <v>212.7356074902058</v>
       </c>
       <c r="O61">
-        <v>58.38030378864964</v>
+        <v>57.43861402235557</v>
       </c>
       <c r="P61">
-        <v>157.8430435767194</v>
+        <v>155.2969934678502</v>
       </c>
       <c r="Q61">
-        <v>410.8430435767194</v>
+        <v>408.2969934678502</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1596699321525351</v>
+        <v>0.1621418320713929</v>
       </c>
       <c r="T61">
-        <v>1.364132445699614</v>
+        <v>1.393745169779569</v>
       </c>
       <c r="U61">
         <v>0.1055994875609555</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.050767152623902</v>
+        <v>2.016587700080171</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1111093083802557</v>
+        <v>0.1175955052854684</v>
       </c>
       <c r="C62">
-        <v>1060.791470620264</v>
+        <v>781.537128905793</v>
       </c>
       <c r="D62">
-        <v>2725.471470620264</v>
+        <v>2479.245128905793</v>
       </c>
       <c r="E62">
-        <v>242.6800000000001</v>
+        <v>275.7080000000001</v>
       </c>
       <c r="F62">
-        <v>1981.68</v>
+        <v>2014.708</v>
       </c>
       <c r="G62">
         <v>317</v>
@@ -6499,45 +6499,45 @@
         <v>422</v>
       </c>
       <c r="M62">
-        <v>209.2643925097942</v>
+        <v>241.3609859849575</v>
       </c>
       <c r="N62">
-        <v>212.7356074902058</v>
+        <v>180.6390140150425</v>
       </c>
       <c r="O62">
-        <v>57.43861402235557</v>
+        <v>48.77253378406149</v>
       </c>
       <c r="P62">
-        <v>155.2969934678502</v>
+        <v>131.866480230981</v>
       </c>
       <c r="Q62">
-        <v>408.2969934678502</v>
+        <v>384.866480230981</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1621418320713929</v>
+        <v>0.1647404960886537</v>
       </c>
       <c r="T62">
-        <v>1.393745169779569</v>
+        <v>1.424876495094394</v>
       </c>
       <c r="U62">
-        <v>0.1055994875609555</v>
+        <v>0.1197994875609555</v>
       </c>
       <c r="V62">
         <v>0.27</v>
       </c>
       <c r="W62">
-        <v>0.07708762591949748</v>
+        <v>0.08745362591949749</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.016587700080171</v>
+        <v>1.748418445830763</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1175955052854684</v>
+        <v>0.1178621021906812</v>
       </c>
       <c r="C63">
-        <v>781.537128905793</v>
+        <v>739.3370528972257</v>
       </c>
       <c r="D63">
-        <v>2479.245128905793</v>
+        <v>2470.073052897226</v>
       </c>
       <c r="E63">
-        <v>275.7080000000001</v>
+        <v>308.7360000000001</v>
       </c>
       <c r="F63">
-        <v>2014.708</v>
+        <v>2047.736</v>
       </c>
       <c r="G63">
         <v>317</v>
@@ -6581,28 +6581,28 @@
         <v>422</v>
       </c>
       <c r="M63">
-        <v>241.3609859849575</v>
+        <v>245.3177234601207</v>
       </c>
       <c r="N63">
-        <v>180.6390140150425</v>
+        <v>176.6822765398793</v>
       </c>
       <c r="O63">
-        <v>48.77253378406149</v>
+        <v>47.70421466576742</v>
       </c>
       <c r="P63">
-        <v>131.866480230981</v>
+        <v>128.9780618741119</v>
       </c>
       <c r="Q63">
-        <v>384.866480230981</v>
+        <v>381.9780618741119</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1647404960886537</v>
+        <v>0.1674759318962966</v>
       </c>
       <c r="T63">
-        <v>1.424876495094394</v>
+        <v>1.457646311215261</v>
       </c>
       <c r="U63">
         <v>0.1197994875609555</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.748418445830763</v>
+        <v>1.720218148317364</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1178621021906812</v>
+        <v>0.1181286990958939</v>
       </c>
       <c r="C64">
-        <v>739.3370528972257</v>
+        <v>697.2045917388864</v>
       </c>
       <c r="D64">
-        <v>2470.073052897226</v>
+        <v>2460.968591738887</v>
       </c>
       <c r="E64">
-        <v>308.7360000000001</v>
+        <v>341.7640000000001</v>
       </c>
       <c r="F64">
-        <v>2047.736</v>
+        <v>2080.764</v>
       </c>
       <c r="G64">
         <v>317</v>
@@ -6663,28 +6663,28 @@
         <v>422</v>
       </c>
       <c r="M64">
-        <v>245.3177234601207</v>
+        <v>249.2744609352839</v>
       </c>
       <c r="N64">
-        <v>176.6822765398793</v>
+        <v>172.7255390647161</v>
       </c>
       <c r="O64">
-        <v>47.70421466576742</v>
+        <v>46.63589554747334</v>
       </c>
       <c r="P64">
-        <v>128.9780618741119</v>
+        <v>126.0896435172427</v>
       </c>
       <c r="Q64">
-        <v>381.9780618741119</v>
+        <v>379.0896435172427</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1674759318962966</v>
+        <v>0.1703592290989473</v>
       </c>
       <c r="T64">
-        <v>1.457646311215261</v>
+        <v>1.492187468748067</v>
       </c>
       <c r="U64">
         <v>0.1197994875609555</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.720218148317364</v>
+        <v>1.692913098344073</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1181286990958939</v>
+        <v>0.1183952960011067</v>
       </c>
       <c r="C65">
-        <v>697.2045917388864</v>
+        <v>655.1390005102012</v>
       </c>
       <c r="D65">
-        <v>2460.968591738887</v>
+        <v>2451.931000510202</v>
       </c>
       <c r="E65">
-        <v>341.7640000000001</v>
+        <v>374.7920000000004</v>
       </c>
       <c r="F65">
-        <v>2080.764</v>
+        <v>2113.792</v>
       </c>
       <c r="G65">
         <v>317</v>
@@ -6745,28 +6745,28 @@
         <v>422</v>
       </c>
       <c r="M65">
-        <v>249.2744609352839</v>
+        <v>253.2311984104472</v>
       </c>
       <c r="N65">
-        <v>172.7255390647161</v>
+        <v>168.7688015895528</v>
       </c>
       <c r="O65">
-        <v>46.63589554747334</v>
+        <v>45.56757642917925</v>
       </c>
       <c r="P65">
-        <v>126.0896435172427</v>
+        <v>123.2012251603735</v>
       </c>
       <c r="Q65">
-        <v>379.0896435172427</v>
+        <v>376.2012251603736</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1703592290989473</v>
+        <v>0.173402709479523</v>
       </c>
       <c r="T65">
-        <v>1.492187468748067</v>
+        <v>1.528647579477141</v>
       </c>
       <c r="U65">
         <v>0.1197994875609555</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.692913098344073</v>
+        <v>1.666461331182446</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1183952960011067</v>
+        <v>0.1186618929063194</v>
       </c>
       <c r="C66">
-        <v>655.1390005102012</v>
+        <v>613.1395451930625</v>
       </c>
       <c r="D66">
-        <v>2451.931000510202</v>
+        <v>2442.959545193063</v>
       </c>
       <c r="E66">
-        <v>374.7920000000004</v>
+        <v>407.8200000000002</v>
       </c>
       <c r="F66">
-        <v>2113.792</v>
+        <v>2146.82</v>
       </c>
       <c r="G66">
         <v>317</v>
@@ -6827,28 +6827,28 @@
         <v>422</v>
       </c>
       <c r="M66">
-        <v>253.2311984104472</v>
+        <v>257.1879358856104</v>
       </c>
       <c r="N66">
-        <v>168.7688015895528</v>
+        <v>164.8120641143896</v>
       </c>
       <c r="O66">
-        <v>45.56757642917925</v>
+        <v>44.49925731088518</v>
       </c>
       <c r="P66">
-        <v>123.2012251603735</v>
+        <v>120.3128068035044</v>
       </c>
       <c r="Q66">
-        <v>376.2012251603736</v>
+        <v>373.3128068035044</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.173402709479523</v>
+        <v>0.176620103024703</v>
       </c>
       <c r="T66">
-        <v>1.528647579477141</v>
+        <v>1.567191125105019</v>
       </c>
       <c r="U66">
         <v>0.1197994875609555</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.666461331182446</v>
+        <v>1.64082346454887</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1186618929063194</v>
+        <v>0.1189284898115322</v>
       </c>
       <c r="C67">
-        <v>613.1395451930625</v>
+        <v>571.2055024730921</v>
       </c>
       <c r="D67">
-        <v>2442.959545193063</v>
+        <v>2434.053502473093</v>
       </c>
       <c r="E67">
-        <v>407.8200000000002</v>
+        <v>440.8480000000004</v>
       </c>
       <c r="F67">
-        <v>2146.82</v>
+        <v>2179.848</v>
       </c>
       <c r="G67">
         <v>317</v>
@@ -6909,28 +6909,28 @@
         <v>422</v>
       </c>
       <c r="M67">
-        <v>257.1879358856104</v>
+        <v>261.1446733607737</v>
       </c>
       <c r="N67">
-        <v>164.8120641143896</v>
+        <v>160.8553266392263</v>
       </c>
       <c r="O67">
-        <v>44.49925731088518</v>
+        <v>43.4309381925911</v>
       </c>
       <c r="P67">
-        <v>120.3128068035044</v>
+        <v>117.4243884466352</v>
       </c>
       <c r="Q67">
-        <v>373.3128068035044</v>
+        <v>370.4243884466352</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.176620103024703</v>
+        <v>0.1800267550137171</v>
       </c>
       <c r="T67">
-        <v>1.567191125105019</v>
+        <v>1.608001938122771</v>
       </c>
       <c r="U67">
         <v>0.1197994875609555</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.64082346454887</v>
+        <v>1.615962502964796</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1189284898115322</v>
+        <v>0.1191950867167449</v>
       </c>
       <c r="C68">
-        <v>571.2055024730921</v>
+        <v>529.3361595452479</v>
       </c>
       <c r="D68">
-        <v>2434.053502473093</v>
+        <v>2425.212159545248</v>
       </c>
       <c r="E68">
-        <v>440.8480000000004</v>
+        <v>473.8760000000002</v>
       </c>
       <c r="F68">
-        <v>2179.848</v>
+        <v>2212.876</v>
       </c>
       <c r="G68">
         <v>317</v>
@@ -6991,28 +6991,28 @@
         <v>422</v>
       </c>
       <c r="M68">
-        <v>261.1446733607737</v>
+        <v>265.1014108359369</v>
       </c>
       <c r="N68">
-        <v>160.8553266392263</v>
+        <v>156.8985891640631</v>
       </c>
       <c r="O68">
-        <v>43.4309381925911</v>
+        <v>42.36261907429704</v>
       </c>
       <c r="P68">
-        <v>117.4243884466352</v>
+        <v>114.535970089766</v>
       </c>
       <c r="Q68">
-        <v>370.4243884466352</v>
+        <v>367.535970089766</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1800267550137171</v>
+        <v>0.1836398707596412</v>
       </c>
       <c r="T68">
-        <v>1.608001938122771</v>
+        <v>1.651286133747661</v>
       </c>
       <c r="U68">
         <v>0.1197994875609555</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.615962502964796</v>
+        <v>1.591843659636964</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1191950867167449</v>
+        <v>0.1194616836219577</v>
       </c>
       <c r="C69">
-        <v>529.3361595452479</v>
+        <v>487.5308139236449</v>
       </c>
       <c r="D69">
-        <v>2425.212159545248</v>
+        <v>2416.434813923645</v>
       </c>
       <c r="E69">
-        <v>473.8760000000002</v>
+        <v>506.9040000000005</v>
       </c>
       <c r="F69">
-        <v>2212.876</v>
+        <v>2245.904</v>
       </c>
       <c r="G69">
         <v>317</v>
@@ -7073,28 +7073,28 @@
         <v>422</v>
       </c>
       <c r="M69">
-        <v>265.1014108359369</v>
+        <v>269.0581483111002</v>
       </c>
       <c r="N69">
-        <v>156.8985891640631</v>
+        <v>152.9418516888998</v>
       </c>
       <c r="O69">
-        <v>42.36261907429704</v>
+        <v>41.29429995600295</v>
       </c>
       <c r="P69">
-        <v>114.535970089766</v>
+        <v>111.6475517328969</v>
       </c>
       <c r="Q69">
-        <v>367.535970089766</v>
+        <v>364.6475517328969</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1836398707596412</v>
+        <v>0.1874788062396855</v>
       </c>
       <c r="T69">
-        <v>1.651286133747661</v>
+        <v>1.697275591599106</v>
       </c>
       <c r="U69">
         <v>0.1197994875609555</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.591843659636964</v>
+        <v>1.568434194054067</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1194616836219577</v>
+        <v>0.1197282805271704</v>
       </c>
       <c r="C70">
-        <v>487.5308139236449</v>
+        <v>445.7887732554918</v>
       </c>
       <c r="D70">
-        <v>2416.434813923645</v>
+        <v>2407.720773255492</v>
       </c>
       <c r="E70">
-        <v>506.9040000000005</v>
+        <v>539.9320000000002</v>
       </c>
       <c r="F70">
-        <v>2245.904</v>
+        <v>2278.932</v>
       </c>
       <c r="G70">
         <v>317</v>
@@ -7155,28 +7155,28 @@
         <v>422</v>
       </c>
       <c r="M70">
-        <v>269.0581483111002</v>
+        <v>273.0148857862634</v>
       </c>
       <c r="N70">
-        <v>152.9418516888998</v>
+        <v>148.9851142137366</v>
       </c>
       <c r="O70">
-        <v>41.29429995600295</v>
+        <v>40.22598083770889</v>
       </c>
       <c r="P70">
-        <v>111.6475517328969</v>
+        <v>108.7591333760277</v>
       </c>
       <c r="Q70">
-        <v>364.6475517328969</v>
+        <v>361.7591333760277</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1874788062396855</v>
+        <v>0.1915654149765069</v>
       </c>
       <c r="T70">
-        <v>1.697275591599106</v>
+        <v>1.746232111247418</v>
       </c>
       <c r="U70">
         <v>0.1197994875609555</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.568434194054067</v>
+        <v>1.545703263705457</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1197282805271704</v>
+        <v>0.1199948774323832</v>
       </c>
       <c r="C71">
-        <v>445.7887732554918</v>
+        <v>404.1093551390409</v>
       </c>
       <c r="D71">
-        <v>2407.720773255492</v>
+        <v>2399.069355139041</v>
       </c>
       <c r="E71">
-        <v>539.9320000000002</v>
+        <v>572.9600000000005</v>
       </c>
       <c r="F71">
-        <v>2278.932</v>
+        <v>2311.96</v>
       </c>
       <c r="G71">
         <v>317</v>
@@ -7237,28 +7237,28 @@
         <v>422</v>
       </c>
       <c r="M71">
-        <v>273.0148857862634</v>
+        <v>276.9716232614267</v>
       </c>
       <c r="N71">
-        <v>148.9851142137366</v>
+        <v>145.0283767385733</v>
       </c>
       <c r="O71">
-        <v>40.22598083770889</v>
+        <v>39.1576617194148</v>
       </c>
       <c r="P71">
-        <v>108.7591333760277</v>
+        <v>105.8707150191585</v>
       </c>
       <c r="Q71">
-        <v>361.7591333760277</v>
+        <v>358.8707150191585</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1915654149765069</v>
+        <v>0.1959244642957831</v>
       </c>
       <c r="T71">
-        <v>1.746232111247418</v>
+        <v>1.798452398872285</v>
       </c>
       <c r="U71">
         <v>0.1197994875609555</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.545703263705457</v>
+        <v>1.523621788509665</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1199948774323832</v>
+        <v>0.1202614743375959</v>
       </c>
       <c r="C72">
-        <v>404.1093551390409</v>
+        <v>362.4918869454486</v>
       </c>
       <c r="D72">
-        <v>2399.069355139041</v>
+        <v>2390.479886945449</v>
       </c>
       <c r="E72">
-        <v>572.9600000000005</v>
+        <v>605.9880000000003</v>
       </c>
       <c r="F72">
-        <v>2311.96</v>
+        <v>2344.988</v>
       </c>
       <c r="G72">
         <v>317</v>
@@ -7319,28 +7319,28 @@
         <v>422</v>
       </c>
       <c r="M72">
-        <v>276.9716232614267</v>
+        <v>280.9283607365899</v>
       </c>
       <c r="N72">
-        <v>145.0283767385733</v>
+        <v>141.0716392634101</v>
       </c>
       <c r="O72">
-        <v>39.1576617194148</v>
+        <v>38.08934260112074</v>
       </c>
       <c r="P72">
-        <v>105.8707150191585</v>
+        <v>102.9822966622894</v>
       </c>
       <c r="Q72">
-        <v>358.8707150191585</v>
+        <v>355.9822966622894</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1959244642957831</v>
+        <v>0.2005841377060438</v>
       </c>
       <c r="T72">
-        <v>1.798452398872285</v>
+        <v>1.854274085643694</v>
       </c>
       <c r="U72">
         <v>0.1197994875609555</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.523621788509665</v>
+        <v>1.50216232669967</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1202614743375959</v>
+        <v>0.1503821512428087</v>
       </c>
       <c r="C73">
-        <v>362.4918869454491</v>
+        <v>-359.0175744458368</v>
       </c>
       <c r="D73">
-        <v>2390.479886945449</v>
+        <v>1701.998425554163</v>
       </c>
       <c r="E73">
-        <v>605.9879999999998</v>
+        <v>639.0160000000001</v>
       </c>
       <c r="F73">
-        <v>2344.988</v>
+        <v>2378.016</v>
       </c>
       <c r="G73">
         <v>317</v>
@@ -7401,45 +7401,45 @@
         <v>422</v>
       </c>
       <c r="M73">
-        <v>280.9283607365898</v>
+        <v>419.9564070117531</v>
       </c>
       <c r="N73">
-        <v>141.0716392634102</v>
+        <v>2.043592988246871</v>
       </c>
       <c r="O73">
-        <v>38.08934260112076</v>
+        <v>0.5517701068266553</v>
       </c>
       <c r="P73">
-        <v>102.9822966622894</v>
+        <v>1.491822881420216</v>
       </c>
       <c r="Q73">
-        <v>355.9822966622894</v>
+        <v>254.4918228814202</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2005841377060438</v>
+        <v>0.2055766449313231</v>
       </c>
       <c r="T73">
-        <v>1.854274085643693</v>
+        <v>1.914083035755917</v>
       </c>
       <c r="U73">
-        <v>0.1197994875609555</v>
+        <v>0.1765994875609555</v>
       </c>
       <c r="V73">
         <v>0.27</v>
       </c>
       <c r="W73">
-        <v>0.08745362591949749</v>
+        <v>0.1289176259194975</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.50216232669967</v>
+        <v>1.004866202668006</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1503821512428087</v>
+        <v>0.151470551064261</v>
       </c>
       <c r="C74">
-        <v>-359.0175744458368</v>
+        <v>-409.5760478258683</v>
       </c>
       <c r="D74">
-        <v>1701.998425554163</v>
+        <v>1684.467952174132</v>
       </c>
       <c r="E74">
-        <v>639.0160000000001</v>
+        <v>672.0439999999999</v>
       </c>
       <c r="F74">
-        <v>2378.016</v>
+        <v>2411.044</v>
       </c>
       <c r="G74">
         <v>317</v>
@@ -7483,37 +7483,37 @@
         <v>422</v>
       </c>
       <c r="M74">
-        <v>419.9564070117531</v>
+        <v>425.7891348869163</v>
       </c>
       <c r="N74">
-        <v>2.043592988246871</v>
+        <v>-3.789134886916315</v>
       </c>
       <c r="O74">
-        <v>0.5517701068266553</v>
+        <v>-1.023066419467405</v>
       </c>
       <c r="P74">
-        <v>1.491822881420216</v>
+        <v>-2.76606846744891</v>
       </c>
       <c r="Q74">
-        <v>254.4918228814202</v>
+        <v>250.2339315325511</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2055766449313231</v>
+        <v>0.211299729038128</v>
       </c>
       <c r="T74">
-        <v>1.914083035755917</v>
+        <v>1.98264410865708</v>
       </c>
       <c r="U74">
         <v>0.1765994875609555</v>
       </c>
       <c r="V74">
-        <v>0.27</v>
+        <v>0.2675972462995349</v>
       </c>
       <c r="W74">
-        <v>0.1289176259194975</v>
+        <v>0.1293419509917348</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.004866202668006</v>
+        <v>0.9911009122204993</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.151470551064261</v>
+        <v>0.1527785459398706</v>
       </c>
       <c r="C75">
-        <v>-409.5760478258683</v>
+        <v>-463.1995366709937</v>
       </c>
       <c r="D75">
-        <v>1684.467952174132</v>
+        <v>1663.872463329006</v>
       </c>
       <c r="E75">
-        <v>672.0439999999999</v>
+        <v>705.0720000000001</v>
       </c>
       <c r="F75">
-        <v>2411.044</v>
+        <v>2444.072</v>
       </c>
       <c r="G75">
         <v>317</v>
@@ -7565,37 +7565,37 @@
         <v>422</v>
       </c>
       <c r="M75">
-        <v>425.7891348869163</v>
+        <v>431.6218627620796</v>
       </c>
       <c r="N75">
-        <v>-3.789134886916315</v>
+        <v>-9.621862762079616</v>
       </c>
       <c r="O75">
-        <v>-1.023066419467405</v>
+        <v>-2.597902945761496</v>
       </c>
       <c r="P75">
-        <v>-2.76606846744891</v>
+        <v>-7.023959816318119</v>
       </c>
       <c r="Q75">
-        <v>250.2339315325511</v>
+        <v>245.9760401836819</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.211299729038128</v>
+        <v>0.2176651032319022</v>
       </c>
       <c r="T75">
-        <v>1.98264410865708</v>
+        <v>2.058899651297737</v>
       </c>
       <c r="U75">
         <v>0.1765994875609555</v>
       </c>
       <c r="V75">
-        <v>0.2675972462995349</v>
+        <v>0.263981067295487</v>
       </c>
       <c r="W75">
-        <v>0.1293419509917348</v>
+        <v>0.1299805663507784</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9911009122204993</v>
+        <v>0.977707656649952</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1527785459398706</v>
+        <v>0.1540865408154801</v>
       </c>
       <c r="C76">
-        <v>-463.1995366709937</v>
+        <v>-516.325479031261</v>
       </c>
       <c r="D76">
-        <v>1663.872463329006</v>
+        <v>1643.774520968739</v>
       </c>
       <c r="E76">
-        <v>705.0720000000001</v>
+        <v>738.1000000000004</v>
       </c>
       <c r="F76">
-        <v>2444.072</v>
+        <v>2477.1</v>
       </c>
       <c r="G76">
         <v>317</v>
@@ -7647,37 +7647,37 @@
         <v>422</v>
       </c>
       <c r="M76">
-        <v>431.6218627620796</v>
+        <v>437.4545906372429</v>
       </c>
       <c r="N76">
-        <v>-9.621862762079616</v>
+        <v>-15.45459063724286</v>
       </c>
       <c r="O76">
-        <v>-2.597902945761496</v>
+        <v>-4.172739472055572</v>
       </c>
       <c r="P76">
-        <v>-7.023959816318119</v>
+        <v>-11.28185116518729</v>
       </c>
       <c r="Q76">
-        <v>245.9760401836819</v>
+        <v>241.7181488348127</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2176651032319022</v>
+        <v>0.2245397073611783</v>
       </c>
       <c r="T76">
-        <v>2.058899651297737</v>
+        <v>2.141255637349647</v>
       </c>
       <c r="U76">
         <v>0.1765994875609555</v>
       </c>
       <c r="V76">
-        <v>0.263981067295487</v>
+        <v>0.2604613197315472</v>
       </c>
       <c r="W76">
-        <v>0.1299805663507784</v>
+        <v>0.1306021519669141</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.977707656649952</v>
+        <v>0.9646715545612858</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1540865408154801</v>
+        <v>0.1553945356910897</v>
       </c>
       <c r="C77">
-        <v>-516.325479031261</v>
+        <v>-568.9716893418995</v>
       </c>
       <c r="D77">
-        <v>1643.774520968739</v>
+        <v>1624.156310658101</v>
       </c>
       <c r="E77">
-        <v>738.1000000000004</v>
+        <v>771.1280000000002</v>
       </c>
       <c r="F77">
-        <v>2477.1</v>
+        <v>2510.128</v>
       </c>
       <c r="G77">
         <v>317</v>
@@ -7729,37 +7729,37 @@
         <v>422</v>
       </c>
       <c r="M77">
-        <v>437.4545906372429</v>
+        <v>443.2873185124061</v>
       </c>
       <c r="N77">
-        <v>-15.45459063724286</v>
+        <v>-21.2873185124061</v>
       </c>
       <c r="O77">
-        <v>-4.172739472055572</v>
+        <v>-5.747575998349648</v>
       </c>
       <c r="P77">
-        <v>-11.28185116518729</v>
+        <v>-15.53974251405645</v>
       </c>
       <c r="Q77">
-        <v>241.7181488348127</v>
+        <v>237.4602574859435</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2245397073611783</v>
+        <v>0.2319871951678941</v>
       </c>
       <c r="T77">
-        <v>2.141255637349647</v>
+        <v>2.230474622239215</v>
       </c>
       <c r="U77">
         <v>0.1765994875609555</v>
       </c>
       <c r="V77">
-        <v>0.2604613197315472</v>
+        <v>0.2570341971035006</v>
       </c>
       <c r="W77">
-        <v>0.1306021519669141</v>
+        <v>0.1312073800668356</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9646715545612858</v>
+        <v>0.9519785077907427</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1553945356910897</v>
+        <v>0.1567025305666992</v>
       </c>
       <c r="C78">
-        <v>-568.9716893418995</v>
+        <v>-621.1551416176446</v>
       </c>
       <c r="D78">
-        <v>1624.156310658101</v>
+        <v>1605.000858382356</v>
       </c>
       <c r="E78">
-        <v>771.1280000000002</v>
+        <v>804.1560000000004</v>
       </c>
       <c r="F78">
-        <v>2510.128</v>
+        <v>2543.156</v>
       </c>
       <c r="G78">
         <v>317</v>
@@ -7811,37 +7811,37 @@
         <v>422</v>
       </c>
       <c r="M78">
-        <v>443.2873185124061</v>
+        <v>449.1200463875693</v>
       </c>
       <c r="N78">
-        <v>-21.2873185124061</v>
+        <v>-27.12004638756935</v>
       </c>
       <c r="O78">
-        <v>-5.747575998349648</v>
+        <v>-7.322412524643724</v>
       </c>
       <c r="P78">
-        <v>-15.53974251405645</v>
+        <v>-19.79763386292562</v>
       </c>
       <c r="Q78">
-        <v>237.4602574859435</v>
+        <v>233.2023661370744</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2319871951678941</v>
+        <v>0.2400822906099764</v>
       </c>
       <c r="T78">
-        <v>2.230474622239215</v>
+        <v>2.327451779727876</v>
       </c>
       <c r="U78">
         <v>0.1765994875609555</v>
       </c>
       <c r="V78">
-        <v>0.2570341971035006</v>
+        <v>0.2536960906476109</v>
       </c>
       <c r="W78">
-        <v>0.1312073800668356</v>
+        <v>0.1317968879563697</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9519785077907427</v>
+        <v>0.939615150546707</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1567025305666992</v>
+        <v>0.1580105254423088</v>
       </c>
       <c r="C79">
-        <v>-621.1551416176446</v>
+        <v>-672.8920184350193</v>
       </c>
       <c r="D79">
-        <v>1605.000858382356</v>
+        <v>1586.291981564981</v>
       </c>
       <c r="E79">
-        <v>804.1560000000004</v>
+        <v>837.1840000000002</v>
       </c>
       <c r="F79">
-        <v>2543.156</v>
+        <v>2576.184</v>
       </c>
       <c r="G79">
         <v>317</v>
@@ -7893,37 +7893,37 @@
         <v>422</v>
       </c>
       <c r="M79">
-        <v>449.1200463875693</v>
+        <v>454.9527742627325</v>
       </c>
       <c r="N79">
-        <v>-27.12004638756935</v>
+        <v>-32.95277426273253</v>
       </c>
       <c r="O79">
-        <v>-7.322412524643724</v>
+        <v>-8.897249050937784</v>
       </c>
       <c r="P79">
-        <v>-19.79763386292562</v>
+        <v>-24.05552521179475</v>
       </c>
       <c r="Q79">
-        <v>233.2023661370744</v>
+        <v>228.9444747882052</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2400822906099764</v>
+        <v>0.2489133038195208</v>
       </c>
       <c r="T79">
-        <v>2.327451779727876</v>
+        <v>2.43324504244278</v>
       </c>
       <c r="U79">
         <v>0.1765994875609555</v>
       </c>
       <c r="V79">
-        <v>0.2536960906476109</v>
+        <v>0.2504435766649493</v>
       </c>
       <c r="W79">
-        <v>0.1317968879563697</v>
+        <v>0.1323712802589926</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.939615150546707</v>
+        <v>0.927568802462775</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1580105254423088</v>
+        <v>0.1593185203179183</v>
       </c>
       <c r="C80">
-        <v>-672.8920184350193</v>
+        <v>-724.1977565282991</v>
       </c>
       <c r="D80">
-        <v>1586.291981564981</v>
+        <v>1568.014243471701</v>
       </c>
       <c r="E80">
-        <v>837.1840000000002</v>
+        <v>870.2120000000004</v>
       </c>
       <c r="F80">
-        <v>2576.184</v>
+        <v>2609.212</v>
       </c>
       <c r="G80">
         <v>317</v>
@@ -7975,37 +7975,37 @@
         <v>422</v>
       </c>
       <c r="M80">
-        <v>454.9527742627325</v>
+        <v>460.7855021378958</v>
       </c>
       <c r="N80">
-        <v>-32.95277426273253</v>
+        <v>-38.78550213789583</v>
       </c>
       <c r="O80">
-        <v>-8.897249050937784</v>
+        <v>-10.47208557723188</v>
       </c>
       <c r="P80">
-        <v>-24.05552521179475</v>
+        <v>-28.31341656066396</v>
       </c>
       <c r="Q80">
-        <v>228.9444747882052</v>
+        <v>224.686583439336</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2489133038195208</v>
+        <v>0.2585853659061647</v>
       </c>
       <c r="T80">
-        <v>2.43324504244278</v>
+        <v>2.549113853987675</v>
       </c>
       <c r="U80">
         <v>0.1765994875609555</v>
       </c>
       <c r="V80">
-        <v>0.2504435766649493</v>
+        <v>0.2472734048084309</v>
       </c>
       <c r="W80">
-        <v>0.1323712802589926</v>
+        <v>0.1329311309843339</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.927568802462775</v>
+        <v>0.9158274252164106</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1593185203179183</v>
+        <v>0.1606265151935279</v>
       </c>
       <c r="C81">
-        <v>-724.1977565282991</v>
+        <v>-775.0870892691482</v>
       </c>
       <c r="D81">
-        <v>1568.014243471701</v>
+        <v>1550.152910730852</v>
       </c>
       <c r="E81">
-        <v>870.2120000000004</v>
+        <v>903.2400000000002</v>
       </c>
       <c r="F81">
-        <v>2609.212</v>
+        <v>2642.24</v>
       </c>
       <c r="G81">
         <v>317</v>
@@ -8057,37 +8057,37 @@
         <v>422</v>
       </c>
       <c r="M81">
-        <v>460.7855021378958</v>
+        <v>466.618230013059</v>
       </c>
       <c r="N81">
-        <v>-38.78550213789583</v>
+        <v>-44.61823001305902</v>
       </c>
       <c r="O81">
-        <v>-10.47208557723188</v>
+        <v>-12.04692210352594</v>
       </c>
       <c r="P81">
-        <v>-28.31341656066396</v>
+        <v>-32.57130790953308</v>
       </c>
       <c r="Q81">
-        <v>224.686583439336</v>
+        <v>220.4286920904669</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2585853659061647</v>
+        <v>0.269224634201473</v>
       </c>
       <c r="T81">
-        <v>2.549113853987675</v>
+        <v>2.676569546687059</v>
       </c>
       <c r="U81">
         <v>0.1765994875609555</v>
       </c>
       <c r="V81">
-        <v>0.2472734048084309</v>
+        <v>0.2441824872483255</v>
       </c>
       <c r="W81">
-        <v>0.1329311309843339</v>
+        <v>0.1334769854415417</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9158274252164106</v>
+        <v>0.9043795824012055</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1606265151935279</v>
+        <v>0.1619345100691374</v>
       </c>
       <c r="C82">
-        <v>-775.0870892691482</v>
+        <v>-825.5740862756377</v>
       </c>
       <c r="D82">
-        <v>1550.152910730852</v>
+        <v>1532.693913724363</v>
       </c>
       <c r="E82">
-        <v>903.2400000000002</v>
+        <v>936.2680000000005</v>
       </c>
       <c r="F82">
-        <v>2642.24</v>
+        <v>2675.268</v>
       </c>
       <c r="G82">
         <v>317</v>
@@ -8139,37 +8139,37 @@
         <v>422</v>
       </c>
       <c r="M82">
-        <v>466.618230013059</v>
+        <v>472.4509578882223</v>
       </c>
       <c r="N82">
-        <v>-44.61823001305902</v>
+        <v>-50.45095788822232</v>
       </c>
       <c r="O82">
-        <v>-12.04692210352594</v>
+        <v>-13.62175862982003</v>
       </c>
       <c r="P82">
-        <v>-32.57130790953308</v>
+        <v>-36.82919925840229</v>
       </c>
       <c r="Q82">
-        <v>220.4286920904669</v>
+        <v>216.1708007415977</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.269224634201473</v>
+        <v>0.2809838254752346</v>
       </c>
       <c r="T82">
-        <v>2.676569546687059</v>
+        <v>2.817441628091641</v>
       </c>
       <c r="U82">
         <v>0.1765994875609555</v>
       </c>
       <c r="V82">
-        <v>0.2441824872483255</v>
+        <v>0.2411678886403215</v>
       </c>
       <c r="W82">
-        <v>0.1334769854415417</v>
+        <v>0.1340093620109171</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.9043795824012055</v>
+        <v>0.8932144023715609</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1619345100691374</v>
+        <v>0.163242504944747</v>
       </c>
       <c r="C83">
-        <v>-825.5740862756377</v>
+        <v>-875.6721903744267</v>
       </c>
       <c r="D83">
-        <v>1532.693913724363</v>
+        <v>1515.623809625574</v>
       </c>
       <c r="E83">
-        <v>936.2680000000005</v>
+        <v>969.2960000000003</v>
       </c>
       <c r="F83">
-        <v>2675.268</v>
+        <v>2708.296</v>
       </c>
       <c r="G83">
         <v>317</v>
@@ -8221,37 +8221,37 @@
         <v>422</v>
       </c>
       <c r="M83">
-        <v>472.4509578882223</v>
+        <v>478.2836857633855</v>
       </c>
       <c r="N83">
-        <v>-50.45095788822232</v>
+        <v>-56.28368576338551</v>
       </c>
       <c r="O83">
-        <v>-13.62175862982003</v>
+        <v>-15.19659515611409</v>
       </c>
       <c r="P83">
-        <v>-36.82919925840229</v>
+        <v>-41.08709060727142</v>
       </c>
       <c r="Q83">
-        <v>216.1708007415977</v>
+        <v>211.9129093927286</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2809838254752346</v>
+        <v>0.2940495935571921</v>
       </c>
       <c r="T83">
-        <v>2.817441628091641</v>
+        <v>2.97396616298562</v>
       </c>
       <c r="U83">
         <v>0.1765994875609555</v>
       </c>
       <c r="V83">
-        <v>0.2411678886403215</v>
+        <v>0.2382268168276347</v>
       </c>
       <c r="W83">
-        <v>0.1340093620109171</v>
+        <v>0.1345287537859176</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8932144023715609</v>
+        <v>0.8823215438060542</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.163242504944747</v>
+        <v>0.1645504998203566</v>
       </c>
       <c r="C84">
-        <v>-875.6721903744267</v>
+        <v>-925.3942521201973</v>
       </c>
       <c r="D84">
-        <v>1515.623809625574</v>
+        <v>1498.929747879803</v>
       </c>
       <c r="E84">
-        <v>969.2960000000003</v>
+        <v>1002.324000000001</v>
       </c>
       <c r="F84">
-        <v>2708.296</v>
+        <v>2741.324000000001</v>
       </c>
       <c r="G84">
         <v>317</v>
@@ -8303,37 +8303,37 @@
         <v>422</v>
       </c>
       <c r="M84">
-        <v>478.2836857633855</v>
+        <v>484.1164136385488</v>
       </c>
       <c r="N84">
-        <v>-56.28368576338551</v>
+        <v>-62.11641363854881</v>
       </c>
       <c r="O84">
-        <v>-15.19659515611409</v>
+        <v>-16.77143168240818</v>
       </c>
       <c r="P84">
-        <v>-41.08709060727142</v>
+        <v>-45.34498195614063</v>
       </c>
       <c r="Q84">
-        <v>211.9129093927286</v>
+        <v>207.6550180438594</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2940495935571921</v>
+        <v>0.3086525108252623</v>
       </c>
       <c r="T84">
-        <v>2.97396616298562</v>
+        <v>3.148905349043599</v>
       </c>
       <c r="U84">
         <v>0.1765994875609555</v>
       </c>
       <c r="V84">
-        <v>0.2382268168276347</v>
+        <v>0.2353566142152535</v>
       </c>
       <c r="W84">
-        <v>0.1345287537859176</v>
+        <v>0.1350356300964602</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8823215438060542</v>
+        <v>0.8716911637601981</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1645504998203566</v>
+        <v>0.1658584946959661</v>
       </c>
       <c r="C85">
-        <v>-925.3942521201973</v>
+        <v>-974.7525620586191</v>
       </c>
       <c r="D85">
-        <v>1498.929747879803</v>
+        <v>1482.599437941381</v>
       </c>
       <c r="E85">
-        <v>1002.324000000001</v>
+        <v>1035.352</v>
       </c>
       <c r="F85">
-        <v>2741.324000000001</v>
+        <v>2774.352</v>
       </c>
       <c r="G85">
         <v>317</v>
@@ -8385,37 +8385,37 @@
         <v>422</v>
       </c>
       <c r="M85">
-        <v>484.1164136385488</v>
+        <v>489.949141513712</v>
       </c>
       <c r="N85">
-        <v>-62.11641363854881</v>
+        <v>-67.94914151371199</v>
       </c>
       <c r="O85">
-        <v>-16.77143168240818</v>
+        <v>-18.34626820870224</v>
       </c>
       <c r="P85">
-        <v>-45.34498195614063</v>
+        <v>-49.60287330500975</v>
       </c>
       <c r="Q85">
-        <v>207.6550180438594</v>
+        <v>203.3971266949902</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3086525108252623</v>
+        <v>0.3250807927518413</v>
       </c>
       <c r="T85">
-        <v>3.148905349043599</v>
+        <v>3.345711933358825</v>
       </c>
       <c r="U85">
         <v>0.1765994875609555</v>
       </c>
       <c r="V85">
-        <v>0.2353566142152535</v>
+        <v>0.23255474976031</v>
       </c>
       <c r="W85">
-        <v>0.1350356300964602</v>
+        <v>0.1355304379234185</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8716911637601981</v>
+        <v>0.8613138880011482</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1658584946959661</v>
+        <v>0.1671664895715756</v>
       </c>
       <c r="C86">
-        <v>-974.7525620586187</v>
+        <v>-1023.75888090309</v>
       </c>
       <c r="D86">
-        <v>1482.599437941381</v>
+        <v>1466.62111909691</v>
       </c>
       <c r="E86">
-        <v>1035.352</v>
+        <v>1068.38</v>
       </c>
       <c r="F86">
-        <v>2774.352</v>
+        <v>2807.38</v>
       </c>
       <c r="G86">
         <v>317</v>
@@ -8467,37 +8467,37 @@
         <v>422</v>
       </c>
       <c r="M86">
-        <v>489.9491415137119</v>
+        <v>495.7818693888752</v>
       </c>
       <c r="N86">
-        <v>-67.94914151371194</v>
+        <v>-73.78186938887518</v>
       </c>
       <c r="O86">
-        <v>-18.34626820870222</v>
+        <v>-19.9211047349963</v>
       </c>
       <c r="P86">
-        <v>-49.60287330500971</v>
+        <v>-53.86076465387888</v>
       </c>
       <c r="Q86">
-        <v>203.3971266949903</v>
+        <v>199.1392353461211</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3250807927518411</v>
+        <v>0.3436995122686305</v>
       </c>
       <c r="T86">
-        <v>3.345711933358822</v>
+        <v>3.568759395582744</v>
       </c>
       <c r="U86">
         <v>0.1765994875609555</v>
       </c>
       <c r="V86">
-        <v>0.23255474976031</v>
+        <v>0.2298188115278358</v>
       </c>
       <c r="W86">
-        <v>0.1355304379234185</v>
+        <v>0.1360136032132719</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8613138880011482</v>
+        <v>0.8511807834364288</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1671664895715756</v>
+        <v>0.1684744844471852</v>
       </c>
       <c r="C87">
-        <v>-1023.75888090309</v>
+        <v>-1072.42446778095</v>
       </c>
       <c r="D87">
-        <v>1466.62111909691</v>
+        <v>1450.983532219049</v>
       </c>
       <c r="E87">
-        <v>1068.38</v>
+        <v>1101.408</v>
       </c>
       <c r="F87">
-        <v>2807.38</v>
+        <v>2840.408</v>
       </c>
       <c r="G87">
         <v>317</v>
@@ -8549,37 +8549,37 @@
         <v>422</v>
       </c>
       <c r="M87">
-        <v>495.7818693888752</v>
+        <v>501.6145972640384</v>
       </c>
       <c r="N87">
-        <v>-73.78186938887518</v>
+        <v>-79.61459726403842</v>
       </c>
       <c r="O87">
-        <v>-19.9211047349963</v>
+        <v>-21.49594126129038</v>
       </c>
       <c r="P87">
-        <v>-53.86076465387888</v>
+        <v>-58.11865600274805</v>
       </c>
       <c r="Q87">
-        <v>199.1392353461211</v>
+        <v>194.8813439972519</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3436995122686305</v>
+        <v>0.364978048859247</v>
       </c>
       <c r="T87">
-        <v>3.568759395582744</v>
+        <v>3.823670780981511</v>
       </c>
       <c r="U87">
         <v>0.1765994875609555</v>
       </c>
       <c r="V87">
-        <v>0.2298188115278358</v>
+        <v>0.2271464997658842</v>
       </c>
       <c r="W87">
-        <v>0.1360136032132719</v>
+        <v>0.1364855321010356</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8511807834364288</v>
+        <v>0.8412833324662378</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1684744844471852</v>
+        <v>0.1697824793227948</v>
       </c>
       <c r="C88">
-        <v>-1072.42446778095</v>
+        <v>-1120.760106691729</v>
       </c>
       <c r="D88">
-        <v>1450.983532219049</v>
+        <v>1435.675893308271</v>
       </c>
       <c r="E88">
-        <v>1101.408</v>
+        <v>1134.436</v>
       </c>
       <c r="F88">
-        <v>2840.408</v>
+        <v>2873.436</v>
       </c>
       <c r="G88">
         <v>317</v>
@@ -8631,37 +8631,37 @@
         <v>422</v>
       </c>
       <c r="M88">
-        <v>501.6145972640384</v>
+        <v>507.4473251392017</v>
       </c>
       <c r="N88">
-        <v>-79.61459726403842</v>
+        <v>-85.44732513920167</v>
       </c>
       <c r="O88">
-        <v>-21.49594126129038</v>
+        <v>-23.07077778758445</v>
       </c>
       <c r="P88">
-        <v>-58.11865600274805</v>
+        <v>-62.37654735161722</v>
       </c>
       <c r="Q88">
-        <v>194.8813439972519</v>
+        <v>190.6234526483828</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.364978048859247</v>
+        <v>0.3895302064638044</v>
       </c>
       <c r="T88">
-        <v>3.823670780981511</v>
+        <v>4.117799302595473</v>
       </c>
       <c r="U88">
         <v>0.1765994875609555</v>
       </c>
       <c r="V88">
-        <v>0.2271464997658842</v>
+        <v>0.2245356204582304</v>
       </c>
       <c r="W88">
-        <v>0.1364855321010356</v>
+        <v>0.1369466120488508</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8412833324662378</v>
+        <v>0.8316134091045568</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1697824793227948</v>
+        <v>0.1710904741984043</v>
       </c>
       <c r="C89">
-        <v>-1120.760106691729</v>
+        <v>-1168.776131308107</v>
       </c>
       <c r="D89">
-        <v>1435.675893308271</v>
+        <v>1420.687868691893</v>
       </c>
       <c r="E89">
-        <v>1134.436</v>
+        <v>1167.464</v>
       </c>
       <c r="F89">
-        <v>2873.436</v>
+        <v>2906.464</v>
       </c>
       <c r="G89">
         <v>317</v>
@@ -8713,37 +8713,37 @@
         <v>422</v>
       </c>
       <c r="M89">
-        <v>507.4473251392017</v>
+        <v>513.280053014365</v>
       </c>
       <c r="N89">
-        <v>-85.44732513920167</v>
+        <v>-91.28005301436497</v>
       </c>
       <c r="O89">
-        <v>-23.07077778758445</v>
+        <v>-24.64561431387854</v>
       </c>
       <c r="P89">
-        <v>-62.37654735161722</v>
+        <v>-66.63443870048643</v>
       </c>
       <c r="Q89">
-        <v>190.6234526483828</v>
+        <v>186.3655612995136</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3895302064638044</v>
+        <v>0.4181743903357882</v>
       </c>
       <c r="T89">
-        <v>4.117799302595473</v>
+        <v>4.460949244478431</v>
       </c>
       <c r="U89">
         <v>0.1765994875609555</v>
       </c>
       <c r="V89">
-        <v>0.2245356204582304</v>
+        <v>0.2219840793166596</v>
       </c>
       <c r="W89">
-        <v>0.1369466120488508</v>
+        <v>0.1373972129069429</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8316134091045568</v>
+        <v>0.8221632567283687</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1710904741984043</v>
+        <v>0.1723984690740139</v>
       </c>
       <c r="C90">
-        <v>-1168.776131308107</v>
+        <v>-1216.482448239438</v>
       </c>
       <c r="D90">
-        <v>1420.687868691893</v>
+        <v>1406.009551760563</v>
       </c>
       <c r="E90">
-        <v>1167.464</v>
+        <v>1200.492</v>
       </c>
       <c r="F90">
-        <v>2906.464</v>
+        <v>2939.492</v>
       </c>
       <c r="G90">
         <v>317</v>
@@ -8795,37 +8795,37 @@
         <v>422</v>
       </c>
       <c r="M90">
-        <v>513.280053014365</v>
+        <v>519.1127808895282</v>
       </c>
       <c r="N90">
-        <v>-91.28005301436497</v>
+        <v>-97.11278088952815</v>
       </c>
       <c r="O90">
-        <v>-24.64561431387854</v>
+        <v>-26.2204508401726</v>
       </c>
       <c r="P90">
-        <v>-66.63443870048643</v>
+        <v>-70.89233004935555</v>
       </c>
       <c r="Q90">
-        <v>186.3655612995136</v>
+        <v>182.1076699506444</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4181743903357882</v>
+        <v>0.4520266076390416</v>
       </c>
       <c r="T90">
-        <v>4.460949244478431</v>
+        <v>4.86649008488556</v>
       </c>
       <c r="U90">
         <v>0.1765994875609555</v>
       </c>
       <c r="V90">
-        <v>0.2219840793166596</v>
+        <v>0.2194898761782701</v>
       </c>
       <c r="W90">
-        <v>0.1373972129069429</v>
+        <v>0.1378376879030554</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8221632567283687</v>
+        <v>0.8129254673269264</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1723984690740139</v>
+        <v>0.1737064639496234</v>
       </c>
       <c r="C91">
-        <v>-1216.482448239438</v>
+        <v>-1263.888558867883</v>
       </c>
       <c r="D91">
-        <v>1406.009551760563</v>
+        <v>1391.631441132118</v>
       </c>
       <c r="E91">
-        <v>1200.492</v>
+        <v>1233.52</v>
       </c>
       <c r="F91">
-        <v>2939.492</v>
+        <v>2972.52</v>
       </c>
       <c r="G91">
         <v>317</v>
@@ -8877,37 +8877,37 @@
         <v>422</v>
       </c>
       <c r="M91">
-        <v>519.1127808895282</v>
+        <v>524.9455087646915</v>
       </c>
       <c r="N91">
-        <v>-97.11278088952815</v>
+        <v>-102.9455087646915</v>
       </c>
       <c r="O91">
-        <v>-26.2204508401726</v>
+        <v>-27.7952873664667</v>
       </c>
       <c r="P91">
-        <v>-70.89233004935555</v>
+        <v>-75.15022139822476</v>
       </c>
       <c r="Q91">
-        <v>182.1076699506444</v>
+        <v>177.8497786017753</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4520266076390416</v>
+        <v>0.4926492684029458</v>
       </c>
       <c r="T91">
-        <v>4.86649008488556</v>
+        <v>5.353139093374117</v>
       </c>
       <c r="U91">
         <v>0.1765994875609555</v>
       </c>
       <c r="V91">
-        <v>0.2194898761782701</v>
+        <v>0.2170510997762893</v>
       </c>
       <c r="W91">
-        <v>0.1378376879030554</v>
+        <v>0.1382683745659209</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8129254673269264</v>
+        <v>0.8038929621344049</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1737064639496234</v>
+        <v>0.226694798513168</v>
       </c>
       <c r="C92">
-        <v>-1263.888558867883</v>
+        <v>-1704.55808862966</v>
       </c>
       <c r="D92">
-        <v>1391.631441132118</v>
+        <v>983.9899113703398</v>
       </c>
       <c r="E92">
-        <v>1233.52</v>
+        <v>1266.548</v>
       </c>
       <c r="F92">
-        <v>2972.52</v>
+        <v>3005.548</v>
       </c>
       <c r="G92">
         <v>317</v>
@@ -8959,45 +8959,45 @@
         <v>422</v>
       </c>
       <c r="M92">
-        <v>524.9455087646915</v>
+        <v>693.0778286398546</v>
       </c>
       <c r="N92">
-        <v>-102.9455087646915</v>
+        <v>-271.0778286398546</v>
       </c>
       <c r="O92">
-        <v>-27.7952873664667</v>
+        <v>-73.19101373276075</v>
       </c>
       <c r="P92">
-        <v>-75.15022139822476</v>
+        <v>-197.8868149070939</v>
       </c>
       <c r="Q92">
-        <v>177.8497786017753</v>
+        <v>55.11318509290615</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4926492684029458</v>
+        <v>0.5705251836469962</v>
       </c>
       <c r="T92">
-        <v>5.353139093374117</v>
+        <v>6.286072491285141</v>
       </c>
       <c r="U92">
-        <v>0.1765994875609555</v>
+        <v>0.2305994875609555</v>
       </c>
       <c r="V92">
-        <v>0.2170510997762893</v>
+        <v>0.1643971214944273</v>
       </c>
       <c r="W92">
-        <v>0.1382683745659209</v>
+        <v>0.1926895955878444</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.8038929621344049</v>
+        <v>0.6088782277571378</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.226694798513168</v>
+        <v>0.2285427933887776</v>
       </c>
       <c r="C93">
-        <v>-1704.55808862966</v>
+        <v>-1747.536731717377</v>
       </c>
       <c r="D93">
-        <v>983.9899113703398</v>
+        <v>974.0392682826239</v>
       </c>
       <c r="E93">
-        <v>1266.548</v>
+        <v>1299.576</v>
       </c>
       <c r="F93">
-        <v>3005.548</v>
+        <v>3038.576</v>
       </c>
       <c r="G93">
         <v>317</v>
@@ -9041,37 +9041,37 @@
         <v>422</v>
       </c>
       <c r="M93">
-        <v>693.0778286398546</v>
+        <v>700.694068515018</v>
       </c>
       <c r="N93">
-        <v>-271.0778286398546</v>
+        <v>-278.694068515018</v>
       </c>
       <c r="O93">
-        <v>-73.19101373276075</v>
+        <v>-75.24739849905487</v>
       </c>
       <c r="P93">
-        <v>-197.8868149070939</v>
+        <v>-203.4466700159631</v>
       </c>
       <c r="Q93">
-        <v>55.11318509290615</v>
+        <v>49.55332998403688</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5705251836469962</v>
+        <v>0.636115831602871</v>
       </c>
       <c r="T93">
-        <v>6.286072491285141</v>
+        <v>7.071831552695787</v>
       </c>
       <c r="U93">
         <v>0.2305994875609555</v>
       </c>
       <c r="V93">
-        <v>0.1643971214944273</v>
+        <v>0.1626101962607921</v>
       </c>
       <c r="W93">
-        <v>0.1926895955878444</v>
+        <v>0.1931016596310304</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.6088782277571378</v>
+        <v>0.602259986151082</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2285427933887776</v>
+        <v>0.2303907882643872</v>
       </c>
       <c r="C94">
-        <v>-1747.536731717377</v>
+        <v>-1790.316136938371</v>
       </c>
       <c r="D94">
-        <v>974.0392682826239</v>
+        <v>964.2878630616298</v>
       </c>
       <c r="E94">
-        <v>1299.576</v>
+        <v>1332.604</v>
       </c>
       <c r="F94">
-        <v>3038.576</v>
+        <v>3071.604</v>
       </c>
       <c r="G94">
         <v>317</v>
@@ -9123,37 +9123,37 @@
         <v>422</v>
       </c>
       <c r="M94">
-        <v>700.694068515018</v>
+        <v>708.3103083901811</v>
       </c>
       <c r="N94">
-        <v>-278.694068515018</v>
+        <v>-286.3103083901811</v>
       </c>
       <c r="O94">
-        <v>-75.24739849905487</v>
+        <v>-77.30378326534891</v>
       </c>
       <c r="P94">
-        <v>-203.4466700159631</v>
+        <v>-209.0065251248323</v>
       </c>
       <c r="Q94">
-        <v>49.55332998403688</v>
+        <v>43.99347487516775</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.636115831602871</v>
+        <v>0.7204466646889957</v>
       </c>
       <c r="T94">
-        <v>7.071831552695787</v>
+        <v>8.082093203080902</v>
       </c>
       <c r="U94">
         <v>0.2305994875609555</v>
       </c>
       <c r="V94">
-        <v>0.1626101962607921</v>
+        <v>0.1608616995268051</v>
       </c>
       <c r="W94">
-        <v>0.1931016596310304</v>
+        <v>0.1935048620818898</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.602259986151082</v>
+        <v>0.5957840723215004</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2303907882643872</v>
+        <v>0.2322387831399967</v>
       </c>
       <c r="C95">
-        <v>-1790.316136938371</v>
+        <v>-1832.902228873632</v>
       </c>
       <c r="D95">
-        <v>964.2878630616298</v>
+        <v>954.7297711263686</v>
       </c>
       <c r="E95">
-        <v>1332.604</v>
+        <v>1365.632000000001</v>
       </c>
       <c r="F95">
-        <v>3071.604</v>
+        <v>3104.632000000001</v>
       </c>
       <c r="G95">
         <v>317</v>
@@ -9205,37 +9205,37 @@
         <v>422</v>
       </c>
       <c r="M95">
-        <v>708.3103083901811</v>
+        <v>715.9265482653444</v>
       </c>
       <c r="N95">
-        <v>-286.3103083901811</v>
+        <v>-293.9265482653444</v>
       </c>
       <c r="O95">
-        <v>-77.30378326534891</v>
+        <v>-79.360168031643</v>
       </c>
       <c r="P95">
-        <v>-209.0065251248323</v>
+        <v>-214.5663802337014</v>
       </c>
       <c r="Q95">
-        <v>43.99347487516775</v>
+        <v>38.43361976629859</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7204466646889957</v>
+        <v>0.832887775470495</v>
       </c>
       <c r="T95">
-        <v>8.082093203080902</v>
+        <v>9.42910873692772</v>
       </c>
       <c r="U95">
         <v>0.2305994875609555</v>
       </c>
       <c r="V95">
-        <v>0.1608616995268051</v>
+        <v>0.1591504048509881</v>
       </c>
       <c r="W95">
-        <v>0.1935048620818898</v>
+        <v>0.193899485757199</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5957840723215004</v>
+        <v>0.5894459438925483</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2322387831399967</v>
+        <v>0.2340867780156063</v>
       </c>
       <c r="C96">
-        <v>-1832.902228873632</v>
+        <v>-1875.300699510116</v>
       </c>
       <c r="D96">
-        <v>954.7297711263686</v>
+        <v>945.3593004898843</v>
       </c>
       <c r="E96">
-        <v>1365.632000000001</v>
+        <v>1398.66</v>
       </c>
       <c r="F96">
-        <v>3104.632000000001</v>
+        <v>3137.66</v>
       </c>
       <c r="G96">
         <v>317</v>
@@ -9287,37 +9287,37 @@
         <v>422</v>
       </c>
       <c r="M96">
-        <v>715.9265482653444</v>
+        <v>723.5427881405076</v>
       </c>
       <c r="N96">
-        <v>-293.9265482653444</v>
+        <v>-301.5427881405076</v>
       </c>
       <c r="O96">
-        <v>-79.360168031643</v>
+        <v>-81.41655279793706</v>
       </c>
       <c r="P96">
-        <v>-214.5663802337014</v>
+        <v>-220.1262353425705</v>
       </c>
       <c r="Q96">
-        <v>38.43361976629859</v>
+        <v>32.87376465742949</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.832887775470495</v>
+        <v>0.9903053305645944</v>
       </c>
       <c r="T96">
-        <v>9.42910873692772</v>
+        <v>11.31493048431327</v>
       </c>
       <c r="U96">
         <v>0.2305994875609555</v>
       </c>
       <c r="V96">
-        <v>0.1591504048509881</v>
+        <v>0.157475137431504</v>
       </c>
       <c r="W96">
-        <v>0.193899485757199</v>
+        <v>0.1942858015656596</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5894459438925483</v>
+        <v>0.5832412497463111</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2340867780156063</v>
+        <v>0.2359347728912159</v>
       </c>
       <c r="C97">
-        <v>-1875.300699510116</v>
+        <v>-1917.51701954411</v>
       </c>
       <c r="D97">
-        <v>945.3593004898843</v>
+        <v>936.1709804558906</v>
       </c>
       <c r="E97">
-        <v>1398.66</v>
+        <v>1431.688000000001</v>
       </c>
       <c r="F97">
-        <v>3137.66</v>
+        <v>3170.688000000001</v>
       </c>
       <c r="G97">
         <v>317</v>
@@ -9369,37 +9369,37 @@
         <v>422</v>
       </c>
       <c r="M97">
-        <v>723.5427881405076</v>
+        <v>731.1590280156709</v>
       </c>
       <c r="N97">
-        <v>-301.5427881405076</v>
+        <v>-309.1590280156709</v>
       </c>
       <c r="O97">
-        <v>-81.41655279793706</v>
+        <v>-83.47293756423113</v>
       </c>
       <c r="P97">
-        <v>-220.1262353425705</v>
+        <v>-225.6860904514397</v>
       </c>
       <c r="Q97">
-        <v>32.87376465742949</v>
+        <v>27.31390954856028</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9903053305645944</v>
+        <v>1.226431663205744</v>
       </c>
       <c r="T97">
-        <v>11.31493048431327</v>
+        <v>14.14366310539159</v>
       </c>
       <c r="U97">
         <v>0.2305994875609555</v>
       </c>
       <c r="V97">
-        <v>0.157475137431504</v>
+        <v>0.1558347714165925</v>
       </c>
       <c r="W97">
-        <v>0.1942858015656596</v>
+        <v>0.1946640691281106</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5832412497463111</v>
+        <v>0.5771658200614536</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2359347728912158</v>
+        <v>0.2377827677668254</v>
       </c>
       <c r="C98">
-        <v>-1917.517019544109</v>
+        <v>-1959.55644903177</v>
       </c>
       <c r="D98">
-        <v>936.1709804558909</v>
+        <v>927.1595509682296</v>
       </c>
       <c r="E98">
-        <v>1431.688</v>
+        <v>1464.716</v>
       </c>
       <c r="F98">
-        <v>3170.688</v>
+        <v>3203.716</v>
       </c>
       <c r="G98">
         <v>317</v>
@@ -9451,37 +9451,37 @@
         <v>422</v>
       </c>
       <c r="M98">
-        <v>731.1590280156707</v>
+        <v>738.775267890834</v>
       </c>
       <c r="N98">
-        <v>-309.1590280156707</v>
+        <v>-316.775267890834</v>
       </c>
       <c r="O98">
-        <v>-83.4729375642311</v>
+        <v>-85.52932233052519</v>
       </c>
       <c r="P98">
-        <v>-225.6860904514396</v>
+        <v>-231.2459455603088</v>
       </c>
       <c r="Q98">
-        <v>27.31390954856036</v>
+        <v>21.75405443969117</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.22643166320574</v>
+        <v>1.619975550940987</v>
       </c>
       <c r="T98">
-        <v>14.14366310539155</v>
+        <v>18.85821747385541</v>
       </c>
       <c r="U98">
         <v>0.2305994875609555</v>
       </c>
       <c r="V98">
-        <v>0.1558347714165925</v>
+        <v>0.1542282273813699</v>
       </c>
       <c r="W98">
-        <v>0.1946640691281106</v>
+        <v>0.1950345373593771</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5771658200614537</v>
+        <v>0.5712156569680367</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2377827677668254</v>
+        <v>0.2396307626424349</v>
       </c>
       <c r="C99">
-        <v>-1959.55644903177</v>
+        <v>-2001.424047430413</v>
       </c>
       <c r="D99">
-        <v>927.1595509682296</v>
+        <v>918.3199525695873</v>
       </c>
       <c r="E99">
-        <v>1464.716</v>
+        <v>1497.744</v>
       </c>
       <c r="F99">
-        <v>3203.716</v>
+        <v>3236.744</v>
       </c>
       <c r="G99">
         <v>317</v>
@@ -9533,37 +9533,37 @@
         <v>422</v>
       </c>
       <c r="M99">
-        <v>738.775267890834</v>
+        <v>746.3915077659973</v>
       </c>
       <c r="N99">
-        <v>-316.775267890834</v>
+        <v>-324.3915077659973</v>
       </c>
       <c r="O99">
-        <v>-85.52932233052519</v>
+        <v>-87.58570709681928</v>
       </c>
       <c r="P99">
-        <v>-231.2459455603088</v>
+        <v>-236.805800669178</v>
       </c>
       <c r="Q99">
-        <v>21.75405443969117</v>
+        <v>16.19419933082199</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.619975550940987</v>
+        <v>2.40706332641148</v>
       </c>
       <c r="T99">
-        <v>18.85821747385541</v>
+        <v>28.28732621078311</v>
       </c>
       <c r="U99">
         <v>0.2305994875609555</v>
       </c>
       <c r="V99">
-        <v>0.1542282273813699</v>
+        <v>0.152654469959111</v>
       </c>
       <c r="W99">
-        <v>0.1950345373593771</v>
+        <v>0.1953974450144952</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5712156569680367</v>
+        <v>0.5653869257744852</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2396307626424349</v>
+        <v>0.2414787575180445</v>
       </c>
       <c r="C100">
-        <v>-2001.424047430413</v>
+        <v>-2043.124683070805</v>
       </c>
       <c r="D100">
-        <v>918.3199525695873</v>
+        <v>909.6473169291951</v>
       </c>
       <c r="E100">
-        <v>1497.744</v>
+        <v>1530.772</v>
       </c>
       <c r="F100">
-        <v>3236.744</v>
+        <v>3269.772</v>
       </c>
       <c r="G100">
         <v>317</v>
@@ -9615,37 +9615,37 @@
         <v>422</v>
       </c>
       <c r="M100">
-        <v>746.3915077659973</v>
+        <v>754.0077476411604</v>
       </c>
       <c r="N100">
-        <v>-324.3915077659973</v>
+        <v>-332.0077476411604</v>
       </c>
       <c r="O100">
-        <v>-87.58570709681928</v>
+        <v>-89.64209186311332</v>
       </c>
       <c r="P100">
-        <v>-236.805800669178</v>
+        <v>-242.3656557780471</v>
       </c>
       <c r="Q100">
-        <v>16.19419933082199</v>
+        <v>10.63434422195286</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.40706332641148</v>
+        <v>4.768326652822961</v>
       </c>
       <c r="T100">
-        <v>28.28732621078311</v>
+        <v>56.57465242156621</v>
       </c>
       <c r="U100">
         <v>0.2305994875609555</v>
       </c>
       <c r="V100">
-        <v>0.152654469959111</v>
+        <v>0.1511125056160897</v>
       </c>
       <c r="W100">
-        <v>0.1953974450144952</v>
+        <v>0.1957530212018332</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5653869257744852</v>
+        <v>0.5596759467262582</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2414787575180445</v>
-      </c>
-      <c r="C101">
-        <v>-2043.124683070805</v>
-      </c>
-      <c r="D101">
-        <v>909.6473169291951</v>
-      </c>
-      <c r="E101">
-        <v>1530.772</v>
-      </c>
-      <c r="F101">
-        <v>3269.772</v>
-      </c>
-      <c r="G101">
-        <v>317</v>
-      </c>
-      <c r="H101">
-        <v>1563.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>675</v>
-      </c>
-      <c r="K101">
-        <v>253</v>
-      </c>
-      <c r="L101">
-        <v>422</v>
-      </c>
-      <c r="M101">
-        <v>754.0077476411604</v>
-      </c>
-      <c r="N101">
-        <v>-332.0077476411604</v>
-      </c>
-      <c r="O101">
-        <v>-89.64209186311332</v>
-      </c>
-      <c r="P101">
-        <v>-242.3656557780471</v>
-      </c>
-      <c r="Q101">
-        <v>10.63434422195286</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.768326652822961</v>
-      </c>
-      <c r="T101">
-        <v>56.57465242156621</v>
-      </c>
-      <c r="U101">
-        <v>0.2305994875609555</v>
-      </c>
-      <c r="V101">
-        <v>0.1511125056160897</v>
-      </c>
-      <c r="W101">
-        <v>0.1957530212018332</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5596759467262582</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
